--- a/LC-CNC-BoM.xlsx
+++ b/LC-CNC-BoM.xlsx
@@ -5774,8 +5774,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="09e37f2ef9bef24154c689c9241203a8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c23ee64ebe9444b24c4b4ef6420ff96" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="71752533c218a459f0bd7314a8d27046">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56df45e61c8cd6f396207a6803100ce0" ns2:_="" ns3:_="">
     <xsd:import namespace="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
     <xsd:import namespace="fb0bfce0-b493-4733-b695-336371de64d4"/>
     <xsd:element name="properties">
@@ -6007,22 +6007,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30F3C9A4-0D35-4985-9741-8479EE24B4B4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
-    <ds:schemaRef ds:uri="fb0bfce0-b493-4733-b695-336371de64d4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E33DD76D-016E-470E-8735-9C85C5BAFB60}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/LC-CNC-BoM.xlsx
+++ b/LC-CNC-BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk.sharepoint.com/sites/UT_DesktopMillingMachine/Shared Documents/General/GitHub-LC_CNC/LC-CNC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1089" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AC1B661-39A2-417C-8ADB-EB4069B0300D}"/>
+  <xr:revisionPtr revIDLastSave="1155" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02B4FEA4-E866-490C-B39E-BE71B8103833}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="320">
   <si>
     <t>Item</t>
   </si>
@@ -725,12 +725,6 @@
     <t xml:space="preserve">https://www.amazon.com/gp/product/B0CJR4Y192/ref=ox_sc_act_title_2?smid=A1NCCSMTWFDZ34&amp;psc=1 </t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.amazon.com/Ethernet-Kit-for-Teensy-4-1/dp/B08CTM1L64/ref=sr_1_5?dib=eyJ2IjoiMSJ9.SbX6rnuR22BHW7UQV6IYcckSiyAyB1ZWr3cUVGCpjmoe8u9La0C4CnpYOniX7CwAfqWVpgmjNbJjLT76DhWe4ldG5P2p4WMYyJenE908txxUrz8DSqOHEjh3oVZE2stHV0rzuhfvuwF3CawGYaDmSg.85Xw8ylPJeTNJvqmoxZDt0Th8_d0wMGVyuH5z7GC-TU&amp;dib_tag=se&amp;qid=1752729706&amp;refinements=p_89%3APJRC&amp;sr=8-5&amp;srs=36931437011 </t>
-  </si>
-  <si>
-    <t>Ethernet Kit</t>
-  </si>
-  <si>
     <t>DAYTON Definite Purpose Magnetic Contactor</t>
   </si>
   <si>
@@ -740,9 +734,6 @@
     <t xml:space="preserve">https://www.amazon.com/dp/B07PZ1WB8S?psc=1&amp;smid=A26VZBPE6PT1GF&amp;ref_=chk_typ_imgToDp </t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.amazon.com/dp/B07TF63R4C?ref_=ppx_hzsearch_conn_dt_b_fed_asin_title_1&amp;th=1 </t>
-  </si>
-  <si>
     <t>10mm to 10mm Shaft Coupling</t>
   </si>
   <si>
@@ -752,9 +743,6 @@
     <t>NEMA 23 Stepper motor 3N-m</t>
   </si>
   <si>
-    <t>https://www.amazon.com/Jienk-KF2EDGK-Terminal-Connector-28-16AWG/dp/B09MHHPP25/ref=sr_1_1_sspa?crid=2AF6A8D8LGV1K&amp;dib=eyJ2IjoiMSJ9.q8IUsYwpHtwxUC4nKvpJJ5E3n8pZqTCBNDUZZZwpJz_cY5sNj3Fq76Fy-Qnl1SgjaCW2vPd-EN-SsNTXsL9li_txRXQWnoG51gzzu7XBZrvcrjbQGV51a41TxeymCRPUBDor-8_OKXwXbrqD6LX23dlwi0A05TCkdYOAKwf1qqH9OT2I9a3h0Ac3SfDbmvdbfLXlcB7ni4DL0bvN6Q3YXHRrUgVij9zRpT0E_MxOV6Sc2uY1_kpXSAUZYY2AG26Cmhr6jE0nPlKpJdHwt2ypNz4mNYmt0n1t5oVeAsT5yLw.bsp1pXhc1Is0gq2fnd2DtSPfsxI0LFXOwK2HSn65Ex0&amp;dib_tag=se&amp;keywords=KF2EDGK%2B3.5mm%2BPitch%2BScrew%2BTerminal%2BBlock&amp;qid=1752780492&amp;s=industrial&amp;sprefix=kf2edgk%2B3.5mm%2Bpitch%2Bscrew%2Bterminal%2Bblock%2Cindustrial%2C95&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 Pin Terminal Block </t>
   </si>
   <si>
@@ -797,16 +785,7 @@
     <t>Breakout board</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.amazon.com/gp/product/B0CJ26FGZC/ref=ox_sc_act_title_2?smid=A2IFOCZBWBH5F8&amp;th=1 </t>
-  </si>
-  <si>
     <t>110v Spindle Motor Kit，2.2Kw Square Air Cooled Spindle Motor 24000Rpm 400Hz ，VFD Variable Frequency Drive ，7 pcs ER11 Collets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.com/gp/product/B09VXH18J8/ref=ewc_pr_img_1?smid=A3E9T3KQ1YPBBY&amp;th=1 </t>
-  </si>
-  <si>
-    <t>RATTMMOTOR 2.2KW VFD</t>
   </si>
   <si>
     <t>Stub Allen Key set</t>
@@ -933,9 +912,6 @@
     <t xml:space="preserve">https://www.mcmaster.com/90031A151/ </t>
   </si>
   <si>
-    <t>Need to add:</t>
-  </si>
-  <si>
     <t>NOTE: Only one set of tools needed</t>
   </si>
   <si>
@@ -1024,9 +1000,6 @@
     </r>
   </si>
   <si>
-    <t>super glue</t>
-  </si>
-  <si>
     <t>1CH Optocoupler isolation board</t>
   </si>
   <si>
@@ -1063,19 +1036,31 @@
     <t xml:space="preserve">https://www.amazon.com/gp/product/B0BY51FJGY/ref=ewc_pr_img_1?smid=AO6JMNGOG26ZH&amp;th=1 </t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t>old motors for x and y</t>
-  </si>
-  <si>
-    <t>Spindle Option 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.com/gp/product/B0B99QL131/ref=ox_sc_act_title_2?th=1 </t>
-  </si>
-  <si>
-    <t>110v Spindle Motor Kit，1.5Kw Square Air Cooled Spindle Motor 24000Rpm 400Hz ，VFD Variable Frequency Drive ，7 pcs ER11 Collets</t>
+    <t xml:space="preserve">https://a.co/d/04KkNO5x </t>
+  </si>
+  <si>
+    <t>NEMA 23 Stepper motor 2.4N-m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/0cYAOFF7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/0aCp7x5M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/0c78GAUY </t>
+  </si>
+  <si>
+    <t>8mm to 10mm Shaft Coupling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/04Kofe6e </t>
+  </si>
+  <si>
+    <t>Teensy 4.1 Ethernet Kit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/07VW1Jxs </t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1071,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1171,15 +1156,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1212,7 +1188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1696,94 +1672,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1813,13 +1707,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1846,23 +1739,14 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1876,31 +1760,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2182,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AA107"/>
+  <dimension ref="B1:R107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -2195,87 +2079,87 @@
     <col min="22" max="22" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="72" t="s">
         <v>187</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="61"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="74"/>
       <c r="G2" s="19">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K2" s="72" t="s">
-        <v>282</v>
-      </c>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="74"/>
-    </row>
-    <row r="3" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
+      <c r="K2" s="55" t="s">
+        <v>274</v>
+      </c>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="57"/>
+    </row>
+    <row r="3" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="44" t="s">
+      <c r="C3" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="F3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="44" t="s">
+      <c r="G3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="J3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="44" t="s">
+      <c r="K3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="44" t="s">
+      <c r="M3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="44" t="s">
+      <c r="N3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="44" t="s">
+      <c r="O3" s="43" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="62" t="s">
+    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="J4" s="62" t="s">
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="J4" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-    </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="60"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
@@ -2285,16 +2169,16 @@
       <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="39">
-        <f>G2*10</f>
-        <v>10</v>
+      <c r="E5" s="38">
+        <f>G2*15</f>
+        <v>15</v>
       </c>
       <c r="F5" s="5">
         <v>3.33</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="39">
         <f>E5*F5</f>
-        <v>33.299999999999997</v>
+        <v>49.95</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>143</v>
@@ -2311,31 +2195,30 @@
       <c r="N5" s="5">
         <v>20.99</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="39">
         <f t="shared" ref="O5:O13" si="0">M5*N5</f>
         <v>20.99</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="37">
-        <f>G2*10</f>
-        <v>10</v>
-      </c>
-      <c r="F6" s="36">
+      <c r="D6" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="36">
+        <v>15</v>
+      </c>
+      <c r="F6" s="35">
         <v>1.73</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="37">
         <f t="shared" ref="G6" si="1">E6*F6</f>
-        <v>17.3</v>
+        <v>25.95</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>12</v>
@@ -2357,15 +2240,15 @@
         <v>14.99</v>
       </c>
     </row>
-    <row r="7" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="62" t="s">
+    <row r="7" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="64"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="60"/>
       <c r="J7" s="2" t="s">
         <v>178</v>
       </c>
@@ -2386,26 +2269,26 @@
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>324</v>
+        <v>249</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="38">
         <f>G2*1</f>
         <v>1</v>
       </c>
       <c r="F8" s="5">
-        <v>278.99</v>
-      </c>
-      <c r="G8" s="40">
+        <v>359.99</v>
+      </c>
+      <c r="G8" s="39">
         <f t="shared" ref="G8:G14" si="2">E8*F8</f>
-        <v>278.99</v>
+        <v>359.99</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>179</v>
@@ -2427,7 +2310,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>120</v>
       </c>
@@ -2468,12 +2351,12 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>9</v>
@@ -2509,7 +2392,7 @@
         <v>27.99</v>
       </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
@@ -2550,7 +2433,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
@@ -2591,7 +2474,7 @@
         <v>18.690000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
@@ -2613,10 +2496,10 @@
         <v>16.989999999999998</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>9</v>
@@ -2632,7 +2515,7 @@
         <v>24.99</v>
       </c>
     </row>
-    <row r="14" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2672,11 +2555,8 @@
         <f t="shared" ref="O14:O20" si="3">M14*N14</f>
         <v>15.09</v>
       </c>
-      <c r="V14" s="78" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>121</v>
       </c>
@@ -2716,28 +2596,8 @@
         <f t="shared" si="3"/>
         <v>25.5</v>
       </c>
-      <c r="V15" s="79" t="s">
-        <v>254</v>
-      </c>
-      <c r="W15" s="80" t="s">
-        <v>253</v>
-      </c>
-      <c r="X15" s="81" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y15" s="82">
-        <f>AA9*1</f>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="83">
-        <v>209.99</v>
-      </c>
-      <c r="AA15" s="84">
-        <f t="shared" ref="AA15:AA16" si="4">Y15*Z15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>24</v>
       </c>
@@ -2777,33 +2637,13 @@
         <f t="shared" si="3"/>
         <v>162</v>
       </c>
-      <c r="V16" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="W16" s="85" t="s">
-        <v>255</v>
-      </c>
-      <c r="X16" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y16" s="86">
-        <f>AA9*1</f>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="31">
-        <v>90</v>
-      </c>
-      <c r="AA16" s="32">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>9</v>
@@ -2816,7 +2656,7 @@
         <v>6.39</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" ref="G17:G22" si="5">E17*F17</f>
+        <f t="shared" ref="G17:G22" si="4">E17*F17</f>
         <v>6.39</v>
       </c>
       <c r="J17" s="2" t="s">
@@ -2839,7 +2679,7 @@
         <v>23.99</v>
       </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
@@ -2857,7 +2697,7 @@
         <v>12.99</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>12.99</v>
       </c>
       <c r="J18" s="2" t="s">
@@ -2879,16 +2719,13 @@
         <f t="shared" si="3"/>
         <v>13.99</v>
       </c>
-      <c r="V18" s="23" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>9</v>
@@ -2901,7 +2738,7 @@
         <v>9.99</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>19.98</v>
       </c>
       <c r="J19" s="2" t="s">
@@ -2923,11 +2760,8 @@
         <f t="shared" si="3"/>
         <v>12.81</v>
       </c>
-      <c r="V19" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="20" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
@@ -2945,7 +2779,7 @@
         <v>39.99</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>39.99</v>
       </c>
       <c r="J20" s="16" t="s">
@@ -2954,21 +2788,21 @@
       <c r="K20" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="L20" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M20" s="35">
-        <v>1</v>
-      </c>
-      <c r="N20" s="36">
+      <c r="L20" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M20" s="34">
+        <v>1</v>
+      </c>
+      <c r="N20" s="35">
         <v>34.97</v>
       </c>
-      <c r="O20" s="38">
+      <c r="O20" s="37">
         <f t="shared" si="3"/>
         <v>34.97</v>
       </c>
     </row>
-    <row r="21" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
@@ -2986,22 +2820,19 @@
         <v>34.69</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>69.38</v>
       </c>
-      <c r="J21" s="62" t="s">
+      <c r="J21" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="63"/>
-      <c r="L21" s="63"/>
-      <c r="M21" s="63"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="64"/>
-      <c r="V21" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="K21" s="59"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="60"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>32</v>
       </c>
@@ -3019,7 +2850,7 @@
         <v>40.39</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>40.39</v>
       </c>
       <c r="J22" s="2" t="s">
@@ -3037,12 +2868,12 @@
       <c r="N22" s="5">
         <v>9.5399999999999991</v>
       </c>
-      <c r="O22" s="40">
-        <f t="shared" ref="O22:O25" si="6">M22*N22</f>
+      <c r="O22" s="39">
+        <f t="shared" ref="O22:O25" si="5">M22*N22</f>
         <v>9.5399999999999991</v>
       </c>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>34</v>
       </c>
@@ -3079,11 +2910,11 @@
         <v>41.86</v>
       </c>
       <c r="O23" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>41.86</v>
       </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
@@ -3101,7 +2932,7 @@
         <v>8.99</v>
       </c>
       <c r="G24" s="6">
-        <f t="shared" ref="G24:G43" si="7">E24*F24</f>
+        <f t="shared" ref="G24:G45" si="6">E24*F24</f>
         <v>8.99</v>
       </c>
       <c r="J24" s="2" t="s">
@@ -3120,11 +2951,11 @@
         <v>36.15</v>
       </c>
       <c r="O24" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>36.15</v>
       </c>
     </row>
-    <row r="25" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
@@ -3142,7 +2973,7 @@
         <v>48.99</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>48.99</v>
       </c>
       <c r="J25" s="16" t="s">
@@ -3151,24 +2982,24 @@
       <c r="K25" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="L25" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M25" s="35">
-        <v>1</v>
-      </c>
-      <c r="N25" s="36">
+      <c r="L25" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M25" s="34">
+        <v>1</v>
+      </c>
+      <c r="N25" s="35">
         <v>7.55</v>
       </c>
-      <c r="O25" s="38">
-        <f t="shared" si="6"/>
+      <c r="O25" s="37">
+        <f t="shared" si="5"/>
         <v>7.55</v>
       </c>
       <c r="R25" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>39</v>
       </c>
@@ -3186,19 +3017,19 @@
         <v>8.99</v>
       </c>
       <c r="G26" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>8.99</v>
       </c>
-      <c r="J26" s="62" t="s">
+      <c r="J26" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="K26" s="63"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="64"/>
-    </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="60"/>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>41</v>
       </c>
@@ -3216,7 +3047,7 @@
         <v>124</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>124</v>
       </c>
       <c r="J27" s="2" t="s">
@@ -3234,12 +3065,12 @@
       <c r="N27" s="5">
         <v>55.35</v>
       </c>
-      <c r="O27" s="40">
+      <c r="O27" s="39">
         <f>M27*N27</f>
         <v>55.35</v>
       </c>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
@@ -3257,7 +3088,7 @@
         <v>45.34</v>
       </c>
       <c r="G28" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>45.34</v>
       </c>
       <c r="J28" s="2" t="s">
@@ -3276,11 +3107,11 @@
         <v>35.76</v>
       </c>
       <c r="O28" s="6">
-        <f t="shared" ref="O28:O29" si="8">M28*N28</f>
+        <f t="shared" ref="O28:O29" si="7">M28*N28</f>
         <v>35.76</v>
       </c>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>57</v>
       </c>
@@ -3317,11 +3148,11 @@
         <v>30.07</v>
       </c>
       <c r="O29" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>30.07</v>
       </c>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
@@ -3339,7 +3170,7 @@
         <v>51.74</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" ref="G30" si="9">E30*F30</f>
+        <f t="shared" ref="G30" si="8">E30*F30</f>
         <v>51.74</v>
       </c>
       <c r="J30" s="2" t="s">
@@ -3362,7 +3193,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>61</v>
       </c>
@@ -3380,7 +3211,7 @@
         <v>15.99</v>
       </c>
       <c r="G31" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>15.99</v>
       </c>
       <c r="J31" s="2" t="s">
@@ -3403,7 +3234,7 @@
         <v>87.75</v>
       </c>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>134</v>
       </c>
@@ -3421,7 +3252,7 @@
         <v>7.69</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7.69</v>
       </c>
       <c r="J32" s="2" t="s">
@@ -3462,7 +3293,7 @@
         <v>11.47</v>
       </c>
       <c r="G33" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>11.47</v>
       </c>
       <c r="J33" s="2" t="s">
@@ -3503,7 +3334,7 @@
         <v>12.99</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" ref="G34" si="10">E34*F34</f>
+        <f t="shared" ref="G34" si="9">E34*F34</f>
         <v>12.99</v>
       </c>
       <c r="J34" s="2" t="s">
@@ -3522,7 +3353,7 @@
         <v>84.66</v>
       </c>
       <c r="O34" s="6">
-        <f t="shared" ref="O34" si="11">M34*N34</f>
+        <f t="shared" ref="O34" si="10">M34*N34</f>
         <v>84.66</v>
       </c>
     </row>
@@ -3563,16 +3394,16 @@
         <v>102.36</v>
       </c>
       <c r="O35" s="6">
-        <f t="shared" ref="O35" si="12">M35*N35</f>
+        <f t="shared" ref="O35" si="11">M35*N35</f>
         <v>102.36</v>
       </c>
     </row>
     <row r="36" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>9</v>
@@ -3584,16 +3415,16 @@
         <v>13.99</v>
       </c>
       <c r="G36" s="6">
-        <f t="shared" ref="G36:G37" si="13">E36*F36</f>
+        <f t="shared" ref="G36:G37" si="12">E36*F36</f>
         <v>13.99</v>
       </c>
-      <c r="J36" s="65" t="s">
+      <c r="J36" s="61" t="s">
         <v>196</v>
       </c>
-      <c r="K36" s="66"/>
-      <c r="L36" s="66"/>
-      <c r="M36" s="66"/>
-      <c r="N36" s="67"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="62"/>
+      <c r="M36" s="62"/>
+      <c r="N36" s="63"/>
       <c r="O36" s="14">
         <f>SUM(O5:O35)</f>
         <v>1259.6799999999998</v>
@@ -3601,10 +3432,10 @@
     </row>
     <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>9</v>
@@ -3617,7 +3448,7 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G37" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>39.979999999999997</v>
       </c>
     </row>
@@ -3645,20 +3476,20 @@
       <c r="J38" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="K38" s="72" t="s">
-        <v>284</v>
-      </c>
-      <c r="L38" s="73"/>
-      <c r="M38" s="73"/>
-      <c r="N38" s="73"/>
-      <c r="O38" s="74"/>
+      <c r="K38" s="55" t="s">
+        <v>276</v>
+      </c>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="57"/>
     </row>
     <row r="39" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>229</v>
+        <v>319</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>9</v>
@@ -3668,37 +3499,37 @@
         <v>1</v>
       </c>
       <c r="F39" s="5">
-        <v>8.5399999999999991</v>
+        <v>9.99</v>
       </c>
       <c r="G39" s="6">
-        <f>E39*F39</f>
-        <v>8.5399999999999991</v>
-      </c>
-      <c r="J39" s="47" t="s">
+        <f t="shared" ref="G39:G44" si="13">E39*F39</f>
+        <v>9.99</v>
+      </c>
+      <c r="J39" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="K39" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="L39" s="44" t="s">
+      <c r="K39" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="L39" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="M39" s="44" t="s">
+      <c r="M39" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="N39" s="44" t="s">
+      <c r="N39" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="O39" s="44" t="s">
+      <c r="O39" s="43" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>238</v>
+        <v>234</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>233</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>9</v>
@@ -3708,43 +3539,44 @@
         <v>1</v>
       </c>
       <c r="F40" s="5">
-        <v>9.99</v>
+        <v>39.99</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" ref="G40:G42" si="14">E40*F40</f>
-        <v>9.99</v>
-      </c>
-      <c r="J40" s="62" t="s">
+        <f t="shared" si="13"/>
+        <v>39.99</v>
+      </c>
+      <c r="J40" s="58" t="s">
         <v>217</v>
       </c>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
-      <c r="O40" s="69"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="67"/>
+      <c r="O40" s="68"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>236</v>
+        <v>312</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>313</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E41" s="20">
-        <v>1</v>
+        <f>G2*2</f>
+        <v>2</v>
       </c>
       <c r="F41" s="5">
-        <v>39.99</v>
+        <v>25.99</v>
       </c>
       <c r="G41" s="6">
-        <f t="shared" si="14"/>
-        <v>39.99</v>
+        <f t="shared" si="13"/>
+        <v>51.98</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>218</v>
@@ -3758,17 +3590,17 @@
       <c r="N41" s="5">
         <v>77.319999999999993</v>
       </c>
-      <c r="O41" s="40">
-        <f t="shared" ref="O41:O42" si="15">M41*N41</f>
+      <c r="O41" s="39">
+        <f t="shared" ref="O41:O42" si="14">M41*N41</f>
         <v>77.319999999999993</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>240</v>
+        <v>316</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>9</v>
@@ -3778,14 +3610,14 @@
         <v>1</v>
       </c>
       <c r="F42" s="5">
-        <v>44.15</v>
+        <v>12.99</v>
       </c>
       <c r="G42" s="6">
-        <f t="shared" si="14"/>
-        <v>44.15</v>
+        <f t="shared" si="13"/>
+        <v>12.99</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>219</v>
@@ -3800,33 +3632,33 @@
         <v>22.81</v>
       </c>
       <c r="O42" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>22.81</v>
       </c>
     </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>234</v>
+        <v>318</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="20">
-        <f>G2*2</f>
-        <v>2</v>
+        <f>G2*1</f>
+        <v>1</v>
       </c>
       <c r="F43" s="5">
-        <v>12.99</v>
+        <v>13.95</v>
       </c>
       <c r="G43" s="6">
-        <f t="shared" si="7"/>
-        <v>25.98</v>
+        <f t="shared" si="13"/>
+        <v>13.95</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="K43" s="12" t="s">
         <v>220</v>
@@ -3845,20 +3677,32 @@
         <v>16.12</v>
       </c>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="62" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="68"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="69"/>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F44" s="5">
+        <v>44.15</v>
+      </c>
+      <c r="G44" s="6">
+        <f t="shared" si="13"/>
+        <v>44.15</v>
+      </c>
       <c r="J44" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>9</v>
@@ -3875,172 +3719,160 @@
       </c>
     </row>
     <row r="45" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F45" s="5">
+        <v>12.99</v>
+      </c>
+      <c r="G45" s="6">
+        <f t="shared" si="6"/>
+        <v>12.99</v>
+      </c>
+      <c r="J45" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="K45" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="L45" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M45" s="36">
+        <v>1</v>
+      </c>
+      <c r="N45" s="35">
+        <v>53</v>
+      </c>
+      <c r="O45" s="37">
+        <f>M45*N45</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="68"/>
+      <c r="J46" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="K46" s="67"/>
+      <c r="L46" s="67"/>
+      <c r="M46" s="67"/>
+      <c r="N46" s="67"/>
+      <c r="O46" s="68"/>
+    </row>
+    <row r="47" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C45" s="22" t="s">
+      <c r="C47" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D45" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="41">
+      <c r="D47" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="40">
         <f>G2*10</f>
         <v>10</v>
       </c>
-      <c r="F45" s="36">
+      <c r="F47" s="35">
         <v>0.88560000000000005</v>
       </c>
-      <c r="G45" s="42">
-        <f>E45*F45</f>
+      <c r="G47" s="41">
+        <f>E47*F47</f>
         <v>8.8559999999999999</v>
       </c>
-      <c r="J45" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="K45" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="L45" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M45" s="37">
-        <v>1</v>
-      </c>
-      <c r="N45" s="36">
-        <v>53</v>
-      </c>
-      <c r="O45" s="38">
-        <f>M45*N45</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="62" t="s">
+      <c r="J47" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M47" s="4">
+        <v>2</v>
+      </c>
+      <c r="N47" s="5">
+        <v>19.63</v>
+      </c>
+      <c r="O47" s="39">
+        <v>39.26</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="63"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="63"/>
-      <c r="G46" s="64"/>
-      <c r="J46" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="K46" s="68"/>
-      <c r="L46" s="68"/>
-      <c r="M46" s="68"/>
-      <c r="N46" s="68"/>
-      <c r="O46" s="69"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="60"/>
+      <c r="J48" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M48" s="4">
+        <v>2</v>
+      </c>
+      <c r="N48" s="5">
+        <v>28.81</v>
+      </c>
+      <c r="O48" s="6">
+        <v>57.62</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C49" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="39">
+      <c r="D49" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="38">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F49" s="5">
         <v>14.77</v>
       </c>
-      <c r="G47" s="40">
-        <f t="shared" ref="G47:G99" si="16">E47*F47</f>
+      <c r="G49" s="39">
+        <f t="shared" ref="G49:G101" si="15">E49*F49</f>
         <v>29.54</v>
       </c>
-      <c r="J47" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M47" s="4">
-        <v>2</v>
-      </c>
-      <c r="N47" s="5">
-        <v>19.63</v>
-      </c>
-      <c r="O47" s="40">
-        <v>39.26</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="20">
-        <f>G2*2</f>
-        <v>2</v>
-      </c>
-      <c r="F48" s="5">
-        <v>7.8</v>
-      </c>
-      <c r="G48" s="6">
-        <f t="shared" si="16"/>
-        <v>15.6</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="K48" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="L48" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M48" s="4">
-        <v>2</v>
-      </c>
-      <c r="N48" s="5">
-        <v>28.81</v>
-      </c>
-      <c r="O48" s="6">
-        <v>57.62</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="20">
-        <f>G2*2</f>
-        <v>2</v>
-      </c>
-      <c r="F49" s="5">
-        <v>13.05</v>
-      </c>
-      <c r="G49" s="6">
-        <f t="shared" si="16"/>
-        <v>26.1</v>
-      </c>
-      <c r="J49" s="65" t="s">
+      <c r="J49" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="K49" s="66"/>
-      <c r="L49" s="66"/>
-      <c r="M49" s="66"/>
-      <c r="N49" s="67"/>
+      <c r="K49" s="62"/>
+      <c r="L49" s="62"/>
+      <c r="M49" s="62"/>
+      <c r="N49" s="63"/>
       <c r="O49" s="14">
         <f>SUM(O40:O48)</f>
         <v>319.13</v>
@@ -4048,296 +3880,296 @@
     </row>
     <row r="50" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>129</v>
+        <v>47</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E50" s="20">
-        <f>G2*1</f>
-        <v>1</v>
+        <f>G2*2</f>
+        <v>2</v>
       </c>
       <c r="F50" s="5">
-        <v>9.01</v>
+        <v>7.8</v>
       </c>
       <c r="G50" s="6">
-        <f t="shared" si="16"/>
-        <v>9.01</v>
+        <f t="shared" si="15"/>
+        <v>15.6</v>
       </c>
     </row>
     <row r="51" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="20">
+        <f>G2*2</f>
+        <v>2</v>
+      </c>
+      <c r="F51" s="5">
+        <v>13.05</v>
+      </c>
+      <c r="G51" s="6">
+        <f t="shared" si="15"/>
+        <v>26.1</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="K51" s="55" t="s">
+        <v>287</v>
+      </c>
+      <c r="L51" s="56"/>
+      <c r="M51" s="56"/>
+      <c r="N51" s="56"/>
+      <c r="O51" s="57"/>
+    </row>
+    <row r="52" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F52" s="5">
+        <v>9.01</v>
+      </c>
+      <c r="G52" s="6">
+        <f t="shared" si="15"/>
+        <v>9.01</v>
+      </c>
+      <c r="J52" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="K52" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="L52" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="M52" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C53" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="20">
+      <c r="D53" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="20">
         <f>G2*4</f>
         <v>4</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F53" s="5">
         <v>3.81</v>
       </c>
-      <c r="G51" s="6">
-        <f t="shared" si="16"/>
+      <c r="G53" s="6">
+        <f t="shared" si="15"/>
         <v>15.24</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="K51" s="72" t="s">
-        <v>295</v>
-      </c>
-      <c r="L51" s="73"/>
-      <c r="M51" s="73"/>
-      <c r="N51" s="73"/>
-      <c r="O51" s="74"/>
-    </row>
-    <row r="52" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="2" t="s">
+      <c r="J53" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="K53" s="67"/>
+      <c r="L53" s="67"/>
+      <c r="M53" s="67"/>
+      <c r="N53" s="67"/>
+      <c r="O53" s="68"/>
+    </row>
+    <row r="54" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C54" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F52" s="5">
+      <c r="D54" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F54" s="5">
         <v>5.29</v>
       </c>
-      <c r="G52" s="6">
-        <f t="shared" si="16"/>
+      <c r="G54" s="6">
+        <f t="shared" si="15"/>
         <v>5.29</v>
       </c>
-      <c r="J52" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="K52" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L52" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="M52" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="45" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="2" t="s">
+      <c r="J54" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="K54" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="L54" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M54" s="34">
+        <v>1</v>
+      </c>
+      <c r="N54" s="35">
+        <v>721.96</v>
+      </c>
+      <c r="O54" s="41">
+        <f t="shared" ref="O54:O56" si="16">M54*N54</f>
+        <v>721.96</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C55" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="20">
+      <c r="D55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="20">
         <f>G2*10</f>
         <v>10</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F55" s="5">
         <v>4.18</v>
       </c>
-      <c r="G53" s="6">
-        <f t="shared" si="16"/>
+      <c r="G55" s="6">
+        <f t="shared" si="15"/>
         <v>41.8</v>
       </c>
-      <c r="J53" s="62" t="s">
-        <v>217</v>
-      </c>
-      <c r="K53" s="68"/>
-      <c r="L53" s="68"/>
-      <c r="M53" s="68"/>
-      <c r="N53" s="68"/>
-      <c r="O53" s="69"/>
-    </row>
-    <row r="54" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="2" t="s">
+      <c r="J55" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="K55" s="67"/>
+      <c r="L55" s="67"/>
+      <c r="M55" s="67"/>
+      <c r="N55" s="67"/>
+      <c r="O55" s="68"/>
+    </row>
+    <row r="56" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="20">
+      <c r="D56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="20">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F56" s="5">
         <v>30.67</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G56" s="6">
+        <f t="shared" si="15"/>
+        <v>61.34</v>
+      </c>
+      <c r="J56" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="K56" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="L56" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M56" s="34">
+        <v>1</v>
+      </c>
+      <c r="N56" s="35">
+        <v>367.84</v>
+      </c>
+      <c r="O56" s="41">
         <f t="shared" si="16"/>
-        <v>61.34</v>
-      </c>
-      <c r="J54" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="K54" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="L54" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M54" s="35">
-        <v>1</v>
-      </c>
-      <c r="N54" s="36">
-        <v>721.96</v>
-      </c>
-      <c r="O54" s="42">
-        <f t="shared" ref="O54:O56" si="17">M54*N54</f>
-        <v>721.96</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="2" t="s">
+        <v>367.84</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" s="20">
+      <c r="D57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="20">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F57" s="5">
         <v>9.5500000000000007</v>
       </c>
-      <c r="G55" s="6">
-        <f t="shared" ref="G55:G62" si="18">E55*F55</f>
+      <c r="G57" s="6">
+        <f t="shared" ref="G57:G64" si="17">E57*F57</f>
         <v>19.100000000000001</v>
       </c>
-      <c r="J55" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="K55" s="68"/>
-      <c r="L55" s="68"/>
-      <c r="M55" s="68"/>
-      <c r="N55" s="68"/>
-      <c r="O55" s="69"/>
-    </row>
-    <row r="56" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="2" t="s">
+      <c r="J57" s="58" t="s">
+        <v>238</v>
+      </c>
+      <c r="K57" s="67"/>
+      <c r="L57" s="67"/>
+      <c r="M57" s="67"/>
+      <c r="N57" s="67"/>
+      <c r="O57" s="68"/>
+    </row>
+    <row r="58" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C58" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F56" s="5">
+      <c r="D58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F58" s="5">
         <v>16.87</v>
       </c>
-      <c r="G56" s="6">
-        <f t="shared" si="18"/>
+      <c r="G58" s="6">
+        <f t="shared" si="17"/>
         <v>16.87</v>
       </c>
-      <c r="J56" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="K56" s="43" t="s">
-        <v>227</v>
-      </c>
-      <c r="L56" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M56" s="35">
-        <v>1</v>
-      </c>
-      <c r="N56" s="36">
-        <v>367.84</v>
-      </c>
-      <c r="O56" s="42">
-        <f t="shared" si="17"/>
-        <v>367.84</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F57" s="5">
-        <v>8.33</v>
-      </c>
-      <c r="G57" s="6">
-        <f t="shared" si="18"/>
-        <v>8.33</v>
-      </c>
-      <c r="J57" s="62" t="s">
-        <v>242</v>
-      </c>
-      <c r="K57" s="68"/>
-      <c r="L57" s="68"/>
-      <c r="M57" s="68"/>
-      <c r="N57" s="68"/>
-      <c r="O57" s="69"/>
-    </row>
-    <row r="58" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F58" s="5">
-        <v>20.87</v>
-      </c>
-      <c r="G58" s="6">
-        <f t="shared" si="18"/>
-        <v>20.87</v>
-      </c>
       <c r="J58" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K58" s="12" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="L58" s="4" t="s">
         <v>9</v>
@@ -4348,143 +4180,144 @@
       <c r="N58" s="5">
         <v>239.99</v>
       </c>
-      <c r="O58" s="40">
-        <f t="shared" ref="O58" si="19">M58*N58</f>
+      <c r="O58" s="39">
+        <f t="shared" ref="O58" si="18">M58*N58</f>
         <v>239.99</v>
       </c>
     </row>
     <row r="59" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F59" s="5">
+        <v>8.33</v>
+      </c>
+      <c r="G59" s="6">
+        <f t="shared" si="17"/>
+        <v>8.33</v>
+      </c>
+      <c r="J59" s="61" t="s">
+        <v>188</v>
+      </c>
+      <c r="K59" s="62"/>
+      <c r="L59" s="62"/>
+      <c r="M59" s="62"/>
+      <c r="N59" s="63"/>
+      <c r="O59" s="14">
+        <f>SUM(O54,O58)</f>
+        <v>961.95</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F60" s="5">
+        <v>20.87</v>
+      </c>
+      <c r="G60" s="6">
+        <f t="shared" si="17"/>
+        <v>20.87</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C61" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" s="20">
+      <c r="D61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="20">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F61" s="5">
         <v>11.38</v>
       </c>
-      <c r="G59" s="6">
-        <f t="shared" si="18"/>
+      <c r="G61" s="6">
+        <f t="shared" si="17"/>
         <v>22.76</v>
       </c>
-      <c r="J59" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="K59" s="66"/>
-      <c r="L59" s="66"/>
-      <c r="M59" s="66"/>
-      <c r="N59" s="67"/>
-      <c r="O59" s="14" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="16" t="s">
+      <c r="J61" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="K61" s="55" t="s">
+        <v>296</v>
+      </c>
+      <c r="L61" s="56"/>
+      <c r="M61" s="56"/>
+      <c r="N61" s="56"/>
+      <c r="O61" s="57"/>
+    </row>
+    <row r="62" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C62" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F60" s="5">
+      <c r="D62" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F62" s="5">
         <v>10.71</v>
       </c>
-      <c r="G60" s="6">
-        <f t="shared" si="18"/>
+      <c r="G62" s="6">
+        <f t="shared" si="17"/>
         <v>10.71</v>
       </c>
-    </row>
-    <row r="61" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F61" s="5">
-        <v>12.36</v>
-      </c>
-      <c r="G61" s="6">
-        <f t="shared" si="18"/>
-        <v>12.36</v>
-      </c>
-      <c r="J61" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="K61" s="72" t="s">
-        <v>304</v>
-      </c>
-      <c r="L61" s="73"/>
-      <c r="M61" s="73"/>
-      <c r="N61" s="73"/>
-      <c r="O61" s="74"/>
-    </row>
-    <row r="62" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F62" s="5">
-        <v>7.78</v>
-      </c>
-      <c r="G62" s="6">
-        <f t="shared" si="18"/>
-        <v>7.78</v>
-      </c>
-      <c r="J62" s="48" t="s">
+      <c r="J62" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="K62" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="L62" s="49" t="s">
+      <c r="K62" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="L62" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="M62" s="49" t="s">
+      <c r="M62" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="49" t="s">
+      <c r="N62" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="50" t="s">
+      <c r="O62" s="49" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="63" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>9</v>
@@ -4494,277 +4327,277 @@
         <v>1</v>
       </c>
       <c r="F63" s="5">
-        <v>12.92</v>
+        <v>12.36</v>
       </c>
       <c r="G63" s="6">
-        <f t="shared" ref="G63:G68" si="20">E63*F63</f>
-        <v>12.92</v>
-      </c>
-      <c r="J63" s="62" t="s">
-        <v>263</v>
-      </c>
-      <c r="K63" s="70"/>
-      <c r="L63" s="70"/>
-      <c r="M63" s="70"/>
-      <c r="N63" s="70"/>
-      <c r="O63" s="71"/>
+        <f t="shared" si="17"/>
+        <v>12.36</v>
+      </c>
+      <c r="J63" s="58" t="s">
+        <v>256</v>
+      </c>
+      <c r="K63" s="75"/>
+      <c r="L63" s="75"/>
+      <c r="M63" s="75"/>
+      <c r="N63" s="75"/>
+      <c r="O63" s="76"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C64" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F64" s="5">
+        <v>7.78</v>
+      </c>
+      <c r="G64" s="6">
+        <f t="shared" si="17"/>
+        <v>7.78</v>
+      </c>
+      <c r="J64" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="K64" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M64" s="4">
+        <v>1</v>
+      </c>
+      <c r="N64" s="5">
+        <v>135</v>
+      </c>
+      <c r="O64" s="50">
+        <f t="shared" ref="O64:O65" si="19">M64*N64</f>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F65" s="5">
+        <v>12.92</v>
+      </c>
+      <c r="G65" s="6">
+        <f t="shared" ref="G65:G70" si="20">E65*F65</f>
+        <v>12.92</v>
+      </c>
+      <c r="J65" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="K65" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M65" s="4">
+        <v>1</v>
+      </c>
+      <c r="N65" s="5">
+        <v>280</v>
+      </c>
+      <c r="O65" s="26">
+        <f t="shared" si="19"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C66" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F64" s="5">
+      <c r="D66" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F66" s="5">
         <v>8</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G66" s="6">
         <f t="shared" si="20"/>
         <v>8</v>
       </c>
-      <c r="J64" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="K64" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M64" s="4">
-        <v>1</v>
-      </c>
-      <c r="N64" s="5">
-        <v>135</v>
-      </c>
-      <c r="O64" s="51">
-        <f t="shared" ref="O64:O65" si="21">M64*N64</f>
-        <v>135</v>
-      </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B65" s="2" t="s">
+      <c r="J66" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="K66" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="L66" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M66" s="29">
+        <v>1</v>
+      </c>
+      <c r="N66" s="30">
+        <v>102</v>
+      </c>
+      <c r="O66" s="31">
+        <f>M66*N66</f>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C67" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F65" s="5">
+      <c r="D67" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F67" s="5">
         <v>13.4</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G67" s="6">
         <f t="shared" si="20"/>
         <v>13.4</v>
       </c>
-      <c r="J65" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="K65" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M65" s="4">
-        <v>1</v>
-      </c>
-      <c r="N65" s="5">
-        <v>280</v>
-      </c>
-      <c r="O65" s="27">
-        <f t="shared" si="21"/>
-        <v>280</v>
-      </c>
-    </row>
-    <row r="66" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="2" t="s">
+      <c r="J67" s="61" t="s">
+        <v>188</v>
+      </c>
+      <c r="K67" s="62"/>
+      <c r="L67" s="62"/>
+      <c r="M67" s="62"/>
+      <c r="N67" s="63"/>
+      <c r="O67" s="32">
+        <f>SUM(O64:O66)</f>
+        <v>517</v>
+      </c>
+    </row>
+    <row r="68" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C68" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F66" s="5">
+      <c r="D68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F68" s="5">
         <v>3.11</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G68" s="6">
         <f t="shared" si="20"/>
         <v>3.11</v>
       </c>
-      <c r="J66" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="K66" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="L66" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M66" s="30">
-        <v>1</v>
-      </c>
-      <c r="N66" s="31">
-        <v>102</v>
-      </c>
-      <c r="O66" s="32">
-        <f>M66*N66</f>
-        <v>102</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="2" t="s">
+    </row>
+    <row r="69" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C69" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D67" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F67" s="5">
+      <c r="D69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F69" s="5">
         <v>3.56</v>
       </c>
-      <c r="G67" s="6">
-        <f t="shared" ref="G67" si="22">E67*F67</f>
+      <c r="G69" s="6">
+        <f t="shared" ref="G69" si="21">E69*F69</f>
         <v>3.56</v>
       </c>
-      <c r="J67" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="K67" s="66"/>
-      <c r="L67" s="66"/>
-      <c r="M67" s="66"/>
-      <c r="N67" s="67"/>
-      <c r="O67" s="33">
-        <f>SUM(O64:O66)</f>
-        <v>517</v>
-      </c>
-    </row>
-    <row r="68" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="2" t="s">
+      <c r="J69" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="K69" s="55" t="s">
+        <v>286</v>
+      </c>
+      <c r="L69" s="56"/>
+      <c r="M69" s="56"/>
+      <c r="N69" s="56"/>
+      <c r="O69" s="57"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C68" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F68" s="5">
+      <c r="C70" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F70" s="5">
         <v>6.69</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G70" s="6">
         <f t="shared" si="20"/>
         <v>6.69</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F69" s="5">
-        <v>27.76</v>
-      </c>
-      <c r="G69" s="6">
-        <f t="shared" si="16"/>
-        <v>27.76</v>
-      </c>
-      <c r="J69" s="34" t="s">
-        <v>296</v>
-      </c>
-      <c r="K69" s="72" t="s">
-        <v>294</v>
-      </c>
-      <c r="L69" s="73"/>
-      <c r="M69" s="73"/>
-      <c r="N69" s="73"/>
-      <c r="O69" s="74"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B70" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F70" s="5">
-        <v>15.31</v>
-      </c>
-      <c r="G70" s="6">
-        <f t="shared" si="16"/>
-        <v>15.31</v>
-      </c>
-      <c r="J70" s="48" t="s">
+      <c r="J70" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="K70" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="L70" s="49" t="s">
+      <c r="K70" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="L70" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="M70" s="49" t="s">
+      <c r="M70" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="N70" s="49" t="s">
+      <c r="N70" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="O70" s="50" t="s">
+      <c r="O70" s="49" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>9</v>
@@ -4774,27 +4607,27 @@
         <v>1</v>
       </c>
       <c r="F71" s="5">
-        <v>20</v>
+        <v>27.76</v>
       </c>
       <c r="G71" s="6">
-        <f t="shared" si="16"/>
-        <v>20</v>
-      </c>
-      <c r="J71" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="K71" s="76"/>
-      <c r="L71" s="76"/>
-      <c r="M71" s="76"/>
-      <c r="N71" s="76"/>
-      <c r="O71" s="77"/>
+        <f t="shared" si="15"/>
+        <v>27.76</v>
+      </c>
+      <c r="J71" s="69" t="s">
+        <v>285</v>
+      </c>
+      <c r="K71" s="70"/>
+      <c r="L71" s="70"/>
+      <c r="M71" s="70"/>
+      <c r="N71" s="70"/>
+      <c r="O71" s="71"/>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>9</v>
@@ -4804,17 +4637,17 @@
         <v>1</v>
       </c>
       <c r="F72" s="5">
-        <v>3.9</v>
+        <v>15.31</v>
       </c>
       <c r="G72" s="6">
-        <f t="shared" si="16"/>
-        <v>3.9</v>
+        <f t="shared" si="15"/>
+        <v>15.31</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="K72" s="12" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="L72" s="4" t="s">
         <v>9</v>
@@ -4826,251 +4659,251 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="O72" s="6">
-        <f t="shared" ref="O72:O76" si="23">M72*N72</f>
+        <f t="shared" ref="O72:O76" si="22">M72*N72</f>
         <v>34.799999999999997</v>
       </c>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F73" s="5">
+        <v>20</v>
+      </c>
+      <c r="G73" s="6">
+        <f t="shared" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K73" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M73" s="4">
+        <v>15</v>
+      </c>
+      <c r="N73" s="5">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="O73" s="6">
+        <f t="shared" si="22"/>
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F74" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="G74" s="6">
+        <f t="shared" si="15"/>
+        <v>3.9</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K74" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="L74" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M74" s="4">
+        <v>24</v>
+      </c>
+      <c r="N74" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="O74" s="6">
+        <f t="shared" si="22"/>
+        <v>42.96</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B75" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C75" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="20">
+      <c r="D75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="20">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F73" s="5">
+      <c r="F75" s="5">
         <v>2.34</v>
       </c>
-      <c r="G73" s="6">
-        <f t="shared" si="16"/>
+      <c r="G75" s="6">
+        <f t="shared" si="15"/>
         <v>4.68</v>
       </c>
-      <c r="J73" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="K73" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="L73" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M73" s="4">
+      <c r="J75" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="K75" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M75" s="4">
         <v>15</v>
       </c>
-      <c r="N73" s="5">
+      <c r="N75" s="5">
         <v>2.3199999999999998</v>
       </c>
-      <c r="O73" s="6">
-        <f t="shared" si="23"/>
+      <c r="O75" s="6">
+        <f t="shared" si="22"/>
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="74" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="2" t="s">
+    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B76" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C76" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="20">
+      <c r="D76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="20">
         <f>G2*3</f>
         <v>3</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F76" s="5">
         <v>2.34</v>
       </c>
-      <c r="G74" s="6">
-        <f t="shared" ref="G74:G80" si="24">E74*F74</f>
+      <c r="G76" s="6">
+        <f t="shared" ref="G76:G82" si="23">E76*F76</f>
         <v>7.02</v>
       </c>
-      <c r="J74" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="K74" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="L74" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M74" s="4">
+      <c r="J76" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="K76" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M76" s="4">
         <v>24</v>
       </c>
-      <c r="N74" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="O74" s="6">
-        <f t="shared" si="23"/>
-        <v>42.96</v>
-      </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B75" s="2" t="s">
+      <c r="N76" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="O76" s="6">
+        <f t="shared" si="22"/>
+        <v>26.64</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B77" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C77" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" s="20">
+      <c r="D77" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="20">
         <f>G2*3</f>
         <v>3</v>
       </c>
-      <c r="F75" s="5">
+      <c r="F77" s="5">
         <v>2.34</v>
       </c>
-      <c r="G75" s="6">
-        <f t="shared" si="24"/>
+      <c r="G77" s="6">
+        <f t="shared" si="23"/>
         <v>7.02</v>
       </c>
-      <c r="J75" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="K75" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="L75" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M75" s="4">
-        <v>15</v>
-      </c>
-      <c r="N75" s="5">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="O75" s="6">
-        <f t="shared" si="23"/>
-        <v>34.799999999999997</v>
-      </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B76" s="2" t="s">
+      <c r="J77" s="69" t="s">
+        <v>293</v>
+      </c>
+      <c r="K77" s="70"/>
+      <c r="L77" s="70"/>
+      <c r="M77" s="70"/>
+      <c r="N77" s="70"/>
+      <c r="O77" s="71"/>
+    </row>
+    <row r="78" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C78" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" s="20">
+      <c r="D78" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="20">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F78" s="5">
         <v>2.34</v>
       </c>
-      <c r="G76" s="6">
-        <f t="shared" si="24"/>
+      <c r="G78" s="6">
+        <f t="shared" si="23"/>
         <v>4.68</v>
       </c>
-      <c r="J76" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="K76" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M76" s="4">
-        <v>24</v>
-      </c>
-      <c r="N76" s="5">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="O76" s="6">
-        <f t="shared" si="23"/>
-        <v>26.64</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B77" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F77" s="5">
-        <v>23.68</v>
-      </c>
-      <c r="G77" s="6">
-        <f t="shared" si="24"/>
-        <v>23.68</v>
-      </c>
-      <c r="J77" s="75" t="s">
-        <v>301</v>
-      </c>
-      <c r="K77" s="76"/>
-      <c r="L77" s="76"/>
-      <c r="M77" s="76"/>
-      <c r="N77" s="76"/>
-      <c r="O77" s="77"/>
-    </row>
-    <row r="78" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F78" s="5">
-        <v>15.54</v>
-      </c>
-      <c r="G78" s="6">
-        <f t="shared" si="24"/>
-        <v>15.54</v>
-      </c>
       <c r="J78" s="16" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="L78" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M78" s="35">
+        <v>289</v>
+      </c>
+      <c r="L78" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M78" s="34">
         <v>15</v>
       </c>
-      <c r="N78" s="36">
+      <c r="N78" s="35">
         <v>2.5</v>
       </c>
-      <c r="O78" s="42">
+      <c r="O78" s="41">
         <f>M78*N78</f>
         <v>37.5</v>
       </c>
     </row>
     <row r="79" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>9</v>
@@ -5080,38 +4913,38 @@
         <v>1</v>
       </c>
       <c r="F79" s="5">
-        <v>4.79</v>
+        <v>23.68</v>
       </c>
       <c r="G79" s="6">
-        <f t="shared" si="24"/>
-        <v>4.79</v>
+        <f t="shared" si="23"/>
+        <v>23.68</v>
       </c>
       <c r="J79" s="16" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="L79" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M79" s="35">
+        <v>291</v>
+      </c>
+      <c r="L79" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M79" s="34">
         <v>8</v>
       </c>
-      <c r="N79" s="36">
+      <c r="N79" s="35">
         <v>14</v>
       </c>
-      <c r="O79" s="42">
+      <c r="O79" s="41">
         <f>M79*N79</f>
         <v>112</v>
       </c>
     </row>
     <row r="80" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>9</v>
@@ -5121,38 +4954,38 @@
         <v>1</v>
       </c>
       <c r="F80" s="5">
+        <v>15.54</v>
+      </c>
+      <c r="G80" s="6">
+        <f t="shared" si="23"/>
+        <v>15.54</v>
+      </c>
+      <c r="J80" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="L80" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M80" s="34">
         <v>8</v>
       </c>
-      <c r="G80" s="6">
-        <f t="shared" si="24"/>
-        <v>8</v>
-      </c>
-      <c r="J80" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="K80" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="L80" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M80" s="35">
-        <v>8</v>
-      </c>
-      <c r="N80" s="36">
+      <c r="N80" s="35">
         <v>11</v>
       </c>
-      <c r="O80" s="42">
+      <c r="O80" s="41">
         <f>M80*N80</f>
         <v>88</v>
       </c>
     </row>
     <row r="81" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="2" t="s">
-        <v>88</v>
+        <v>212</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>89</v>
+        <v>213</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>9</v>
@@ -5162,30 +4995,30 @@
         <v>1</v>
       </c>
       <c r="F81" s="5">
-        <v>3.64</v>
+        <v>4.79</v>
       </c>
       <c r="G81" s="6">
-        <f t="shared" si="16"/>
-        <v>3.64</v>
-      </c>
-      <c r="J81" s="65" t="s">
+        <f t="shared" si="23"/>
+        <v>4.79</v>
+      </c>
+      <c r="J81" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="K81" s="66"/>
-      <c r="L81" s="66"/>
-      <c r="M81" s="66"/>
-      <c r="N81" s="66"/>
-      <c r="O81" s="55">
+      <c r="K81" s="62"/>
+      <c r="L81" s="62"/>
+      <c r="M81" s="62"/>
+      <c r="N81" s="62"/>
+      <c r="O81" s="54">
         <f>SUM(O72:O80)</f>
         <v>411.5</v>
       </c>
     </row>
     <row r="82" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B82" s="2" t="s">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>91</v>
+        <v>211</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>9</v>
@@ -5195,19 +5028,19 @@
         <v>1</v>
       </c>
       <c r="F82" s="5">
-        <v>3.64</v>
+        <v>8</v>
       </c>
       <c r="G82" s="6">
-        <f t="shared" si="16"/>
-        <v>3.64</v>
+        <f t="shared" si="23"/>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B83" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>9</v>
@@ -5220,16 +5053,16 @@
         <v>3.64</v>
       </c>
       <c r="G83" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>3.64</v>
       </c>
     </row>
     <row r="84" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B84" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>9</v>
@@ -5242,16 +5075,16 @@
         <v>3.64</v>
       </c>
       <c r="G84" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>3.64</v>
       </c>
     </row>
     <row r="85" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B85" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>278</v>
+        <v>93</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>9</v>
@@ -5261,19 +5094,19 @@
         <v>1</v>
       </c>
       <c r="F85" s="5">
-        <v>15.26</v>
+        <v>3.64</v>
       </c>
       <c r="G85" s="6">
-        <f t="shared" si="16"/>
-        <v>15.26</v>
+        <f t="shared" si="15"/>
+        <v>3.64</v>
       </c>
     </row>
     <row r="86" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B86" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>9</v>
@@ -5283,19 +5116,19 @@
         <v>1</v>
       </c>
       <c r="F86" s="5">
-        <v>8.16</v>
+        <v>3.64</v>
       </c>
       <c r="G86" s="6">
-        <f t="shared" si="16"/>
-        <v>8.16</v>
+        <f t="shared" si="15"/>
+        <v>3.64</v>
       </c>
     </row>
     <row r="87" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B87" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>100</v>
+        <v>271</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>9</v>
@@ -5305,19 +5138,19 @@
         <v>1</v>
       </c>
       <c r="F87" s="5">
-        <v>8.16</v>
+        <v>15.26</v>
       </c>
       <c r="G87" s="6">
-        <f t="shared" si="16"/>
-        <v>8.16</v>
+        <f t="shared" si="15"/>
+        <v>15.26</v>
       </c>
     </row>
     <row r="88" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B88" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>9</v>
@@ -5330,267 +5163,325 @@
         <v>8.16</v>
       </c>
       <c r="G88" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>8.16</v>
       </c>
     </row>
-    <row r="89" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="16" t="s">
+    <row r="89" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B89" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F89" s="5">
+        <v>8.16</v>
+      </c>
+      <c r="G89" s="6">
+        <f t="shared" si="15"/>
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="90" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B90" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F90" s="5">
+        <v>8.16</v>
+      </c>
+      <c r="G90" s="6">
+        <f t="shared" si="15"/>
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="91" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C89" s="22" t="s">
+      <c r="C91" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D89" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" s="37">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F89" s="36">
+      <c r="D91" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="36">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F91" s="35">
         <v>85.17</v>
       </c>
-      <c r="G89" s="38">
-        <f>E89*F89</f>
+      <c r="G91" s="37">
+        <f>E91*F91</f>
         <v>85.17</v>
       </c>
     </row>
-    <row r="90" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="62" t="s">
-        <v>271</v>
-      </c>
-      <c r="C90" s="63"/>
-      <c r="D90" s="63"/>
-      <c r="E90" s="63"/>
-      <c r="F90" s="63"/>
-      <c r="G90" s="64"/>
-    </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B91" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="C91" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="D91" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" s="37">
+    <row r="92" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="58" t="s">
+        <v>264</v>
+      </c>
+      <c r="C92" s="59"/>
+      <c r="D92" s="59"/>
+      <c r="E92" s="59"/>
+      <c r="F92" s="59"/>
+      <c r="G92" s="60"/>
+    </row>
+    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B93" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="C93" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D93" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="36">
         <f>G2*8</f>
         <v>8</v>
       </c>
-      <c r="F91" s="36">
+      <c r="F93" s="35">
         <v>9.07</v>
       </c>
-      <c r="G91" s="38">
-        <f>E91*F91</f>
+      <c r="G93" s="37">
+        <f>E93*F93</f>
         <v>72.56</v>
       </c>
     </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B92" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C92" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="D92" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="37">
+    <row r="94" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B94" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C94" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D94" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="36">
         <f>G2*4</f>
         <v>4</v>
       </c>
-      <c r="F92" s="36">
+      <c r="F94" s="35">
         <v>9.49</v>
       </c>
-      <c r="G92" s="38">
-        <f>E92*F92</f>
+      <c r="G94" s="37">
+        <f>E94*F94</f>
         <v>37.96</v>
       </c>
     </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B93" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="C93" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="D93" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="37">
+    <row r="95" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B95" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="C95" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D95" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="36">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F93" s="36">
+      <c r="F95" s="35">
         <v>9.0399999999999991</v>
       </c>
-      <c r="G93" s="38">
-        <f>E93*F93</f>
+      <c r="G95" s="37">
+        <f>E95*F95</f>
         <v>18.079999999999998</v>
       </c>
     </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B94" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="C94" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="D94" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E94" s="37">
+    <row r="96" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B96" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D96" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="36">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F94" s="36">
+      <c r="F96" s="35">
         <v>8.6300000000000008</v>
       </c>
-      <c r="G94" s="38">
-        <f>E94*F94</f>
+      <c r="G96" s="37">
+        <f>E96*F96</f>
         <v>17.260000000000002</v>
       </c>
     </row>
-    <row r="95" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="C95" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="D95" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="37">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F95" s="36">
+    <row r="97" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B97" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="D97" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="36">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F97" s="35">
         <v>28.24</v>
       </c>
-      <c r="G95" s="38">
-        <f>E95*F95</f>
+      <c r="G97" s="37">
+        <f>E97*F97</f>
         <v>28.24</v>
       </c>
     </row>
-    <row r="96" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="62" t="s">
-        <v>317</v>
-      </c>
-      <c r="C96" s="63"/>
-      <c r="D96" s="63"/>
-      <c r="E96" s="63"/>
-      <c r="F96" s="63"/>
-      <c r="G96" s="64"/>
-    </row>
-    <row r="97" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B97" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E97" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F97" s="5">
-        <v>20.9</v>
-      </c>
-      <c r="G97" s="6">
-        <f>E97*F97</f>
-        <v>20.9</v>
-      </c>
-    </row>
     <row r="98" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="62" t="s">
-        <v>247</v>
-      </c>
-      <c r="C98" s="63"/>
-      <c r="D98" s="63"/>
-      <c r="E98" s="63"/>
-      <c r="F98" s="63"/>
-      <c r="G98" s="64"/>
+      <c r="B98" s="58" t="s">
+        <v>308</v>
+      </c>
+      <c r="C98" s="59"/>
+      <c r="D98" s="59"/>
+      <c r="E98" s="59"/>
+      <c r="F98" s="59"/>
+      <c r="G98" s="60"/>
     </row>
     <row r="99" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>232</v>
+        <v>248</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>307</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F99" s="5">
+        <v>20.9</v>
+      </c>
+      <c r="G99" s="6">
+        <f>E99*F99</f>
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="C100" s="59"/>
+      <c r="D100" s="59"/>
+      <c r="E100" s="59"/>
+      <c r="F100" s="59"/>
+      <c r="G100" s="60"/>
+    </row>
+    <row r="101" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B101" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E99" s="46">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F99" s="5">
+      <c r="E101" s="45">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F101" s="5">
         <v>30.21</v>
       </c>
-      <c r="G99" s="40">
-        <f t="shared" si="16"/>
+      <c r="G101" s="39">
+        <f t="shared" si="15"/>
         <v>30.21</v>
       </c>
     </row>
-    <row r="100" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="56" t="s">
-        <v>287</v>
-      </c>
-      <c r="C100" s="57"/>
-      <c r="D100" s="57"/>
-      <c r="E100" s="57"/>
-      <c r="F100" s="58"/>
-      <c r="G100" s="21">
-        <f>SUM(G5:G99)</f>
-        <v>2376.7359999999994</v>
-      </c>
-    </row>
-    <row r="101" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="56" t="s">
-        <v>288</v>
-      </c>
-      <c r="C101" s="57"/>
-      <c r="D101" s="57"/>
-      <c r="E101" s="57"/>
-      <c r="F101" s="58"/>
-      <c r="G101" s="53">
-        <f>(SUM(G5:G99))/G2</f>
-        <v>2376.7359999999994</v>
-      </c>
-    </row>
     <row r="102" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="C102" s="57"/>
-      <c r="D102" s="57"/>
-      <c r="E102" s="57"/>
-      <c r="F102" s="58"/>
-      <c r="G102" s="54">
-        <f>G101+O67</f>
-        <v>2893.7359999999994</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G105" s="52"/>
+      <c r="B102" s="64" t="s">
+        <v>279</v>
+      </c>
+      <c r="C102" s="65"/>
+      <c r="D102" s="65"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="66"/>
+      <c r="G102" s="21">
+        <f>SUM(G5:G101)</f>
+        <v>2540.4259999999981</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B103" s="64" t="s">
+        <v>280</v>
+      </c>
+      <c r="C103" s="65"/>
+      <c r="D103" s="65"/>
+      <c r="E103" s="65"/>
+      <c r="F103" s="66"/>
+      <c r="G103" s="52">
+        <f>(SUM(G5:G101))/G2</f>
+        <v>2540.4259999999981</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="64" t="s">
+        <v>270</v>
+      </c>
+      <c r="C104" s="65"/>
+      <c r="D104" s="65"/>
+      <c r="E104" s="65"/>
+      <c r="F104" s="66"/>
+      <c r="G104" s="53">
+        <f>G103+O67</f>
+        <v>3057.4259999999981</v>
+      </c>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="I107" s="52"/>
+      <c r="G107" s="51"/>
+      <c r="I107" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J21:O21"/>
+    <mergeCell ref="J26:O26"/>
+    <mergeCell ref="J36:N36"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B100:G100"/>
+    <mergeCell ref="J40:O40"/>
+    <mergeCell ref="J46:O46"/>
+    <mergeCell ref="J63:O63"/>
+    <mergeCell ref="K61:O61"/>
     <mergeCell ref="K2:O2"/>
-    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="B92:G92"/>
     <mergeCell ref="J67:N67"/>
-    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B103:F103"/>
     <mergeCell ref="J49:N49"/>
     <mergeCell ref="J53:O53"/>
     <mergeCell ref="J55:O55"/>
@@ -5602,34 +5493,18 @@
     <mergeCell ref="K51:O51"/>
     <mergeCell ref="K38:O38"/>
     <mergeCell ref="J77:O77"/>
-    <mergeCell ref="B96:G96"/>
-    <mergeCell ref="B102:F102"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J21:O21"/>
-    <mergeCell ref="J26:O26"/>
-    <mergeCell ref="J36:N36"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B46:G46"/>
     <mergeCell ref="B98:G98"/>
-    <mergeCell ref="J40:O40"/>
-    <mergeCell ref="J46:O46"/>
-    <mergeCell ref="J63:O63"/>
-    <mergeCell ref="K61:O61"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{182E6AD4-2BF8-453D-8168-0C5471656634}"/>
     <hyperlink ref="C16" r:id="rId2" xr:uid="{C0F4C0B5-36EF-43C3-B339-AACD5F5C72D4}"/>
-    <hyperlink ref="C48" r:id="rId3" xr:uid="{4723D3D0-CD4D-4359-8424-14CD9D28018C}"/>
+    <hyperlink ref="C50" r:id="rId3" xr:uid="{4723D3D0-CD4D-4359-8424-14CD9D28018C}"/>
     <hyperlink ref="C13" r:id="rId4" xr:uid="{7199B3E1-AB52-4D30-8183-99799A857909}"/>
-    <hyperlink ref="C52" r:id="rId5" xr:uid="{EFD4686C-AD95-420F-B095-B339D96CC0D7}"/>
+    <hyperlink ref="C54" r:id="rId5" xr:uid="{EFD4686C-AD95-420F-B095-B339D96CC0D7}"/>
     <hyperlink ref="C24" r:id="rId6" xr:uid="{5BD6981B-839D-4A2C-87F6-A3A00277C1E1}"/>
     <hyperlink ref="C25" r:id="rId7" xr:uid="{83DDA003-7213-4872-9D45-C4AF554BCA16}"/>
     <hyperlink ref="C27" r:id="rId8" display="https://www.amazon.com/AccusizeTools-Precision-Screwless-Hardened-0235-0303/dp/B00UCHGLUO/ref=sr_1_4?crid=WNIAUY5BPIE9&amp;dib=eyJ2IjoiMSJ9.Alni0qKZidsPooyk9GGkscfUQZ9tprkI4ET4wZoa_sbmUZzmmHVhxG7QmPDJX0AgSAHOykns84uDryc6E7grIuMWH375GMdVZCsMAZ8LQWFZfsy0ap0IiyiakunP6-_Y_ZcDHD9KuT9yk_DQjq9f6gKLk67aPwlGKsH16OBIZkb21bcZCjyEa7uJSWibaAc10B_8EIUViXEP_aCH2N7ITGBqK5oE8fgWj9yQaBwlw3DGARF2vyT4HE9hjWenKAVNJo79vmFegHMaPvq3QdGLRmFHCoGTuR7VlvFRIoLSNQs.7Kq1hNBbhFLTD57n8wr2lu-XKNLhMjGU5tZpFHisrPo&amp;dib_tag=se&amp;keywords=tool+maker+vice&amp;qid=1730493392&amp;sprefix=tool+maker+vice%2Caps%2C116&amp;sr=8-4" xr:uid="{4D66E69B-DE62-4D72-8B93-7F2E10874F91}"/>
-    <hyperlink ref="C51" r:id="rId9" xr:uid="{195A8F65-5906-4CC2-8230-372547AF30BC}"/>
+    <hyperlink ref="C53" r:id="rId9" xr:uid="{195A8F65-5906-4CC2-8230-372547AF30BC}"/>
     <hyperlink ref="C12" r:id="rId10" xr:uid="{68F00171-2727-43C8-B806-6B84C0184221}"/>
     <hyperlink ref="C11" r:id="rId11" location="customerReviews" xr:uid="{1A30128C-4F39-476D-97A8-AD250362EF88}"/>
     <hyperlink ref="K6" r:id="rId12" display="https://www.amazon.com/Fidioto-Terminals-Connector-Insulated-Industrial/dp/B09XQN3J6N/ref=sr_1_4?crid=9H73LST8YIJ5&amp;dib=eyJ2IjoiMSJ9.4GqBP1GBFaFPA0ydu3pf4E3drhrQBaiW09s5HBTixU2FjpaI-lQCi05VuNttif5SPyO5YPMQmiMI-Ln0MgmDooCOP2eZFsGw34JeesE9saSZOv5prr2QOuSwWgN7ynmhHAEYIJ6rP0v3XZOHMXrilaL9CJsYk1y2eURr1MMMAhbgUoFnWKVdPCzgToUNb0MRAeHQXIr7ACGFcGoEVjd41Ivpp40V3XA73Tx9HJAH-hM0laKEit0D2ZIkjTH3O1SpLc4K0_0SeSSXBSoAnNmqBXvG80iOUVvPuEP2oq_QBik.b-Wv2CuNpmfovLWKkfygBpQaQ9DDjyppvviR9L2qfRw&amp;dib_tag=se&amp;keywords=ferrule+connectors&amp;qid=1712253462&amp;s=industrial&amp;sprefix=ferr%2Cindustrial%2C158&amp;sr=1-4" xr:uid="{505E1876-1438-44B0-8CE3-B5857B28634C}"/>
@@ -5639,46 +5514,46 @@
     <hyperlink ref="C21" r:id="rId16" xr:uid="{BA6B4435-5F59-4C51-B877-F6D2850A5686}"/>
     <hyperlink ref="C20" r:id="rId17" xr:uid="{A44AC21F-D9EC-4BA8-8CB3-CDF163864C7A}"/>
     <hyperlink ref="C26" r:id="rId18" xr:uid="{3ACBC04B-80B5-483C-B223-DCC06D04EB43}"/>
-    <hyperlink ref="C47" r:id="rId19" xr:uid="{AB2A0A29-8665-4F12-85CA-729F9AEF1954}"/>
-    <hyperlink ref="C53" r:id="rId20" xr:uid="{DF72ED0E-A6AE-405C-A831-47EAF4A0978E}"/>
+    <hyperlink ref="C49" r:id="rId19" xr:uid="{AB2A0A29-8665-4F12-85CA-729F9AEF1954}"/>
+    <hyperlink ref="C55" r:id="rId20" xr:uid="{DF72ED0E-A6AE-405C-A831-47EAF4A0978E}"/>
     <hyperlink ref="C29" r:id="rId21" xr:uid="{3D2201C7-6C8A-4773-B48C-DEC55AB9CE5D}"/>
     <hyperlink ref="C28" r:id="rId22" xr:uid="{A7E3198B-4B0E-463C-BC5D-907882FF4F1D}"/>
     <hyperlink ref="C31" r:id="rId23" display="https://www.amazon.com/TYUMEN-Hookup-Electrical-Strips-Extension/dp/B07SLBD1FY?crid=3DSOPLHQPDC41&amp;dib=eyJ2IjoiMSJ9.LbfmNeaOMKQc2NnauqoG3ikk9ANZN_ur4lUWCOCW1O50UvTYKXmiV3AA8Ril1fLOmFRcVVCi_eXXhqwFcZtIW8vmaESTdy6oz8DZxn_URYzZU9OQiHvftwQ3KnaAl6ba-cfRNhMbR7Fpx7tqwarEMqmVU0t2BYcH56emRvXvgV1aTOFyjOYBpkeQMF4SwuInBmgz7WD_t5spHjwSbDYPmshu2rmE36AdUCByV1ie631jZjWBFXP_gl822MkqR8EixD-piO5IZ22jBqlSbpf0TcMJdhRwDpP5zuWzH47ITPk.AI3vrrrkl4uXviMH51NrHs3QtR7dKc_HTTFAhHq9paA&amp;dib_tag=se&amp;keywords=22+awg+wire&amp;qid=1733387088&amp;s=industrial&amp;sprefix=22+awg%2Cindustrial%2C149&amp;sr=1-8" xr:uid="{E82B0C83-0745-457F-853F-CF7C98A9BBAF}"/>
     <hyperlink ref="K18" r:id="rId24" display="https://www.amazon.com/HUAREW-Values-Ferrite-Suppressor-Diameter/dp/B09SWNPY2Y?crid=25SF4JZN6UMCO&amp;dib=eyJ2IjoiMSJ9.BECN3Z-pnF_DHO20UYNRh-xF2WQPuabKc-oibkz7-5pf-LFqEqaxgUTsjAY9NMHye5H2wuD5X3xZHc2XF6v_ZmAzcFy34lVzkGSEseb_JQsXhQ_lHx78wyV8_2Bl5O2FXq_OPNVVnus4XAq2V7L8dtacsFGCRlHZwgnYlurEB2URoEWdU24JZSoJOdjnTKoB-Nm2-vu6eTFFOKyg0bYDhkvLpIooINxXg8mYy1zuu90.aHjsj2UYUYYX1n4w2EmKBChz9hsqz6bpyNaSrZmD_Pc&amp;dib_tag=se&amp;keywords=ferrite%2Bcore%2Bbead&amp;qid=1733391188&amp;sprefix=ferrite%2Bcore%2Bbead%2Caps%2C148&amp;sr=8-3&amp;th=1 " xr:uid="{3624AB78-BD37-43C7-ABBC-ABDD2D49F1BD}"/>
-    <hyperlink ref="C54" r:id="rId25" xr:uid="{32DB5FB3-622F-4B80-98A2-9D63982309B9}"/>
-    <hyperlink ref="C70" r:id="rId26" xr:uid="{E95793D2-E192-4066-88A4-5B88C4EB6441}"/>
-    <hyperlink ref="C69" r:id="rId27" xr:uid="{89E89EFA-A33B-49E7-9CA3-3AA3F3B2419C}"/>
-    <hyperlink ref="C81" r:id="rId28" xr:uid="{C0887221-10A6-49C9-9592-F29719AB1146}"/>
-    <hyperlink ref="C82" r:id="rId29" xr:uid="{5D432ACC-1036-40C7-BAF5-8E7A9DEE269C}"/>
-    <hyperlink ref="C83" r:id="rId30" xr:uid="{373A1D9B-E52A-4919-BF46-F0054AD0383E}"/>
-    <hyperlink ref="C84" r:id="rId31" xr:uid="{67F0F7A2-8F53-4145-AE23-1984596864D2}"/>
-    <hyperlink ref="C86" r:id="rId32" xr:uid="{0AE9CA58-FE72-4AAA-B4AE-ED28FC16E141}"/>
-    <hyperlink ref="C87" r:id="rId33" xr:uid="{649DFB24-658E-46D9-8DD3-8968123090EE}"/>
-    <hyperlink ref="C88" r:id="rId34" xr:uid="{41AC74BE-2B55-4941-9CA1-1FB8B496080B}"/>
-    <hyperlink ref="C89" r:id="rId35" xr:uid="{673DF358-F6E2-431B-8C25-0F1712C2A5BE}"/>
+    <hyperlink ref="C56" r:id="rId25" xr:uid="{32DB5FB3-622F-4B80-98A2-9D63982309B9}"/>
+    <hyperlink ref="C72" r:id="rId26" xr:uid="{E95793D2-E192-4066-88A4-5B88C4EB6441}"/>
+    <hyperlink ref="C71" r:id="rId27" xr:uid="{89E89EFA-A33B-49E7-9CA3-3AA3F3B2419C}"/>
+    <hyperlink ref="C83" r:id="rId28" xr:uid="{C0887221-10A6-49C9-9592-F29719AB1146}"/>
+    <hyperlink ref="C84" r:id="rId29" xr:uid="{5D432ACC-1036-40C7-BAF5-8E7A9DEE269C}"/>
+    <hyperlink ref="C85" r:id="rId30" xr:uid="{373A1D9B-E52A-4919-BF46-F0054AD0383E}"/>
+    <hyperlink ref="C86" r:id="rId31" xr:uid="{67F0F7A2-8F53-4145-AE23-1984596864D2}"/>
+    <hyperlink ref="C88" r:id="rId32" xr:uid="{0AE9CA58-FE72-4AAA-B4AE-ED28FC16E141}"/>
+    <hyperlink ref="C89" r:id="rId33" xr:uid="{649DFB24-658E-46D9-8DD3-8968123090EE}"/>
+    <hyperlink ref="C90" r:id="rId34" xr:uid="{41AC74BE-2B55-4941-9CA1-1FB8B496080B}"/>
+    <hyperlink ref="C91" r:id="rId35" xr:uid="{673DF358-F6E2-431B-8C25-0F1712C2A5BE}"/>
     <hyperlink ref="K35" r:id="rId36" xr:uid="{F7DD1C65-60DD-46DD-9FE7-6744F8BA03E7}"/>
-    <hyperlink ref="C57" r:id="rId37" xr:uid="{EF358443-AF57-40E1-92E1-8BF6DD299077}"/>
-    <hyperlink ref="C59" r:id="rId38" xr:uid="{12762096-DC6B-44F2-8ADB-0F58C1B3AEEF}"/>
-    <hyperlink ref="C58" r:id="rId39" xr:uid="{3EFF0D79-73FC-4F62-B070-424FEA2B0998}"/>
-    <hyperlink ref="C61" r:id="rId40" xr:uid="{4C882C61-8A3D-4FF6-8AA2-3CFEBE6A8E31}"/>
-    <hyperlink ref="C55" r:id="rId41" xr:uid="{8C08A008-7728-44D3-BA67-48DB3EEFA7BB}"/>
-    <hyperlink ref="C63" r:id="rId42" xr:uid="{1E69FF1B-0FFD-4B85-B8D4-6662499D5EC6}"/>
-    <hyperlink ref="C65" r:id="rId43" xr:uid="{7C60CB7E-E2C1-46DC-BD3E-B770093F52D5}"/>
-    <hyperlink ref="C66" r:id="rId44" xr:uid="{3FB0574C-FDA6-4DB0-863A-DD9D050D7C39}"/>
-    <hyperlink ref="C56" r:id="rId45" xr:uid="{CFDEAC1B-A32C-4050-8273-2439C47581BB}"/>
-    <hyperlink ref="C60" r:id="rId46" xr:uid="{9A55F38E-8B5A-4A95-8F81-373F25553D76}"/>
-    <hyperlink ref="C62" r:id="rId47" xr:uid="{78F0AA91-375E-4C85-9A3E-A171D50577BA}"/>
+    <hyperlink ref="C59" r:id="rId37" xr:uid="{EF358443-AF57-40E1-92E1-8BF6DD299077}"/>
+    <hyperlink ref="C61" r:id="rId38" xr:uid="{12762096-DC6B-44F2-8ADB-0F58C1B3AEEF}"/>
+    <hyperlink ref="C60" r:id="rId39" xr:uid="{3EFF0D79-73FC-4F62-B070-424FEA2B0998}"/>
+    <hyperlink ref="C63" r:id="rId40" xr:uid="{4C882C61-8A3D-4FF6-8AA2-3CFEBE6A8E31}"/>
+    <hyperlink ref="C57" r:id="rId41" xr:uid="{8C08A008-7728-44D3-BA67-48DB3EEFA7BB}"/>
+    <hyperlink ref="C65" r:id="rId42" xr:uid="{1E69FF1B-0FFD-4B85-B8D4-6662499D5EC6}"/>
+    <hyperlink ref="C67" r:id="rId43" xr:uid="{7C60CB7E-E2C1-46DC-BD3E-B770093F52D5}"/>
+    <hyperlink ref="C68" r:id="rId44" xr:uid="{3FB0574C-FDA6-4DB0-863A-DD9D050D7C39}"/>
+    <hyperlink ref="C58" r:id="rId45" xr:uid="{CFDEAC1B-A32C-4050-8273-2439C47581BB}"/>
+    <hyperlink ref="C62" r:id="rId46" xr:uid="{9A55F38E-8B5A-4A95-8F81-373F25553D76}"/>
+    <hyperlink ref="C64" r:id="rId47" xr:uid="{78F0AA91-375E-4C85-9A3E-A171D50577BA}"/>
     <hyperlink ref="C6" r:id="rId48" xr:uid="{AED92118-DDB2-4EF3-AC67-4C4C07E0C841}"/>
     <hyperlink ref="C9" r:id="rId49" xr:uid="{FE9C3C2A-AF4A-4E14-BBDB-335DF3BC0F13}"/>
     <hyperlink ref="C18" r:id="rId50" xr:uid="{94451722-66BC-4F98-8B43-3E0FC394E5EA}"/>
     <hyperlink ref="C23" r:id="rId51" xr:uid="{8B80B60C-F876-4871-8577-DC9ACEA588AC}"/>
     <hyperlink ref="C30" r:id="rId52" xr:uid="{0492A76A-498E-4001-829F-D792C40ACDBA}"/>
-    <hyperlink ref="C50" r:id="rId53" xr:uid="{D6C0DDCE-AD68-4B51-98DF-B171BC702B91}"/>
-    <hyperlink ref="C67" r:id="rId54" xr:uid="{68484166-BD87-4E39-9BD4-46B04DB0A082}"/>
+    <hyperlink ref="C52" r:id="rId53" xr:uid="{D6C0DDCE-AD68-4B51-98DF-B171BC702B91}"/>
+    <hyperlink ref="C69" r:id="rId54" xr:uid="{68484166-BD87-4E39-9BD4-46B04DB0A082}"/>
     <hyperlink ref="C38" r:id="rId55" display="https://www.amazon.com/Universal-Regulated-Switching-Converter-Transformer/dp/B07PPPF1R5/ref=sr_1_6?dib=eyJ2IjoiMSJ9.ghI_8NCu8MWYClVH1bcXae0-G1NHsVMPKXgQ-q9tD7DBjxsd-n2e4GXZyzhj32lWCmUMKNTvmGLgthtkozNnkvRJfBHn4VuSCeTc5lP748T7kJtgdQqg9MH80QXTBMNWupAT-RBnmpw_wBXBO26SKIbj1k64fqcpbisodWHH80xxJPdJFOijPa1IA51xm60Wi2aU2vCne6MmqM3RncHLRYr931SD1UNb9aMjXyOF6U4.dija8_tU-NIlFsudkA1tvV6C6mk8gUO-_lwM8li1rMY&amp;dib_tag=se&amp;keywords=5v%2Bpower%2Bsupply&amp;qid=1743186298&amp;sr=8-6&amp;th=1 " xr:uid="{88BB23CD-312A-41E1-B370-C0D92A466099}"/>
     <hyperlink ref="C32" r:id="rId56" display="https://www.amazon.com/HiLetgo-Channels-Converter-Bi-Directional-3-3V-5V/dp/B07F7W91LC/ref=sr_1_2?crid=2O7B6QA8ZSPZK&amp;dib=eyJ2IjoiMSJ9.hg1xpaR1IOVH3e6fV4tFyZB8elQluWDLIScr-WIbHEosPLIRhqXG5AnMJTwgM0K6TrBGR457D8AftNCas1RwwWglHyp8zMGTpS2Jwm4xa_uAl0aEMGjby7ffGvEP4lloYctRt9gX4TE3gjllm6sYLU-fsW7zpvcw5ZYESHBPOBCKcQrbrqb3arWPwpjMs7PwokFja-obLRKIr-SuthVfiG0yGem5Rc41xB6eDkr3AZehwq0tgYmv9VxxVa-jlxf9M9Jmhd8G9HvRemxc8IltnV6CNWKiDi1dgnDBhhj15Hs.b7q4qr8rSADKOOdi-2C89QYAixVQ_S86lTmLM2WBijs&amp;dib_tag=se&amp;keywords=logic+converter&amp;qid=1732221329&amp;s=industrial&amp;sprefix=logic+convertyer%2Cindustrial%2C103&amp;sr=1-2" xr:uid="{AA94D625-0126-47B8-979E-9BE236BAD9AD}"/>
     <hyperlink ref="K17" r:id="rId57" xr:uid="{0F474C1B-53F3-45D5-A2EC-5FEABEC629CC}"/>
-    <hyperlink ref="C45" r:id="rId58" display="https://www.digikey.com/en/products/detail/w-rth-elektronik/691210910002/10668428?gclsrc=aw.ds&amp;&amp;utm_adgroup=&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=PMax%20Supplier_Focus%20Supplier&amp;utm_term=&amp;utm_content=&amp;utm_id=go_cmp-20243063242_adg-_ad-__dev-c_ext-_prd-10668428_sig-CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gad_source=1&amp;gclid=CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gclsrc=aw.ds " xr:uid="{DCE5683A-0BC1-49BA-8FB0-36DC1C1C9A9C}"/>
+    <hyperlink ref="C47" r:id="rId58" display="https://www.digikey.com/en/products/detail/w-rth-elektronik/691210910002/10668428?gclsrc=aw.ds&amp;&amp;utm_adgroup=&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=PMax%20Supplier_Focus%20Supplier&amp;utm_term=&amp;utm_content=&amp;utm_id=go_cmp-20243063242_adg-_ad-__dev-c_ext-_prd-10668428_sig-CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gad_source=1&amp;gclid=CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gclsrc=aw.ds " xr:uid="{DCE5683A-0BC1-49BA-8FB0-36DC1C1C9A9C}"/>
     <hyperlink ref="C34" r:id="rId59" xr:uid="{A29FBA48-6899-42FA-AA59-0FC1E2A5A45B}"/>
     <hyperlink ref="K5" r:id="rId60" display="https://www.amazon.com/Klein-Tools-34056-Adjustable-Electrical/dp/B0D98N52HS/ref=sr_1_1?crid=2OB42YRNYW5S8&amp;dib=eyJ2IjoiMSJ9.55eyclIvGQBRs_G9kszoUlEHRgUtyYkcxabPk-sLw5mt7xuGNeudbfTW8xclKppzTejqidNByQBdPqeEXGg2aJrgDuRoxPddnr7un1KzGrHylGN5yiKL4ycDLAz23bHXFS35VarXoP5Hhq810Sdco6qhSeWGVplSUIYpl56zvRZNrenZvPGmvYU7Y6nsIMihDbf5RoNPi8sUcALPKWZoFyR-Fs3jx2RBJISOeui_PdRPNKnGLGC0Uz395rIEcZ1F9icIwzDBX00JzMC1ZjD_KvEf_nXltgLaawa8vee6Efs.PDGEHgTlQjY0Jz82g_64nVgHTsayEsuiw1VPN9n4cXc&amp;dib_tag=se&amp;keywords=klein%2Bferrule%2Bcrimper&amp;qid=1730823384&amp;sprefix=klein%2Bferrule%2Bcrimper%2Caps%2C132&amp;sr=8-1&amp;th=1 " xr:uid="{CEBE3ECF-00C1-476F-B5EA-6B34F3C440E0}"/>
     <hyperlink ref="K9" r:id="rId61" display="https://www.amazon.com/Ginsco-580-pcs-Assorted-Sleeving/dp/B01MFA3OFA/ref=sr_1_3?crid=19V7T4IBHC5QO&amp;dib=eyJ2IjoiMSJ9.afAtOFc0AWv7IewHnY-SsmFPIWDeFgvxv7nXELH8Q5qH5K9drWIEjyb4PZCDtpgcSjO1zJt_d_d3Bzwc58g899uhvXzTWNoWa7P0XxuvXztW-5Tc85nP2v3ZP7OVkL9CptCT1e2fAdSg9fifPtR8m9aUVniGOD_xVLXrYdiBq6lh_RbbHkqSMJ69bG3sHk4HbEXsrxggq5C19I64px1H3_Ik8TcJWmowUEtAS4Q9W-qfDLzF-ZeqrhVHbQsdU60_CMcyHcb-SzXuOkdEyVk4hxnhYPkE9DVIFlnwUZ_gnFs.KYnfl9oSznG3OdVCEMra_IGu5ndQOaOh0V01hKDX2Cg&amp;dib_tag=se&amp;keywords=heat+shrink&amp;qid=1730826521&amp;s=industrial&amp;sprefix=heat+shrink%2Cindustrial%2C153&amp;sr=1-3" xr:uid="{332F4161-5937-4DDE-ABA6-DACEB1F4794A}"/>
@@ -5702,14 +5577,14 @@
     <hyperlink ref="K28" r:id="rId79" xr:uid="{5F7730D8-6AC1-4AFC-BDF9-357875FD1123}"/>
     <hyperlink ref="K29" r:id="rId80" xr:uid="{7D645F8A-33CD-418D-8D23-F32705DFD52D}"/>
     <hyperlink ref="K32" r:id="rId81" xr:uid="{72352CC7-698C-4AF0-BCF4-715EF6461852}"/>
-    <hyperlink ref="C74" r:id="rId82" xr:uid="{D0BFB25A-21DF-4F2E-8B59-E3DD05C3B098}"/>
-    <hyperlink ref="C73" r:id="rId83" xr:uid="{D5A5F088-A84E-4368-83A3-93B6A7392B62}"/>
-    <hyperlink ref="C75" r:id="rId84" xr:uid="{03C53325-8F52-47AD-98AA-5B3BD79FCDF7}"/>
-    <hyperlink ref="C76" r:id="rId85" xr:uid="{BC613FBE-2FF7-47F4-BA8F-9A2B780CBF4D}"/>
-    <hyperlink ref="C77" r:id="rId86" xr:uid="{18524F55-8313-44A2-98E0-8D3476379625}"/>
-    <hyperlink ref="C78" r:id="rId87" xr:uid="{C5B457D0-EBF2-4473-8DE5-A2CBF0192FC7}"/>
-    <hyperlink ref="C80" r:id="rId88" xr:uid="{E9EBC0D2-18CA-4009-92BF-AA4627474036}"/>
-    <hyperlink ref="C79" r:id="rId89" xr:uid="{F9DC2B0F-6CC2-4333-B6A0-4C461C26A42D}"/>
+    <hyperlink ref="C76" r:id="rId82" xr:uid="{D0BFB25A-21DF-4F2E-8B59-E3DD05C3B098}"/>
+    <hyperlink ref="C75" r:id="rId83" xr:uid="{D5A5F088-A84E-4368-83A3-93B6A7392B62}"/>
+    <hyperlink ref="C77" r:id="rId84" xr:uid="{03C53325-8F52-47AD-98AA-5B3BD79FCDF7}"/>
+    <hyperlink ref="C78" r:id="rId85" xr:uid="{BC613FBE-2FF7-47F4-BA8F-9A2B780CBF4D}"/>
+    <hyperlink ref="C79" r:id="rId86" xr:uid="{18524F55-8313-44A2-98E0-8D3476379625}"/>
+    <hyperlink ref="C80" r:id="rId87" xr:uid="{C5B457D0-EBF2-4473-8DE5-A2CBF0192FC7}"/>
+    <hyperlink ref="C82" r:id="rId88" xr:uid="{E9EBC0D2-18CA-4009-92BF-AA4627474036}"/>
+    <hyperlink ref="C81" r:id="rId89" xr:uid="{F9DC2B0F-6CC2-4333-B6A0-4C461C26A42D}"/>
     <hyperlink ref="C35" r:id="rId90" xr:uid="{B350E38A-0704-49E3-B0A0-6AC64705FFA8}"/>
     <hyperlink ref="K24" r:id="rId91" xr:uid="{38DE31D1-83D2-44D7-B2DB-47B0912A74D8}"/>
     <hyperlink ref="K42" r:id="rId92" xr:uid="{99DE23E2-FB55-46E7-81C4-10D9C3F12704}"/>
@@ -5720,60 +5595,50 @@
     <hyperlink ref="K54" r:id="rId97" xr:uid="{08CDA0A7-76D0-4386-8DF9-D40020E4F6BB}"/>
     <hyperlink ref="K56" r:id="rId98" xr:uid="{B817C2C0-888A-41EE-BB96-AA202FF7D26F}"/>
     <hyperlink ref="K7" r:id="rId99" xr:uid="{403CBC77-BB8E-482D-ADB0-566010CFFBFE}"/>
-    <hyperlink ref="C39" r:id="rId100" display="https://www.amazon.com/Ethernet-Kit-for-Teensy-4-1/dp/B08CTM1L64/ref=sr_1_5?dib=eyJ2IjoiMSJ9.SbX6rnuR22BHW7UQV6IYcckSiyAyB1ZWr3cUVGCpjmoe8u9La0C4CnpYOniX7CwAfqWVpgmjNbJjLT76DhWe4ldG5P2p4WMYyJenE908txxUrz8DSqOHEjh3oVZE2stHV0rzuhfvuwF3CawGYaDmSg.85Xw8ylPJeTNJvqmoxZDt0Th8_d0wMGVyuH5z7GC-TU&amp;dib_tag=se&amp;qid=1752729706&amp;refinements=p_89%3APJRC&amp;sr=8-5&amp;srs=36931437011 " xr:uid="{E3DAB6D6-41C5-4F47-B4DE-A540D085825C}"/>
-    <hyperlink ref="C99" r:id="rId101" xr:uid="{66B61CB6-8DEE-47E0-8F58-13DFE696A594}"/>
-    <hyperlink ref="C19" r:id="rId102" xr:uid="{25851340-5A38-4A26-A3FC-843A61F946D3}"/>
-    <hyperlink ref="C43" r:id="rId103" xr:uid="{21E4C4A3-A6F2-4A9D-B5C5-679DA6006B33}"/>
-    <hyperlink ref="C41" r:id="rId104" xr:uid="{E912526C-B82A-4A44-8481-EFACD695EA8D}"/>
-    <hyperlink ref="C42" r:id="rId105" xr:uid="{E865141B-878A-4CD6-B122-3ADC6852D520}"/>
-    <hyperlink ref="K58" r:id="rId106" location="tabbed-customerreviews " xr:uid="{24F44932-6634-42FE-8337-20CA3C2EC1E4}"/>
-    <hyperlink ref="C72" r:id="rId107" xr:uid="{326567BB-9D82-4E92-ACC4-530A6BCCFC38}"/>
-    <hyperlink ref="C17" r:id="rId108" display="https://www.amazon.com/Amazon-Basics-Ethernet-High-Speed-Snagless/dp/B089MGH8W3/ref=sr_1_6?crid=15O99JJ9VZUDS&amp;dib=eyJ2IjoiMSJ9.Qrm0YFmTEww5DZc4mrTYoBW2ITYU8YDRmdb4HE4nmukqEngrlTfGgHLb5uoFzqyB8DY16yxmWqTI2jhY13tKSS_gVPXMFmLrV8CwN6seDqr3fe6RoYGbAYOThLs_GPXGD9BG1xBtpSbQCaOmPeX6onzLKT90VpHEp8g8rhIrccYIWeUVb1y9yQszCgP-aLtJNIsqNx1o-8aHQGBnXQxbEdINQFklL4UDCld4WzwhnXy0xN-YFaHdxcyM5kmfmoYQEhD8UEUeVcULGl7eYpTBQi8RxGrjeWwsXTnPG7oVA4s.SJ0prHAqUML_3kLplif-xyTccwFoBx4GiK1cGmdOyLI&amp;dib_tag=se&amp;keywords=ethernet%2Bcable&amp;qid=1752782277&amp;s=electronics&amp;sprefix=ethernet%2Celectronics%2C124&amp;sr=1-6&amp;th=1 " xr:uid="{83A0A177-ED38-4C3C-B1E2-6D1A2C00DD2C}"/>
-    <hyperlink ref="C10" r:id="rId109" xr:uid="{5EF2B5FA-9EB9-4ED3-A87B-DB000918746C}"/>
-    <hyperlink ref="K13" r:id="rId110" display="https://www.amazon.com/Powerbuilt-Piece-Stubby-Long-Wrench/dp/B07N8F7W7K/ref=sr_1_19?dib=eyJ2IjoiMSJ9.URwdEPQXxCMLBhxvS9K5ftG6hwdCaLy_xWZ0vGXOdbuaNrb8XAmO4DQhIxovkvuXsRHPo7oCqjy9Wwt6H6QvZeRYOqVzaLjKkETlnA83OkSSXLxlPpzMt1Qy3kJt-T7GsO_Bq0c0QItERYLb6VTtZmMQdlqDEtc5mdwZiAksW1Y2IKpS2cr-V_j1_L0qMFZKPy2WuoytvNj5MEhK80MOfMrjnaTsJLpB9Io2Jt4xFodm6EN5AwCetZhDdsJTY6jdeOdEdPi6COl5b1RI-6XJHwylh2H13M74HgAUrEaRfoY.bAaypnaW3mj6ulkwXEha2QJSRXBFsgrmQMhuIwb4S2o&amp;dib_tag=se&amp;keywords=stubby%2Ballen%2Bwrench%2Bset&amp;qid=1752911269&amp;sr=8-19&amp;th=1 " xr:uid="{F2200CD7-83CF-497A-91E0-EF5B6CA80C0C}"/>
-    <hyperlink ref="K44" r:id="rId111" xr:uid="{F40A70E6-7F31-454F-9558-A7291A2A2DCF}"/>
-    <hyperlink ref="K45" r:id="rId112" xr:uid="{4A6F6959-0930-44EE-A971-B3EF13DA9390}"/>
-    <hyperlink ref="C49" r:id="rId113" xr:uid="{7963F571-8F62-4D9F-BEF7-F802CD4D18FC}"/>
-    <hyperlink ref="C91" r:id="rId114" xr:uid="{5A200CB5-C655-478F-B00B-2E82D8CC5C77}"/>
-    <hyperlink ref="C92:C93" r:id="rId115" display="https://8020.net/20-2020.html " xr:uid="{94C82CF7-4209-49DE-A286-0E429370F935}"/>
-    <hyperlink ref="C94" r:id="rId116" xr:uid="{3653483D-B8D7-4970-8BE1-067F3CE7FF42}"/>
-    <hyperlink ref="C85" r:id="rId117" xr:uid="{E1AC3FAD-797D-4D40-89E1-E0B078028B08}"/>
-    <hyperlink ref="C64" r:id="rId118" xr:uid="{8B53B0C9-AEB9-4C25-B4D5-D709A9909BD6}"/>
-    <hyperlink ref="C68" r:id="rId119" xr:uid="{2521E3A3-9809-485D-8952-C732415A0425}"/>
-    <hyperlink ref="K41" r:id="rId120" xr:uid="{BE5F57C8-C44E-47CF-B992-FEB02C6C001F}"/>
-    <hyperlink ref="K72" r:id="rId121" xr:uid="{A8E5D7AD-E110-498C-AD66-4031E7159275}"/>
-    <hyperlink ref="K74" r:id="rId122" xr:uid="{686F1C5B-AD14-408B-9AF5-1B4D26D75248}"/>
-    <hyperlink ref="K78" r:id="rId123" xr:uid="{A8336809-C542-4E15-9187-DB4F43D26933}"/>
-    <hyperlink ref="K79" r:id="rId124" xr:uid="{49B9B422-CDDA-427C-82B9-729F2266C333}"/>
-    <hyperlink ref="K80" r:id="rId125" xr:uid="{3E0AC7C3-82FC-4B11-AD25-3DE1DD9499EF}"/>
-    <hyperlink ref="C95" r:id="rId126" xr:uid="{2C6B41AF-87E5-4DA5-9686-67EEDF628339}"/>
-    <hyperlink ref="C36" r:id="rId127" xr:uid="{1800FA32-51EA-41AB-8A1C-BCA281C1CA6B}"/>
-    <hyperlink ref="K75" r:id="rId128" xr:uid="{D1950805-AAE5-4A33-803E-9858D08F12A2}"/>
-    <hyperlink ref="K73" r:id="rId129" xr:uid="{01D963BB-A0C2-4C40-BA01-8B0B76381716}"/>
-    <hyperlink ref="K76" r:id="rId130" xr:uid="{D9B5F8EE-01B9-4AA5-9918-F987CA2D7884}"/>
-    <hyperlink ref="C97" r:id="rId131" display="https://czh-labs.com/products/terminal-block-breakout-board-module-for-teensy-41-screw-mount-version?gad_source=1&amp;gad_campaignid=17335691898&amp;gbraid=0AAAAADQKSWrLA97xSr9gmMM99UCSLmr58&amp;gclid=CjwKCAjwp_LDBhBCEiwAK7FnklUhjhvxFgmMMu0XiWu80nKxdv4QNWNVcUvZhioyk86weMe15LnzoRoClR4QAvD_BwE " xr:uid="{944A4911-F6CF-4EB3-82C2-8B8DAFBE56E9}"/>
-    <hyperlink ref="C37" r:id="rId132" xr:uid="{737F7509-05EB-4CE3-AA5B-929CB63FC161}"/>
-    <hyperlink ref="W16" r:id="rId133" xr:uid="{8B918A02-0CA6-4A4E-AA77-82C812145661}"/>
-    <hyperlink ref="W15" r:id="rId134" xr:uid="{1BBD1B38-BB9C-4FBE-A797-58DECC2562DA}"/>
-    <hyperlink ref="C8" r:id="rId135" xr:uid="{4755A74A-BAA1-4451-A83C-5F6302BF9DF2}"/>
+    <hyperlink ref="C101" r:id="rId100" xr:uid="{66B61CB6-8DEE-47E0-8F58-13DFE696A594}"/>
+    <hyperlink ref="C19" r:id="rId101" xr:uid="{25851340-5A38-4A26-A3FC-843A61F946D3}"/>
+    <hyperlink ref="C40" r:id="rId102" xr:uid="{E912526C-B82A-4A44-8481-EFACD695EA8D}"/>
+    <hyperlink ref="C44" r:id="rId103" xr:uid="{E865141B-878A-4CD6-B122-3ADC6852D520}"/>
+    <hyperlink ref="K58" r:id="rId104" location="tabbed-customerreviews " xr:uid="{24F44932-6634-42FE-8337-20CA3C2EC1E4}"/>
+    <hyperlink ref="C74" r:id="rId105" xr:uid="{326567BB-9D82-4E92-ACC4-530A6BCCFC38}"/>
+    <hyperlink ref="C17" r:id="rId106" display="https://www.amazon.com/Amazon-Basics-Ethernet-High-Speed-Snagless/dp/B089MGH8W3/ref=sr_1_6?crid=15O99JJ9VZUDS&amp;dib=eyJ2IjoiMSJ9.Qrm0YFmTEww5DZc4mrTYoBW2ITYU8YDRmdb4HE4nmukqEngrlTfGgHLb5uoFzqyB8DY16yxmWqTI2jhY13tKSS_gVPXMFmLrV8CwN6seDqr3fe6RoYGbAYOThLs_GPXGD9BG1xBtpSbQCaOmPeX6onzLKT90VpHEp8g8rhIrccYIWeUVb1y9yQszCgP-aLtJNIsqNx1o-8aHQGBnXQxbEdINQFklL4UDCld4WzwhnXy0xN-YFaHdxcyM5kmfmoYQEhD8UEUeVcULGl7eYpTBQi8RxGrjeWwsXTnPG7oVA4s.SJ0prHAqUML_3kLplif-xyTccwFoBx4GiK1cGmdOyLI&amp;dib_tag=se&amp;keywords=ethernet%2Bcable&amp;qid=1752782277&amp;s=electronics&amp;sprefix=ethernet%2Celectronics%2C124&amp;sr=1-6&amp;th=1 " xr:uid="{83A0A177-ED38-4C3C-B1E2-6D1A2C00DD2C}"/>
+    <hyperlink ref="C10" r:id="rId107" xr:uid="{5EF2B5FA-9EB9-4ED3-A87B-DB000918746C}"/>
+    <hyperlink ref="K13" r:id="rId108" display="https://www.amazon.com/Powerbuilt-Piece-Stubby-Long-Wrench/dp/B07N8F7W7K/ref=sr_1_19?dib=eyJ2IjoiMSJ9.URwdEPQXxCMLBhxvS9K5ftG6hwdCaLy_xWZ0vGXOdbuaNrb8XAmO4DQhIxovkvuXsRHPo7oCqjy9Wwt6H6QvZeRYOqVzaLjKkETlnA83OkSSXLxlPpzMt1Qy3kJt-T7GsO_Bq0c0QItERYLb6VTtZmMQdlqDEtc5mdwZiAksW1Y2IKpS2cr-V_j1_L0qMFZKPy2WuoytvNj5MEhK80MOfMrjnaTsJLpB9Io2Jt4xFodm6EN5AwCetZhDdsJTY6jdeOdEdPi6COl5b1RI-6XJHwylh2H13M74HgAUrEaRfoY.bAaypnaW3mj6ulkwXEha2QJSRXBFsgrmQMhuIwb4S2o&amp;dib_tag=se&amp;keywords=stubby%2Ballen%2Bwrench%2Bset&amp;qid=1752911269&amp;sr=8-19&amp;th=1 " xr:uid="{F2200CD7-83CF-497A-91E0-EF5B6CA80C0C}"/>
+    <hyperlink ref="K44" r:id="rId109" xr:uid="{F40A70E6-7F31-454F-9558-A7291A2A2DCF}"/>
+    <hyperlink ref="K45" r:id="rId110" xr:uid="{4A6F6959-0930-44EE-A971-B3EF13DA9390}"/>
+    <hyperlink ref="C51" r:id="rId111" xr:uid="{7963F571-8F62-4D9F-BEF7-F802CD4D18FC}"/>
+    <hyperlink ref="C93" r:id="rId112" xr:uid="{5A200CB5-C655-478F-B00B-2E82D8CC5C77}"/>
+    <hyperlink ref="C94:C95" r:id="rId113" display="https://8020.net/20-2020.html " xr:uid="{94C82CF7-4209-49DE-A286-0E429370F935}"/>
+    <hyperlink ref="C96" r:id="rId114" xr:uid="{3653483D-B8D7-4970-8BE1-067F3CE7FF42}"/>
+    <hyperlink ref="C87" r:id="rId115" xr:uid="{E1AC3FAD-797D-4D40-89E1-E0B078028B08}"/>
+    <hyperlink ref="C66" r:id="rId116" xr:uid="{8B53B0C9-AEB9-4C25-B4D5-D709A9909BD6}"/>
+    <hyperlink ref="C70" r:id="rId117" xr:uid="{2521E3A3-9809-485D-8952-C732415A0425}"/>
+    <hyperlink ref="K41" r:id="rId118" xr:uid="{BE5F57C8-C44E-47CF-B992-FEB02C6C001F}"/>
+    <hyperlink ref="K72" r:id="rId119" xr:uid="{A8E5D7AD-E110-498C-AD66-4031E7159275}"/>
+    <hyperlink ref="K74" r:id="rId120" xr:uid="{686F1C5B-AD14-408B-9AF5-1B4D26D75248}"/>
+    <hyperlink ref="K78" r:id="rId121" xr:uid="{A8336809-C542-4E15-9187-DB4F43D26933}"/>
+    <hyperlink ref="K79" r:id="rId122" xr:uid="{49B9B422-CDDA-427C-82B9-729F2266C333}"/>
+    <hyperlink ref="K80" r:id="rId123" xr:uid="{3E0AC7C3-82FC-4B11-AD25-3DE1DD9499EF}"/>
+    <hyperlink ref="C97" r:id="rId124" xr:uid="{2C6B41AF-87E5-4DA5-9686-67EEDF628339}"/>
+    <hyperlink ref="C36" r:id="rId125" xr:uid="{1800FA32-51EA-41AB-8A1C-BCA281C1CA6B}"/>
+    <hyperlink ref="K75" r:id="rId126" xr:uid="{D1950805-AAE5-4A33-803E-9858D08F12A2}"/>
+    <hyperlink ref="K73" r:id="rId127" xr:uid="{01D963BB-A0C2-4C40-BA01-8B0B76381716}"/>
+    <hyperlink ref="K76" r:id="rId128" xr:uid="{D9B5F8EE-01B9-4AA5-9918-F987CA2D7884}"/>
+    <hyperlink ref="C99" r:id="rId129" display="https://czh-labs.com/products/terminal-block-breakout-board-module-for-teensy-41-screw-mount-version?gad_source=1&amp;gad_campaignid=17335691898&amp;gbraid=0AAAAADQKSWrLA97xSr9gmMM99UCSLmr58&amp;gclid=CjwKCAjwp_LDBhBCEiwAK7FnklUhjhvxFgmMMu0XiWu80nKxdv4QNWNVcUvZhioyk86weMe15LnzoRoClR4QAvD_BwE " xr:uid="{944A4911-F6CF-4EB3-82C2-8B8DAFBE56E9}"/>
+    <hyperlink ref="C37" r:id="rId130" xr:uid="{737F7509-05EB-4CE3-AA5B-929CB63FC161}"/>
+    <hyperlink ref="C8" r:id="rId131" xr:uid="{64F7CD2D-21CD-4075-A33B-B33CA2888693}"/>
+    <hyperlink ref="C41" r:id="rId132" xr:uid="{C902CDD9-1F9D-452D-9583-852C1F7B1429}"/>
+    <hyperlink ref="C45" r:id="rId133" xr:uid="{7DA2E625-AACF-4DED-9279-AA3DDE590F85}"/>
+    <hyperlink ref="C42" r:id="rId134" xr:uid="{EA50026D-4CC0-4262-AA82-1A8C4D553DA4}"/>
+    <hyperlink ref="C43" r:id="rId135" xr:uid="{21A1C6AF-63D2-4FA9-AD9E-D674C1D15883}"/>
+    <hyperlink ref="C39" r:id="rId136" xr:uid="{63D3DD15-6374-4167-9E3E-2CFCBF201E30}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId136"/>
+  <pageSetup orientation="portrait" r:id="rId137"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="fb0bfce0-b493-4733-b695-336371de64d4" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a816e368-bd7d-4e73-ae60-f7bbf4d187c7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="71752533c218a459f0bd7314a8d27046">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56df45e61c8cd6f396207a6803100ce0" ns2:_="" ns3:_="">
     <xsd:import namespace="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
@@ -5986,6 +5851,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="fb0bfce0-b493-4733-b695-336371de64d4" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a816e368-bd7d-4e73-ae60-f7bbf4d187c7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5996,6 +5872,25 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5B4CFA9-3BF7-4410-A240-4C3EA4FF6CE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
+    <ds:schemaRef ds:uri="fb0bfce0-b493-4733-b695-336371de64d4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD534FFF-F9D4-45E9-B4A8-C5178968AA79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -6006,10 +5901,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E33DD76D-016E-470E-8735-9C85C5BAFB60}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
   <ds:schemaRefs>

--- a/LC-CNC-BoM.xlsx
+++ b/LC-CNC-BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk.sharepoint.com/sites/UT_DesktopMillingMachine/Shared Documents/General/GitHub-LC_CNC/LC-CNC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1089" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AC1B661-39A2-417C-8ADB-EB4069B0300D}"/>
+  <xr:revisionPtr revIDLastSave="1157" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C299951-1E5D-482B-8ECC-EC4B1A01A7AD}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4575" yWindow="1650" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="320">
   <si>
     <t>Item</t>
   </si>
@@ -725,12 +725,6 @@
     <t xml:space="preserve">https://www.amazon.com/gp/product/B0CJR4Y192/ref=ox_sc_act_title_2?smid=A1NCCSMTWFDZ34&amp;psc=1 </t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.amazon.com/Ethernet-Kit-for-Teensy-4-1/dp/B08CTM1L64/ref=sr_1_5?dib=eyJ2IjoiMSJ9.SbX6rnuR22BHW7UQV6IYcckSiyAyB1ZWr3cUVGCpjmoe8u9La0C4CnpYOniX7CwAfqWVpgmjNbJjLT76DhWe4ldG5P2p4WMYyJenE908txxUrz8DSqOHEjh3oVZE2stHV0rzuhfvuwF3CawGYaDmSg.85Xw8ylPJeTNJvqmoxZDt0Th8_d0wMGVyuH5z7GC-TU&amp;dib_tag=se&amp;qid=1752729706&amp;refinements=p_89%3APJRC&amp;sr=8-5&amp;srs=36931437011 </t>
-  </si>
-  <si>
-    <t>Ethernet Kit</t>
-  </si>
-  <si>
     <t>DAYTON Definite Purpose Magnetic Contactor</t>
   </si>
   <si>
@@ -740,9 +734,6 @@
     <t xml:space="preserve">https://www.amazon.com/dp/B07PZ1WB8S?psc=1&amp;smid=A26VZBPE6PT1GF&amp;ref_=chk_typ_imgToDp </t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.amazon.com/dp/B07TF63R4C?ref_=ppx_hzsearch_conn_dt_b_fed_asin_title_1&amp;th=1 </t>
-  </si>
-  <si>
     <t>10mm to 10mm Shaft Coupling</t>
   </si>
   <si>
@@ -752,9 +743,6 @@
     <t>NEMA 23 Stepper motor 3N-m</t>
   </si>
   <si>
-    <t>https://www.amazon.com/Jienk-KF2EDGK-Terminal-Connector-28-16AWG/dp/B09MHHPP25/ref=sr_1_1_sspa?crid=2AF6A8D8LGV1K&amp;dib=eyJ2IjoiMSJ9.q8IUsYwpHtwxUC4nKvpJJ5E3n8pZqTCBNDUZZZwpJz_cY5sNj3Fq76Fy-Qnl1SgjaCW2vPd-EN-SsNTXsL9li_txRXQWnoG51gzzu7XBZrvcrjbQGV51a41TxeymCRPUBDor-8_OKXwXbrqD6LX23dlwi0A05TCkdYOAKwf1qqH9OT2I9a3h0Ac3SfDbmvdbfLXlcB7ni4DL0bvN6Q3YXHRrUgVij9zRpT0E_MxOV6Sc2uY1_kpXSAUZYY2AG26Cmhr6jE0nPlKpJdHwt2ypNz4mNYmt0n1t5oVeAsT5yLw.bsp1pXhc1Is0gq2fnd2DtSPfsxI0LFXOwK2HSn65Ex0&amp;dib_tag=se&amp;keywords=KF2EDGK%2B3.5mm%2BPitch%2BScrew%2BTerminal%2BBlock&amp;qid=1752780492&amp;s=industrial&amp;sprefix=kf2edgk%2B3.5mm%2Bpitch%2Bscrew%2Bterminal%2Bblock%2Cindustrial%2C95&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 Pin Terminal Block </t>
   </si>
   <si>
@@ -797,16 +785,7 @@
     <t>Breakout board</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.amazon.com/gp/product/B0CJ26FGZC/ref=ox_sc_act_title_2?smid=A2IFOCZBWBH5F8&amp;th=1 </t>
-  </si>
-  <si>
     <t>110v Spindle Motor Kit，2.2Kw Square Air Cooled Spindle Motor 24000Rpm 400Hz ，VFD Variable Frequency Drive ，7 pcs ER11 Collets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.com/gp/product/B09VXH18J8/ref=ewc_pr_img_1?smid=A3E9T3KQ1YPBBY&amp;th=1 </t>
-  </si>
-  <si>
-    <t>RATTMMOTOR 2.2KW VFD</t>
   </si>
   <si>
     <t>Stub Allen Key set</t>
@@ -933,9 +912,6 @@
     <t xml:space="preserve">https://www.mcmaster.com/90031A151/ </t>
   </si>
   <si>
-    <t>Need to add:</t>
-  </si>
-  <si>
     <t>NOTE: Only one set of tools needed</t>
   </si>
   <si>
@@ -1024,9 +1000,6 @@
     </r>
   </si>
   <si>
-    <t>super glue</t>
-  </si>
-  <si>
     <t>1CH Optocoupler isolation board</t>
   </si>
   <si>
@@ -1063,19 +1036,31 @@
     <t xml:space="preserve">https://www.amazon.com/gp/product/B0BY51FJGY/ref=ewc_pr_img_1?smid=AO6JMNGOG26ZH&amp;th=1 </t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t>old motors for x and y</t>
-  </si>
-  <si>
-    <t>Spindle Option 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.com/gp/product/B0B99QL131/ref=ox_sc_act_title_2?th=1 </t>
-  </si>
-  <si>
-    <t>110v Spindle Motor Kit，1.5Kw Square Air Cooled Spindle Motor 24000Rpm 400Hz ，VFD Variable Frequency Drive ，7 pcs ER11 Collets</t>
+    <t xml:space="preserve">https://a.co/d/04KkNO5x </t>
+  </si>
+  <si>
+    <t>NEMA 23 Stepper motor 2.4N-m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/0cYAOFF7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/0aCp7x5M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/0c78GAUY </t>
+  </si>
+  <si>
+    <t>8mm to 10mm Shaft Coupling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/04Kofe6e </t>
+  </si>
+  <si>
+    <t>Teensy 4.1 Ethernet Kit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/07VW1Jxs </t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1071,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1171,15 +1156,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1212,7 +1188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1696,94 +1672,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1813,13 +1707,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1878,8 +1771,8 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1892,15 +1785,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2182,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AA107"/>
+  <dimension ref="B1:R107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -2195,87 +2079,87 @@
     <col min="22" max="22" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="61"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="19">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K2" s="72" t="s">
-        <v>282</v>
-      </c>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="74"/>
-    </row>
-    <row r="3" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
+      <c r="K2" s="71" t="s">
+        <v>274</v>
+      </c>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="73"/>
+    </row>
+    <row r="3" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="44" t="s">
+      <c r="C3" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="F3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="44" t="s">
+      <c r="G3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="J3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="44" t="s">
+      <c r="K3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="44" t="s">
+      <c r="M3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="44" t="s">
+      <c r="N3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="44" t="s">
+      <c r="O3" s="43" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="62" t="s">
+    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="J4" s="62" t="s">
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="68"/>
+      <c r="J4" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-    </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="63"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
@@ -2285,16 +2169,16 @@
       <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="39">
-        <f>G2*10</f>
-        <v>10</v>
+      <c r="E5" s="38">
+        <f>G2*15</f>
+        <v>15</v>
       </c>
       <c r="F5" s="5">
         <v>3.33</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="39">
         <f>E5*F5</f>
-        <v>33.299999999999997</v>
+        <v>49.95</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>143</v>
@@ -2311,31 +2195,30 @@
       <c r="N5" s="5">
         <v>20.99</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="39">
         <f t="shared" ref="O5:O13" si="0">M5*N5</f>
         <v>20.99</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="37">
-        <f>G2*10</f>
-        <v>10</v>
-      </c>
-      <c r="F6" s="36">
+      <c r="D6" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="36">
+        <v>15</v>
+      </c>
+      <c r="F6" s="35">
         <v>1.73</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="37">
         <f t="shared" ref="G6" si="1">E6*F6</f>
-        <v>17.3</v>
+        <v>25.95</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>12</v>
@@ -2357,15 +2240,15 @@
         <v>14.99</v>
       </c>
     </row>
-    <row r="7" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="62" t="s">
+    <row r="7" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="64"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63"/>
       <c r="J7" s="2" t="s">
         <v>178</v>
       </c>
@@ -2386,26 +2269,26 @@
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>324</v>
+        <v>249</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="38">
         <f>G2*1</f>
         <v>1</v>
       </c>
       <c r="F8" s="5">
-        <v>278.99</v>
-      </c>
-      <c r="G8" s="40">
+        <v>359.99</v>
+      </c>
+      <c r="G8" s="39">
         <f t="shared" ref="G8:G14" si="2">E8*F8</f>
-        <v>278.99</v>
+        <v>359.99</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>179</v>
@@ -2427,7 +2310,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>120</v>
       </c>
@@ -2468,12 +2351,12 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>9</v>
@@ -2509,7 +2392,7 @@
         <v>27.99</v>
       </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
@@ -2550,7 +2433,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
@@ -2591,7 +2474,7 @@
         <v>18.690000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
@@ -2613,10 +2496,10 @@
         <v>16.989999999999998</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>9</v>
@@ -2632,7 +2515,7 @@
         <v>24.99</v>
       </c>
     </row>
-    <row r="14" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2672,11 +2555,8 @@
         <f t="shared" ref="O14:O20" si="3">M14*N14</f>
         <v>15.09</v>
       </c>
-      <c r="V14" s="78" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>121</v>
       </c>
@@ -2716,28 +2596,8 @@
         <f t="shared" si="3"/>
         <v>25.5</v>
       </c>
-      <c r="V15" s="79" t="s">
-        <v>254</v>
-      </c>
-      <c r="W15" s="80" t="s">
-        <v>253</v>
-      </c>
-      <c r="X15" s="81" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y15" s="82">
-        <f>AA9*1</f>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="83">
-        <v>209.99</v>
-      </c>
-      <c r="AA15" s="84">
-        <f t="shared" ref="AA15:AA16" si="4">Y15*Z15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>24</v>
       </c>
@@ -2777,33 +2637,13 @@
         <f t="shared" si="3"/>
         <v>162</v>
       </c>
-      <c r="V16" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="W16" s="85" t="s">
-        <v>255</v>
-      </c>
-      <c r="X16" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y16" s="86">
-        <f>AA9*1</f>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="31">
-        <v>90</v>
-      </c>
-      <c r="AA16" s="32">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>9</v>
@@ -2816,7 +2656,7 @@
         <v>6.39</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" ref="G17:G22" si="5">E17*F17</f>
+        <f t="shared" ref="G17:G22" si="4">E17*F17</f>
         <v>6.39</v>
       </c>
       <c r="J17" s="2" t="s">
@@ -2839,7 +2679,7 @@
         <v>23.99</v>
       </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
@@ -2857,7 +2697,7 @@
         <v>12.99</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>12.99</v>
       </c>
       <c r="J18" s="2" t="s">
@@ -2879,16 +2719,13 @@
         <f t="shared" si="3"/>
         <v>13.99</v>
       </c>
-      <c r="V18" s="23" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>9</v>
@@ -2901,7 +2738,7 @@
         <v>9.99</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>19.98</v>
       </c>
       <c r="J19" s="2" t="s">
@@ -2923,11 +2760,8 @@
         <f t="shared" si="3"/>
         <v>12.81</v>
       </c>
-      <c r="V19" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="20" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
@@ -2945,7 +2779,7 @@
         <v>39.99</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>39.99</v>
       </c>
       <c r="J20" s="16" t="s">
@@ -2954,21 +2788,21 @@
       <c r="K20" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="L20" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M20" s="35">
-        <v>1</v>
-      </c>
-      <c r="N20" s="36">
+      <c r="L20" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M20" s="34">
+        <v>1</v>
+      </c>
+      <c r="N20" s="35">
         <v>34.97</v>
       </c>
-      <c r="O20" s="38">
+      <c r="O20" s="37">
         <f t="shared" si="3"/>
         <v>34.97</v>
       </c>
     </row>
-    <row r="21" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
@@ -2986,22 +2820,19 @@
         <v>34.69</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>69.38</v>
       </c>
-      <c r="J21" s="62" t="s">
+      <c r="J21" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="63"/>
-      <c r="L21" s="63"/>
-      <c r="M21" s="63"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="64"/>
-      <c r="V21" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="63"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>32</v>
       </c>
@@ -3019,7 +2850,7 @@
         <v>40.39</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>40.39</v>
       </c>
       <c r="J22" s="2" t="s">
@@ -3037,12 +2868,12 @@
       <c r="N22" s="5">
         <v>9.5399999999999991</v>
       </c>
-      <c r="O22" s="40">
-        <f t="shared" ref="O22:O25" si="6">M22*N22</f>
+      <c r="O22" s="39">
+        <f t="shared" ref="O22:O25" si="5">M22*N22</f>
         <v>9.5399999999999991</v>
       </c>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>34</v>
       </c>
@@ -3079,11 +2910,11 @@
         <v>41.86</v>
       </c>
       <c r="O23" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>41.86</v>
       </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
@@ -3101,7 +2932,7 @@
         <v>8.99</v>
       </c>
       <c r="G24" s="6">
-        <f t="shared" ref="G24:G43" si="7">E24*F24</f>
+        <f t="shared" ref="G24:G45" si="6">E24*F24</f>
         <v>8.99</v>
       </c>
       <c r="J24" s="2" t="s">
@@ -3120,11 +2951,11 @@
         <v>36.15</v>
       </c>
       <c r="O24" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>36.15</v>
       </c>
     </row>
-    <row r="25" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
@@ -3142,7 +2973,7 @@
         <v>48.99</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>48.99</v>
       </c>
       <c r="J25" s="16" t="s">
@@ -3151,24 +2982,24 @@
       <c r="K25" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="L25" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M25" s="35">
-        <v>1</v>
-      </c>
-      <c r="N25" s="36">
+      <c r="L25" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M25" s="34">
+        <v>1</v>
+      </c>
+      <c r="N25" s="35">
         <v>7.55</v>
       </c>
-      <c r="O25" s="38">
-        <f t="shared" si="6"/>
+      <c r="O25" s="37">
+        <f t="shared" si="5"/>
         <v>7.55</v>
       </c>
       <c r="R25" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>39</v>
       </c>
@@ -3186,19 +3017,19 @@
         <v>8.99</v>
       </c>
       <c r="G26" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>8.99</v>
       </c>
-      <c r="J26" s="62" t="s">
+      <c r="J26" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="K26" s="63"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="64"/>
-    </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="K26" s="62"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="63"/>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>41</v>
       </c>
@@ -3216,7 +3047,7 @@
         <v>124</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>124</v>
       </c>
       <c r="J27" s="2" t="s">
@@ -3234,12 +3065,12 @@
       <c r="N27" s="5">
         <v>55.35</v>
       </c>
-      <c r="O27" s="40">
+      <c r="O27" s="39">
         <f>M27*N27</f>
         <v>55.35</v>
       </c>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
@@ -3257,7 +3088,7 @@
         <v>45.34</v>
       </c>
       <c r="G28" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>45.34</v>
       </c>
       <c r="J28" s="2" t="s">
@@ -3276,11 +3107,11 @@
         <v>35.76</v>
       </c>
       <c r="O28" s="6">
-        <f t="shared" ref="O28:O29" si="8">M28*N28</f>
+        <f t="shared" ref="O28:O29" si="7">M28*N28</f>
         <v>35.76</v>
       </c>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>57</v>
       </c>
@@ -3317,11 +3148,11 @@
         <v>30.07</v>
       </c>
       <c r="O29" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>30.07</v>
       </c>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
@@ -3339,7 +3170,7 @@
         <v>51.74</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" ref="G30" si="9">E30*F30</f>
+        <f t="shared" ref="G30" si="8">E30*F30</f>
         <v>51.74</v>
       </c>
       <c r="J30" s="2" t="s">
@@ -3362,7 +3193,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>61</v>
       </c>
@@ -3380,7 +3211,7 @@
         <v>15.99</v>
       </c>
       <c r="G31" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>15.99</v>
       </c>
       <c r="J31" s="2" t="s">
@@ -3403,7 +3234,7 @@
         <v>87.75</v>
       </c>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>134</v>
       </c>
@@ -3421,7 +3252,7 @@
         <v>7.69</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7.69</v>
       </c>
       <c r="J32" s="2" t="s">
@@ -3462,7 +3293,7 @@
         <v>11.47</v>
       </c>
       <c r="G33" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>11.47</v>
       </c>
       <c r="J33" s="2" t="s">
@@ -3503,7 +3334,7 @@
         <v>12.99</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" ref="G34" si="10">E34*F34</f>
+        <f t="shared" ref="G34" si="9">E34*F34</f>
         <v>12.99</v>
       </c>
       <c r="J34" s="2" t="s">
@@ -3522,7 +3353,7 @@
         <v>84.66</v>
       </c>
       <c r="O34" s="6">
-        <f t="shared" ref="O34" si="11">M34*N34</f>
+        <f t="shared" ref="O34" si="10">M34*N34</f>
         <v>84.66</v>
       </c>
     </row>
@@ -3563,16 +3394,16 @@
         <v>102.36</v>
       </c>
       <c r="O35" s="6">
-        <f t="shared" ref="O35" si="12">M35*N35</f>
+        <f t="shared" ref="O35" si="11">M35*N35</f>
         <v>102.36</v>
       </c>
     </row>
     <row r="36" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>9</v>
@@ -3584,16 +3415,16 @@
         <v>13.99</v>
       </c>
       <c r="G36" s="6">
-        <f t="shared" ref="G36:G37" si="13">E36*F36</f>
+        <f t="shared" ref="G36:G37" si="12">E36*F36</f>
         <v>13.99</v>
       </c>
-      <c r="J36" s="65" t="s">
+      <c r="J36" s="64" t="s">
         <v>196</v>
       </c>
-      <c r="K36" s="66"/>
-      <c r="L36" s="66"/>
-      <c r="M36" s="66"/>
-      <c r="N36" s="67"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="66"/>
       <c r="O36" s="14">
         <f>SUM(O5:O35)</f>
         <v>1259.6799999999998</v>
@@ -3601,10 +3432,10 @@
     </row>
     <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>9</v>
@@ -3617,7 +3448,7 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G37" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>39.979999999999997</v>
       </c>
     </row>
@@ -3645,20 +3476,20 @@
       <c r="J38" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="K38" s="72" t="s">
-        <v>284</v>
-      </c>
-      <c r="L38" s="73"/>
-      <c r="M38" s="73"/>
-      <c r="N38" s="73"/>
-      <c r="O38" s="74"/>
+      <c r="K38" s="71" t="s">
+        <v>276</v>
+      </c>
+      <c r="L38" s="72"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="73"/>
     </row>
     <row r="39" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>229</v>
+        <v>319</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>9</v>
@@ -3668,37 +3499,37 @@
         <v>1</v>
       </c>
       <c r="F39" s="5">
-        <v>8.5399999999999991</v>
+        <v>9.99</v>
       </c>
       <c r="G39" s="6">
-        <f>E39*F39</f>
-        <v>8.5399999999999991</v>
-      </c>
-      <c r="J39" s="47" t="s">
+        <f t="shared" ref="G39:G44" si="13">E39*F39</f>
+        <v>9.99</v>
+      </c>
+      <c r="J39" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="K39" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="L39" s="44" t="s">
+      <c r="K39" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="L39" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="M39" s="44" t="s">
+      <c r="M39" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="N39" s="44" t="s">
+      <c r="N39" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="O39" s="44" t="s">
+      <c r="O39" s="43" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>238</v>
+        <v>234</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>233</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>9</v>
@@ -3708,43 +3539,44 @@
         <v>1</v>
       </c>
       <c r="F40" s="5">
-        <v>9.99</v>
+        <v>39.99</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" ref="G40:G42" si="14">E40*F40</f>
-        <v>9.99</v>
-      </c>
-      <c r="J40" s="62" t="s">
+        <f t="shared" si="13"/>
+        <v>39.99</v>
+      </c>
+      <c r="J40" s="61" t="s">
         <v>217</v>
       </c>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
-      <c r="O40" s="69"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="67"/>
+      <c r="O40" s="68"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>236</v>
+        <v>312</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>313</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E41" s="20">
-        <v>1</v>
+        <f>G2*2</f>
+        <v>2</v>
       </c>
       <c r="F41" s="5">
-        <v>39.99</v>
+        <v>25.99</v>
       </c>
       <c r="G41" s="6">
-        <f t="shared" si="14"/>
-        <v>39.99</v>
+        <f t="shared" si="13"/>
+        <v>51.98</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>218</v>
@@ -3758,17 +3590,17 @@
       <c r="N41" s="5">
         <v>77.319999999999993</v>
       </c>
-      <c r="O41" s="40">
-        <f t="shared" ref="O41:O42" si="15">M41*N41</f>
+      <c r="O41" s="39">
+        <f t="shared" ref="O41:O42" si="14">M41*N41</f>
         <v>77.319999999999993</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>240</v>
+        <v>316</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>9</v>
@@ -3778,14 +3610,14 @@
         <v>1</v>
       </c>
       <c r="F42" s="5">
-        <v>44.15</v>
+        <v>12.99</v>
       </c>
       <c r="G42" s="6">
-        <f t="shared" si="14"/>
-        <v>44.15</v>
+        <f t="shared" si="13"/>
+        <v>12.99</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>219</v>
@@ -3800,33 +3632,33 @@
         <v>22.81</v>
       </c>
       <c r="O42" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>22.81</v>
       </c>
     </row>
-    <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>234</v>
+        <v>318</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="20">
-        <f>G2*2</f>
-        <v>2</v>
+        <f>G2*1</f>
+        <v>1</v>
       </c>
       <c r="F43" s="5">
-        <v>12.99</v>
+        <v>13.95</v>
       </c>
       <c r="G43" s="6">
-        <f t="shared" si="7"/>
-        <v>25.98</v>
+        <f t="shared" si="13"/>
+        <v>13.95</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="K43" s="12" t="s">
         <v>220</v>
@@ -3845,20 +3677,32 @@
         <v>16.12</v>
       </c>
     </row>
-    <row r="44" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="62" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="68"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="69"/>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F44" s="5">
+        <v>44.15</v>
+      </c>
+      <c r="G44" s="6">
+        <f t="shared" si="13"/>
+        <v>44.15</v>
+      </c>
       <c r="J44" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>9</v>
@@ -3875,172 +3719,160 @@
       </c>
     </row>
     <row r="45" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F45" s="5">
+        <v>12.99</v>
+      </c>
+      <c r="G45" s="6">
+        <f t="shared" si="6"/>
+        <v>12.99</v>
+      </c>
+      <c r="J45" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="K45" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="L45" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M45" s="36">
+        <v>1</v>
+      </c>
+      <c r="N45" s="35">
+        <v>53</v>
+      </c>
+      <c r="O45" s="37">
+        <f>M45*N45</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="68"/>
+      <c r="J46" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="K46" s="67"/>
+      <c r="L46" s="67"/>
+      <c r="M46" s="67"/>
+      <c r="N46" s="67"/>
+      <c r="O46" s="68"/>
+    </row>
+    <row r="47" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C45" s="22" t="s">
+      <c r="C47" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D45" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="41">
+      <c r="D47" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="40">
         <f>G2*10</f>
         <v>10</v>
       </c>
-      <c r="F45" s="36">
+      <c r="F47" s="35">
         <v>0.88560000000000005</v>
       </c>
-      <c r="G45" s="42">
-        <f>E45*F45</f>
+      <c r="G47" s="41">
+        <f>E47*F47</f>
         <v>8.8559999999999999</v>
       </c>
-      <c r="J45" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="K45" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="L45" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M45" s="37">
-        <v>1</v>
-      </c>
-      <c r="N45" s="36">
-        <v>53</v>
-      </c>
-      <c r="O45" s="38">
-        <f>M45*N45</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="62" t="s">
+      <c r="J47" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M47" s="4">
+        <v>2</v>
+      </c>
+      <c r="N47" s="5">
+        <v>19.63</v>
+      </c>
+      <c r="O47" s="39">
+        <v>39.26</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="63"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="63"/>
-      <c r="G46" s="64"/>
-      <c r="J46" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="K46" s="68"/>
-      <c r="L46" s="68"/>
-      <c r="M46" s="68"/>
-      <c r="N46" s="68"/>
-      <c r="O46" s="69"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="63"/>
+      <c r="J48" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M48" s="4">
+        <v>2</v>
+      </c>
+      <c r="N48" s="5">
+        <v>28.81</v>
+      </c>
+      <c r="O48" s="6">
+        <v>57.62</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C49" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="39">
+      <c r="D49" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="38">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F49" s="5">
         <v>14.77</v>
       </c>
-      <c r="G47" s="40">
-        <f t="shared" ref="G47:G99" si="16">E47*F47</f>
+      <c r="G49" s="39">
+        <f t="shared" ref="G49:G101" si="15">E49*F49</f>
         <v>29.54</v>
       </c>
-      <c r="J47" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M47" s="4">
-        <v>2</v>
-      </c>
-      <c r="N47" s="5">
-        <v>19.63</v>
-      </c>
-      <c r="O47" s="40">
-        <v>39.26</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="20">
-        <f>G2*2</f>
-        <v>2</v>
-      </c>
-      <c r="F48" s="5">
-        <v>7.8</v>
-      </c>
-      <c r="G48" s="6">
-        <f t="shared" si="16"/>
-        <v>15.6</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="K48" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="L48" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M48" s="4">
-        <v>2</v>
-      </c>
-      <c r="N48" s="5">
-        <v>28.81</v>
-      </c>
-      <c r="O48" s="6">
-        <v>57.62</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="20">
-        <f>G2*2</f>
-        <v>2</v>
-      </c>
-      <c r="F49" s="5">
-        <v>13.05</v>
-      </c>
-      <c r="G49" s="6">
-        <f t="shared" si="16"/>
-        <v>26.1</v>
-      </c>
-      <c r="J49" s="65" t="s">
+      <c r="J49" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="K49" s="66"/>
-      <c r="L49" s="66"/>
-      <c r="M49" s="66"/>
-      <c r="N49" s="67"/>
+      <c r="K49" s="65"/>
+      <c r="L49" s="65"/>
+      <c r="M49" s="65"/>
+      <c r="N49" s="66"/>
       <c r="O49" s="14">
         <f>SUM(O40:O48)</f>
         <v>319.13</v>
@@ -4048,296 +3880,296 @@
     </row>
     <row r="50" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>129</v>
+        <v>47</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E50" s="20">
-        <f>G2*1</f>
-        <v>1</v>
+        <f>G2*2</f>
+        <v>2</v>
       </c>
       <c r="F50" s="5">
-        <v>9.01</v>
+        <v>7.8</v>
       </c>
       <c r="G50" s="6">
-        <f t="shared" si="16"/>
-        <v>9.01</v>
+        <f t="shared" si="15"/>
+        <v>15.6</v>
       </c>
     </row>
     <row r="51" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="20">
+        <f>G2*2</f>
+        <v>2</v>
+      </c>
+      <c r="F51" s="5">
+        <v>13.05</v>
+      </c>
+      <c r="G51" s="6">
+        <f t="shared" si="15"/>
+        <v>26.1</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="K51" s="71" t="s">
+        <v>287</v>
+      </c>
+      <c r="L51" s="72"/>
+      <c r="M51" s="72"/>
+      <c r="N51" s="72"/>
+      <c r="O51" s="73"/>
+    </row>
+    <row r="52" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F52" s="5">
+        <v>9.01</v>
+      </c>
+      <c r="G52" s="6">
+        <f t="shared" si="15"/>
+        <v>9.01</v>
+      </c>
+      <c r="J52" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="K52" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="L52" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="M52" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C53" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="20">
+      <c r="D53" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="20">
         <f>G2*4</f>
         <v>4</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F53" s="5">
         <v>3.81</v>
       </c>
-      <c r="G51" s="6">
-        <f t="shared" si="16"/>
+      <c r="G53" s="6">
+        <f t="shared" si="15"/>
         <v>15.24</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="K51" s="72" t="s">
-        <v>295</v>
-      </c>
-      <c r="L51" s="73"/>
-      <c r="M51" s="73"/>
-      <c r="N51" s="73"/>
-      <c r="O51" s="74"/>
-    </row>
-    <row r="52" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="2" t="s">
+      <c r="J53" s="61" t="s">
+        <v>217</v>
+      </c>
+      <c r="K53" s="67"/>
+      <c r="L53" s="67"/>
+      <c r="M53" s="67"/>
+      <c r="N53" s="67"/>
+      <c r="O53" s="68"/>
+    </row>
+    <row r="54" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C54" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F52" s="5">
+      <c r="D54" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F54" s="5">
         <v>5.29</v>
       </c>
-      <c r="G52" s="6">
-        <f t="shared" si="16"/>
+      <c r="G54" s="6">
+        <f t="shared" si="15"/>
         <v>5.29</v>
       </c>
-      <c r="J52" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="K52" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="L52" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="M52" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="45" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="2" t="s">
+      <c r="J54" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="K54" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="L54" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M54" s="34">
+        <v>1</v>
+      </c>
+      <c r="N54" s="35">
+        <v>721.96</v>
+      </c>
+      <c r="O54" s="41">
+        <f t="shared" ref="O54:O56" si="16">M54*N54</f>
+        <v>721.96</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C55" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="20">
+      <c r="D55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="20">
         <f>G2*10</f>
         <v>10</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F55" s="5">
         <v>4.18</v>
       </c>
-      <c r="G53" s="6">
-        <f t="shared" si="16"/>
+      <c r="G55" s="6">
+        <f t="shared" si="15"/>
         <v>41.8</v>
       </c>
-      <c r="J53" s="62" t="s">
-        <v>217</v>
-      </c>
-      <c r="K53" s="68"/>
-      <c r="L53" s="68"/>
-      <c r="M53" s="68"/>
-      <c r="N53" s="68"/>
-      <c r="O53" s="69"/>
-    </row>
-    <row r="54" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="2" t="s">
+      <c r="J55" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="K55" s="67"/>
+      <c r="L55" s="67"/>
+      <c r="M55" s="67"/>
+      <c r="N55" s="67"/>
+      <c r="O55" s="68"/>
+    </row>
+    <row r="56" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="20">
+      <c r="D56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="20">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F56" s="5">
         <v>30.67</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G56" s="6">
+        <f t="shared" si="15"/>
+        <v>61.34</v>
+      </c>
+      <c r="J56" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="K56" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="L56" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M56" s="34">
+        <v>1</v>
+      </c>
+      <c r="N56" s="35">
+        <v>367.84</v>
+      </c>
+      <c r="O56" s="41">
         <f t="shared" si="16"/>
-        <v>61.34</v>
-      </c>
-      <c r="J54" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="K54" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="L54" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M54" s="35">
-        <v>1</v>
-      </c>
-      <c r="N54" s="36">
-        <v>721.96</v>
-      </c>
-      <c r="O54" s="42">
-        <f t="shared" ref="O54:O56" si="17">M54*N54</f>
-        <v>721.96</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="2" t="s">
+        <v>367.84</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" s="20">
+      <c r="D57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="20">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F57" s="5">
         <v>9.5500000000000007</v>
       </c>
-      <c r="G55" s="6">
-        <f t="shared" ref="G55:G62" si="18">E55*F55</f>
+      <c r="G57" s="6">
+        <f t="shared" ref="G57:G64" si="17">E57*F57</f>
         <v>19.100000000000001</v>
       </c>
-      <c r="J55" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="K55" s="68"/>
-      <c r="L55" s="68"/>
-      <c r="M55" s="68"/>
-      <c r="N55" s="68"/>
-      <c r="O55" s="69"/>
-    </row>
-    <row r="56" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="2" t="s">
+      <c r="J57" s="61" t="s">
+        <v>238</v>
+      </c>
+      <c r="K57" s="67"/>
+      <c r="L57" s="67"/>
+      <c r="M57" s="67"/>
+      <c r="N57" s="67"/>
+      <c r="O57" s="68"/>
+    </row>
+    <row r="58" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C58" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F56" s="5">
+      <c r="D58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F58" s="5">
         <v>16.87</v>
       </c>
-      <c r="G56" s="6">
-        <f t="shared" si="18"/>
+      <c r="G58" s="6">
+        <f t="shared" si="17"/>
         <v>16.87</v>
       </c>
-      <c r="J56" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="K56" s="43" t="s">
-        <v>227</v>
-      </c>
-      <c r="L56" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M56" s="35">
-        <v>1</v>
-      </c>
-      <c r="N56" s="36">
-        <v>367.84</v>
-      </c>
-      <c r="O56" s="42">
-        <f t="shared" si="17"/>
-        <v>367.84</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F57" s="5">
-        <v>8.33</v>
-      </c>
-      <c r="G57" s="6">
-        <f t="shared" si="18"/>
-        <v>8.33</v>
-      </c>
-      <c r="J57" s="62" t="s">
-        <v>242</v>
-      </c>
-      <c r="K57" s="68"/>
-      <c r="L57" s="68"/>
-      <c r="M57" s="68"/>
-      <c r="N57" s="68"/>
-      <c r="O57" s="69"/>
-    </row>
-    <row r="58" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F58" s="5">
-        <v>20.87</v>
-      </c>
-      <c r="G58" s="6">
-        <f t="shared" si="18"/>
-        <v>20.87</v>
-      </c>
       <c r="J58" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K58" s="12" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="L58" s="4" t="s">
         <v>9</v>
@@ -4348,143 +4180,144 @@
       <c r="N58" s="5">
         <v>239.99</v>
       </c>
-      <c r="O58" s="40">
-        <f t="shared" ref="O58" si="19">M58*N58</f>
+      <c r="O58" s="39">
+        <f t="shared" ref="O58" si="18">M58*N58</f>
         <v>239.99</v>
       </c>
     </row>
     <row r="59" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F59" s="5">
+        <v>8.33</v>
+      </c>
+      <c r="G59" s="6">
+        <f t="shared" si="17"/>
+        <v>8.33</v>
+      </c>
+      <c r="J59" s="64" t="s">
+        <v>188</v>
+      </c>
+      <c r="K59" s="65"/>
+      <c r="L59" s="65"/>
+      <c r="M59" s="65"/>
+      <c r="N59" s="66"/>
+      <c r="O59" s="14">
+        <f>SUM(O54,O58)</f>
+        <v>961.95</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F60" s="5">
+        <v>20.87</v>
+      </c>
+      <c r="G60" s="6">
+        <f t="shared" si="17"/>
+        <v>20.87</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C61" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" s="20">
+      <c r="D61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="20">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F61" s="5">
         <v>11.38</v>
       </c>
-      <c r="G59" s="6">
-        <f t="shared" si="18"/>
+      <c r="G61" s="6">
+        <f t="shared" si="17"/>
         <v>22.76</v>
       </c>
-      <c r="J59" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="K59" s="66"/>
-      <c r="L59" s="66"/>
-      <c r="M59" s="66"/>
-      <c r="N59" s="67"/>
-      <c r="O59" s="14" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="16" t="s">
+      <c r="J61" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="K61" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="L61" s="72"/>
+      <c r="M61" s="72"/>
+      <c r="N61" s="72"/>
+      <c r="O61" s="73"/>
+    </row>
+    <row r="62" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C62" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F60" s="5">
+      <c r="D62" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F62" s="5">
         <v>10.71</v>
       </c>
-      <c r="G60" s="6">
-        <f t="shared" si="18"/>
+      <c r="G62" s="6">
+        <f t="shared" si="17"/>
         <v>10.71</v>
       </c>
-    </row>
-    <row r="61" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F61" s="5">
-        <v>12.36</v>
-      </c>
-      <c r="G61" s="6">
-        <f t="shared" si="18"/>
-        <v>12.36</v>
-      </c>
-      <c r="J61" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="K61" s="72" t="s">
-        <v>304</v>
-      </c>
-      <c r="L61" s="73"/>
-      <c r="M61" s="73"/>
-      <c r="N61" s="73"/>
-      <c r="O61" s="74"/>
-    </row>
-    <row r="62" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F62" s="5">
-        <v>7.78</v>
-      </c>
-      <c r="G62" s="6">
-        <f t="shared" si="18"/>
-        <v>7.78</v>
-      </c>
-      <c r="J62" s="48" t="s">
+      <c r="J62" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="K62" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="L62" s="49" t="s">
+      <c r="K62" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="L62" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="M62" s="49" t="s">
+      <c r="M62" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="49" t="s">
+      <c r="N62" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="50" t="s">
+      <c r="O62" s="49" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="63" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>9</v>
@@ -4494,277 +4327,277 @@
         <v>1</v>
       </c>
       <c r="F63" s="5">
-        <v>12.92</v>
+        <v>12.36</v>
       </c>
       <c r="G63" s="6">
-        <f t="shared" ref="G63:G68" si="20">E63*F63</f>
-        <v>12.92</v>
-      </c>
-      <c r="J63" s="62" t="s">
-        <v>263</v>
-      </c>
-      <c r="K63" s="70"/>
-      <c r="L63" s="70"/>
-      <c r="M63" s="70"/>
-      <c r="N63" s="70"/>
-      <c r="O63" s="71"/>
+        <f t="shared" si="17"/>
+        <v>12.36</v>
+      </c>
+      <c r="J63" s="61" t="s">
+        <v>256</v>
+      </c>
+      <c r="K63" s="69"/>
+      <c r="L63" s="69"/>
+      <c r="M63" s="69"/>
+      <c r="N63" s="69"/>
+      <c r="O63" s="70"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C64" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F64" s="5">
+        <v>7.78</v>
+      </c>
+      <c r="G64" s="6">
+        <f t="shared" si="17"/>
+        <v>7.78</v>
+      </c>
+      <c r="J64" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="K64" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M64" s="4">
+        <v>1</v>
+      </c>
+      <c r="N64" s="5">
+        <v>135</v>
+      </c>
+      <c r="O64" s="50">
+        <f t="shared" ref="O64:O65" si="19">M64*N64</f>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F65" s="5">
+        <v>12.92</v>
+      </c>
+      <c r="G65" s="6">
+        <f t="shared" ref="G65:G70" si="20">E65*F65</f>
+        <v>12.92</v>
+      </c>
+      <c r="J65" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="K65" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M65" s="4">
+        <v>1</v>
+      </c>
+      <c r="N65" s="5">
+        <v>280</v>
+      </c>
+      <c r="O65" s="26">
+        <f t="shared" si="19"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C66" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F64" s="5">
+      <c r="D66" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F66" s="5">
         <v>8</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G66" s="6">
         <f t="shared" si="20"/>
         <v>8</v>
       </c>
-      <c r="J64" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="K64" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M64" s="4">
-        <v>1</v>
-      </c>
-      <c r="N64" s="5">
-        <v>135</v>
-      </c>
-      <c r="O64" s="51">
-        <f t="shared" ref="O64:O65" si="21">M64*N64</f>
-        <v>135</v>
-      </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B65" s="2" t="s">
+      <c r="J66" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="K66" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="L66" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M66" s="29">
+        <v>1</v>
+      </c>
+      <c r="N66" s="30">
+        <v>102</v>
+      </c>
+      <c r="O66" s="31">
+        <f>M66*N66</f>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C67" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F65" s="5">
+      <c r="D67" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F67" s="5">
         <v>13.4</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G67" s="6">
         <f t="shared" si="20"/>
         <v>13.4</v>
       </c>
-      <c r="J65" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="K65" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M65" s="4">
-        <v>1</v>
-      </c>
-      <c r="N65" s="5">
-        <v>280</v>
-      </c>
-      <c r="O65" s="27">
-        <f t="shared" si="21"/>
-        <v>280</v>
-      </c>
-    </row>
-    <row r="66" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="2" t="s">
+      <c r="J67" s="64" t="s">
+        <v>188</v>
+      </c>
+      <c r="K67" s="65"/>
+      <c r="L67" s="65"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="66"/>
+      <c r="O67" s="32">
+        <f>SUM(O64:O66)</f>
+        <v>517</v>
+      </c>
+    </row>
+    <row r="68" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C68" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F66" s="5">
+      <c r="D68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F68" s="5">
         <v>3.11</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G68" s="6">
         <f t="shared" si="20"/>
         <v>3.11</v>
       </c>
-      <c r="J66" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="K66" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="L66" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M66" s="30">
-        <v>1</v>
-      </c>
-      <c r="N66" s="31">
-        <v>102</v>
-      </c>
-      <c r="O66" s="32">
-        <f>M66*N66</f>
-        <v>102</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="2" t="s">
+    </row>
+    <row r="69" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C69" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D67" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F67" s="5">
+      <c r="D69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F69" s="5">
         <v>3.56</v>
       </c>
-      <c r="G67" s="6">
-        <f t="shared" ref="G67" si="22">E67*F67</f>
+      <c r="G69" s="6">
+        <f t="shared" ref="G69" si="21">E69*F69</f>
         <v>3.56</v>
       </c>
-      <c r="J67" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="K67" s="66"/>
-      <c r="L67" s="66"/>
-      <c r="M67" s="66"/>
-      <c r="N67" s="67"/>
-      <c r="O67" s="33">
-        <f>SUM(O64:O66)</f>
-        <v>517</v>
-      </c>
-    </row>
-    <row r="68" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="2" t="s">
+      <c r="J69" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="K69" s="71" t="s">
+        <v>286</v>
+      </c>
+      <c r="L69" s="72"/>
+      <c r="M69" s="72"/>
+      <c r="N69" s="72"/>
+      <c r="O69" s="73"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C68" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F68" s="5">
+      <c r="C70" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F70" s="5">
         <v>6.69</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G70" s="6">
         <f t="shared" si="20"/>
         <v>6.69</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F69" s="5">
-        <v>27.76</v>
-      </c>
-      <c r="G69" s="6">
-        <f t="shared" si="16"/>
-        <v>27.76</v>
-      </c>
-      <c r="J69" s="34" t="s">
-        <v>296</v>
-      </c>
-      <c r="K69" s="72" t="s">
-        <v>294</v>
-      </c>
-      <c r="L69" s="73"/>
-      <c r="M69" s="73"/>
-      <c r="N69" s="73"/>
-      <c r="O69" s="74"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B70" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F70" s="5">
-        <v>15.31</v>
-      </c>
-      <c r="G70" s="6">
-        <f t="shared" si="16"/>
-        <v>15.31</v>
-      </c>
-      <c r="J70" s="48" t="s">
+      <c r="J70" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="K70" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="L70" s="49" t="s">
+      <c r="K70" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="L70" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="M70" s="49" t="s">
+      <c r="M70" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="N70" s="49" t="s">
+      <c r="N70" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="O70" s="50" t="s">
+      <c r="O70" s="49" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>9</v>
@@ -4774,27 +4607,27 @@
         <v>1</v>
       </c>
       <c r="F71" s="5">
-        <v>20</v>
+        <v>27.76</v>
       </c>
       <c r="G71" s="6">
-        <f t="shared" si="16"/>
-        <v>20</v>
-      </c>
-      <c r="J71" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="K71" s="76"/>
-      <c r="L71" s="76"/>
-      <c r="M71" s="76"/>
-      <c r="N71" s="76"/>
-      <c r="O71" s="77"/>
+        <f t="shared" si="15"/>
+        <v>27.76</v>
+      </c>
+      <c r="J71" s="74" t="s">
+        <v>285</v>
+      </c>
+      <c r="K71" s="75"/>
+      <c r="L71" s="75"/>
+      <c r="M71" s="75"/>
+      <c r="N71" s="75"/>
+      <c r="O71" s="76"/>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>9</v>
@@ -4804,17 +4637,17 @@
         <v>1</v>
       </c>
       <c r="F72" s="5">
-        <v>3.9</v>
+        <v>15.31</v>
       </c>
       <c r="G72" s="6">
-        <f t="shared" si="16"/>
-        <v>3.9</v>
+        <f t="shared" si="15"/>
+        <v>15.31</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="K72" s="12" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="L72" s="4" t="s">
         <v>9</v>
@@ -4826,251 +4659,251 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="O72" s="6">
-        <f t="shared" ref="O72:O76" si="23">M72*N72</f>
+        <f t="shared" ref="O72:O76" si="22">M72*N72</f>
         <v>34.799999999999997</v>
       </c>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F73" s="5">
+        <v>20</v>
+      </c>
+      <c r="G73" s="6">
+        <f t="shared" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K73" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M73" s="4">
+        <v>15</v>
+      </c>
+      <c r="N73" s="5">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="O73" s="6">
+        <f t="shared" si="22"/>
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F74" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="G74" s="6">
+        <f t="shared" si="15"/>
+        <v>3.9</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K74" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="L74" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M74" s="4">
+        <v>24</v>
+      </c>
+      <c r="N74" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="O74" s="6">
+        <f t="shared" si="22"/>
+        <v>42.96</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B75" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C75" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="20">
+      <c r="D75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="20">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F73" s="5">
+      <c r="F75" s="5">
         <v>2.34</v>
       </c>
-      <c r="G73" s="6">
-        <f t="shared" si="16"/>
+      <c r="G75" s="6">
+        <f t="shared" si="15"/>
         <v>4.68</v>
       </c>
-      <c r="J73" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="K73" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="L73" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M73" s="4">
+      <c r="J75" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="K75" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M75" s="4">
         <v>15</v>
       </c>
-      <c r="N73" s="5">
+      <c r="N75" s="5">
         <v>2.3199999999999998</v>
       </c>
-      <c r="O73" s="6">
-        <f t="shared" si="23"/>
+      <c r="O75" s="6">
+        <f t="shared" si="22"/>
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="74" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="2" t="s">
+    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B76" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C76" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="20">
+      <c r="D76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="20">
         <f>G2*3</f>
         <v>3</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F76" s="5">
         <v>2.34</v>
       </c>
-      <c r="G74" s="6">
-        <f t="shared" ref="G74:G80" si="24">E74*F74</f>
+      <c r="G76" s="6">
+        <f t="shared" ref="G76:G82" si="23">E76*F76</f>
         <v>7.02</v>
       </c>
-      <c r="J74" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="K74" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="L74" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M74" s="4">
+      <c r="J76" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="K76" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M76" s="4">
         <v>24</v>
       </c>
-      <c r="N74" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="O74" s="6">
-        <f t="shared" si="23"/>
-        <v>42.96</v>
-      </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B75" s="2" t="s">
+      <c r="N76" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="O76" s="6">
+        <f t="shared" si="22"/>
+        <v>26.64</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B77" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C77" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" s="20">
+      <c r="D77" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="20">
         <f>G2*3</f>
         <v>3</v>
       </c>
-      <c r="F75" s="5">
+      <c r="F77" s="5">
         <v>2.34</v>
       </c>
-      <c r="G75" s="6">
-        <f t="shared" si="24"/>
+      <c r="G77" s="6">
+        <f t="shared" si="23"/>
         <v>7.02</v>
       </c>
-      <c r="J75" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="K75" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="L75" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M75" s="4">
-        <v>15</v>
-      </c>
-      <c r="N75" s="5">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="O75" s="6">
-        <f t="shared" si="23"/>
-        <v>34.799999999999997</v>
-      </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B76" s="2" t="s">
+      <c r="J77" s="74" t="s">
+        <v>293</v>
+      </c>
+      <c r="K77" s="75"/>
+      <c r="L77" s="75"/>
+      <c r="M77" s="75"/>
+      <c r="N77" s="75"/>
+      <c r="O77" s="76"/>
+    </row>
+    <row r="78" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C78" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" s="20">
+      <c r="D78" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="20">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F78" s="5">
         <v>2.34</v>
       </c>
-      <c r="G76" s="6">
-        <f t="shared" si="24"/>
+      <c r="G78" s="6">
+        <f t="shared" si="23"/>
         <v>4.68</v>
       </c>
-      <c r="J76" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="K76" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M76" s="4">
-        <v>24</v>
-      </c>
-      <c r="N76" s="5">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="O76" s="6">
-        <f t="shared" si="23"/>
-        <v>26.64</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B77" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F77" s="5">
-        <v>23.68</v>
-      </c>
-      <c r="G77" s="6">
-        <f t="shared" si="24"/>
-        <v>23.68</v>
-      </c>
-      <c r="J77" s="75" t="s">
-        <v>301</v>
-      </c>
-      <c r="K77" s="76"/>
-      <c r="L77" s="76"/>
-      <c r="M77" s="76"/>
-      <c r="N77" s="76"/>
-      <c r="O77" s="77"/>
-    </row>
-    <row r="78" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F78" s="5">
-        <v>15.54</v>
-      </c>
-      <c r="G78" s="6">
-        <f t="shared" si="24"/>
-        <v>15.54</v>
-      </c>
       <c r="J78" s="16" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="L78" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M78" s="35">
+        <v>289</v>
+      </c>
+      <c r="L78" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M78" s="34">
         <v>15</v>
       </c>
-      <c r="N78" s="36">
+      <c r="N78" s="35">
         <v>2.5</v>
       </c>
-      <c r="O78" s="42">
+      <c r="O78" s="41">
         <f>M78*N78</f>
         <v>37.5</v>
       </c>
     </row>
     <row r="79" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>9</v>
@@ -5080,38 +4913,38 @@
         <v>1</v>
       </c>
       <c r="F79" s="5">
-        <v>4.79</v>
+        <v>23.68</v>
       </c>
       <c r="G79" s="6">
-        <f t="shared" si="24"/>
-        <v>4.79</v>
+        <f t="shared" si="23"/>
+        <v>23.68</v>
       </c>
       <c r="J79" s="16" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="L79" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M79" s="35">
+        <v>291</v>
+      </c>
+      <c r="L79" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M79" s="34">
         <v>8</v>
       </c>
-      <c r="N79" s="36">
+      <c r="N79" s="35">
         <v>14</v>
       </c>
-      <c r="O79" s="42">
+      <c r="O79" s="41">
         <f>M79*N79</f>
         <v>112</v>
       </c>
     </row>
     <row r="80" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>9</v>
@@ -5121,38 +4954,38 @@
         <v>1</v>
       </c>
       <c r="F80" s="5">
+        <v>15.54</v>
+      </c>
+      <c r="G80" s="6">
+        <f t="shared" si="23"/>
+        <v>15.54</v>
+      </c>
+      <c r="J80" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="L80" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M80" s="34">
         <v>8</v>
       </c>
-      <c r="G80" s="6">
-        <f t="shared" si="24"/>
-        <v>8</v>
-      </c>
-      <c r="J80" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="K80" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="L80" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M80" s="35">
-        <v>8</v>
-      </c>
-      <c r="N80" s="36">
+      <c r="N80" s="35">
         <v>11</v>
       </c>
-      <c r="O80" s="42">
+      <c r="O80" s="41">
         <f>M80*N80</f>
         <v>88</v>
       </c>
     </row>
     <row r="81" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="2" t="s">
-        <v>88</v>
+        <v>212</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>89</v>
+        <v>213</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>9</v>
@@ -5162,30 +4995,30 @@
         <v>1</v>
       </c>
       <c r="F81" s="5">
-        <v>3.64</v>
+        <v>4.79</v>
       </c>
       <c r="G81" s="6">
-        <f t="shared" si="16"/>
-        <v>3.64</v>
-      </c>
-      <c r="J81" s="65" t="s">
+        <f t="shared" si="23"/>
+        <v>4.79</v>
+      </c>
+      <c r="J81" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="K81" s="66"/>
-      <c r="L81" s="66"/>
-      <c r="M81" s="66"/>
-      <c r="N81" s="66"/>
-      <c r="O81" s="55">
+      <c r="K81" s="65"/>
+      <c r="L81" s="65"/>
+      <c r="M81" s="65"/>
+      <c r="N81" s="65"/>
+      <c r="O81" s="54">
         <f>SUM(O72:O80)</f>
         <v>411.5</v>
       </c>
     </row>
     <row r="82" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B82" s="2" t="s">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>91</v>
+        <v>211</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>9</v>
@@ -5195,19 +5028,19 @@
         <v>1</v>
       </c>
       <c r="F82" s="5">
-        <v>3.64</v>
+        <v>8</v>
       </c>
       <c r="G82" s="6">
-        <f t="shared" si="16"/>
-        <v>3.64</v>
+        <f t="shared" si="23"/>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B83" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>9</v>
@@ -5220,16 +5053,16 @@
         <v>3.64</v>
       </c>
       <c r="G83" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>3.64</v>
       </c>
     </row>
     <row r="84" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B84" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>9</v>
@@ -5242,16 +5075,16 @@
         <v>3.64</v>
       </c>
       <c r="G84" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>3.64</v>
       </c>
     </row>
     <row r="85" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B85" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>278</v>
+        <v>93</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>9</v>
@@ -5261,19 +5094,19 @@
         <v>1</v>
       </c>
       <c r="F85" s="5">
-        <v>15.26</v>
+        <v>3.64</v>
       </c>
       <c r="G85" s="6">
-        <f t="shared" si="16"/>
-        <v>15.26</v>
+        <f t="shared" si="15"/>
+        <v>3.64</v>
       </c>
     </row>
     <row r="86" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B86" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>9</v>
@@ -5283,19 +5116,19 @@
         <v>1</v>
       </c>
       <c r="F86" s="5">
-        <v>8.16</v>
+        <v>3.64</v>
       </c>
       <c r="G86" s="6">
-        <f t="shared" si="16"/>
-        <v>8.16</v>
+        <f t="shared" si="15"/>
+        <v>3.64</v>
       </c>
     </row>
     <row r="87" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B87" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>100</v>
+        <v>271</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>9</v>
@@ -5305,19 +5138,19 @@
         <v>1</v>
       </c>
       <c r="F87" s="5">
-        <v>8.16</v>
+        <v>15.26</v>
       </c>
       <c r="G87" s="6">
-        <f t="shared" si="16"/>
-        <v>8.16</v>
+        <f t="shared" si="15"/>
+        <v>15.26</v>
       </c>
     </row>
     <row r="88" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B88" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>9</v>
@@ -5330,267 +5163,309 @@
         <v>8.16</v>
       </c>
       <c r="G88" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>8.16</v>
       </c>
     </row>
-    <row r="89" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="16" t="s">
+    <row r="89" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B89" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F89" s="5">
+        <v>8.16</v>
+      </c>
+      <c r="G89" s="6">
+        <f t="shared" si="15"/>
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="90" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B90" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F90" s="5">
+        <v>8.16</v>
+      </c>
+      <c r="G90" s="6">
+        <f t="shared" si="15"/>
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="91" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C89" s="22" t="s">
+      <c r="C91" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D89" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" s="37">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F89" s="36">
+      <c r="D91" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="36">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F91" s="35">
         <v>85.17</v>
       </c>
-      <c r="G89" s="38">
-        <f>E89*F89</f>
+      <c r="G91" s="37">
+        <f>E91*F91</f>
         <v>85.17</v>
       </c>
     </row>
-    <row r="90" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="62" t="s">
-        <v>271</v>
-      </c>
-      <c r="C90" s="63"/>
-      <c r="D90" s="63"/>
-      <c r="E90" s="63"/>
-      <c r="F90" s="63"/>
-      <c r="G90" s="64"/>
-    </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B91" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="C91" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="D91" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" s="37">
+    <row r="92" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="C92" s="62"/>
+      <c r="D92" s="62"/>
+      <c r="E92" s="62"/>
+      <c r="F92" s="62"/>
+      <c r="G92" s="63"/>
+    </row>
+    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B93" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="C93" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D93" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="36">
         <f>G2*8</f>
         <v>8</v>
       </c>
-      <c r="F91" s="36">
+      <c r="F93" s="35">
         <v>9.07</v>
       </c>
-      <c r="G91" s="38">
-        <f>E91*F91</f>
+      <c r="G93" s="37">
+        <f>E93*F93</f>
         <v>72.56</v>
       </c>
     </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B92" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C92" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="D92" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="37">
+    <row r="94" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B94" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C94" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D94" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="36">
         <f>G2*4</f>
         <v>4</v>
       </c>
-      <c r="F92" s="36">
+      <c r="F94" s="35">
         <v>9.49</v>
       </c>
-      <c r="G92" s="38">
-        <f>E92*F92</f>
+      <c r="G94" s="37">
+        <f>E94*F94</f>
         <v>37.96</v>
       </c>
     </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B93" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="C93" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="D93" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="37">
+    <row r="95" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B95" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="C95" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D95" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="36">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F93" s="36">
+      <c r="F95" s="35">
         <v>9.0399999999999991</v>
       </c>
-      <c r="G93" s="38">
-        <f>E93*F93</f>
+      <c r="G95" s="37">
+        <f>E95*F95</f>
         <v>18.079999999999998</v>
       </c>
     </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B94" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="C94" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="D94" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E94" s="37">
+    <row r="96" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B96" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D96" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="36">
         <f>G2*2</f>
         <v>2</v>
       </c>
-      <c r="F94" s="36">
+      <c r="F96" s="35">
         <v>8.6300000000000008</v>
       </c>
-      <c r="G94" s="38">
-        <f>E94*F94</f>
+      <c r="G96" s="37">
+        <f>E96*F96</f>
         <v>17.260000000000002</v>
       </c>
     </row>
-    <row r="95" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="C95" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="D95" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="37">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F95" s="36">
+    <row r="97" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B97" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="D97" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="36">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F97" s="35">
         <v>28.24</v>
       </c>
-      <c r="G95" s="38">
-        <f>E95*F95</f>
+      <c r="G97" s="37">
+        <f>E97*F97</f>
         <v>28.24</v>
       </c>
     </row>
-    <row r="96" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="62" t="s">
-        <v>317</v>
-      </c>
-      <c r="C96" s="63"/>
-      <c r="D96" s="63"/>
-      <c r="E96" s="63"/>
-      <c r="F96" s="63"/>
-      <c r="G96" s="64"/>
-    </row>
-    <row r="97" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B97" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E97" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F97" s="5">
-        <v>20.9</v>
-      </c>
-      <c r="G97" s="6">
-        <f>E97*F97</f>
-        <v>20.9</v>
-      </c>
-    </row>
     <row r="98" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="62" t="s">
-        <v>247</v>
-      </c>
-      <c r="C98" s="63"/>
-      <c r="D98" s="63"/>
-      <c r="E98" s="63"/>
-      <c r="F98" s="63"/>
-      <c r="G98" s="64"/>
+      <c r="B98" s="61" t="s">
+        <v>308</v>
+      </c>
+      <c r="C98" s="62"/>
+      <c r="D98" s="62"/>
+      <c r="E98" s="62"/>
+      <c r="F98" s="62"/>
+      <c r="G98" s="63"/>
     </row>
     <row r="99" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>232</v>
+        <v>248</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>307</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="20">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F99" s="5">
+        <v>20.9</v>
+      </c>
+      <c r="G99" s="6">
+        <f>E99*F99</f>
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="61" t="s">
+        <v>243</v>
+      </c>
+      <c r="C100" s="62"/>
+      <c r="D100" s="62"/>
+      <c r="E100" s="62"/>
+      <c r="F100" s="62"/>
+      <c r="G100" s="63"/>
+    </row>
+    <row r="101" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B101" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E99" s="46">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F99" s="5">
+      <c r="E101" s="45">
+        <f>G2*1</f>
+        <v>1</v>
+      </c>
+      <c r="F101" s="5">
         <v>30.21</v>
       </c>
-      <c r="G99" s="40">
-        <f t="shared" si="16"/>
+      <c r="G101" s="39">
+        <f t="shared" si="15"/>
         <v>30.21</v>
       </c>
     </row>
-    <row r="100" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="56" t="s">
-        <v>287</v>
-      </c>
-      <c r="C100" s="57"/>
-      <c r="D100" s="57"/>
-      <c r="E100" s="57"/>
-      <c r="F100" s="58"/>
-      <c r="G100" s="21">
-        <f>SUM(G5:G99)</f>
-        <v>2376.7359999999994</v>
-      </c>
-    </row>
-    <row r="101" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="56" t="s">
-        <v>288</v>
-      </c>
-      <c r="C101" s="57"/>
-      <c r="D101" s="57"/>
-      <c r="E101" s="57"/>
-      <c r="F101" s="58"/>
-      <c r="G101" s="53">
-        <f>(SUM(G5:G99))/G2</f>
-        <v>2376.7359999999994</v>
-      </c>
-    </row>
     <row r="102" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="C102" s="57"/>
-      <c r="D102" s="57"/>
-      <c r="E102" s="57"/>
-      <c r="F102" s="58"/>
-      <c r="G102" s="54">
-        <f>G101+O67</f>
-        <v>2893.7359999999994</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G105" s="52"/>
+      <c r="B102" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="C102" s="56"/>
+      <c r="D102" s="56"/>
+      <c r="E102" s="56"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="21">
+        <f>SUM(G5:G101)</f>
+        <v>2540.4259999999981</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B103" s="55" t="s">
+        <v>280</v>
+      </c>
+      <c r="C103" s="56"/>
+      <c r="D103" s="56"/>
+      <c r="E103" s="56"/>
+      <c r="F103" s="57"/>
+      <c r="G103" s="52">
+        <f>(SUM(G5:G101))/G2</f>
+        <v>2540.4259999999981</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="55" t="s">
+        <v>270</v>
+      </c>
+      <c r="C104" s="56"/>
+      <c r="D104" s="56"/>
+      <c r="E104" s="56"/>
+      <c r="F104" s="57"/>
+      <c r="G104" s="53">
+        <f>G103+O67</f>
+        <v>3057.4259999999981</v>
+      </c>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="I107" s="52"/>
+      <c r="G107" s="51"/>
+      <c r="I107" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="32">
     <mergeCell ref="K2:O2"/>
-    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="B92:G92"/>
     <mergeCell ref="J67:N67"/>
-    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B103:F103"/>
     <mergeCell ref="J49:N49"/>
     <mergeCell ref="J53:O53"/>
     <mergeCell ref="J55:O55"/>
@@ -5602,19 +5477,19 @@
     <mergeCell ref="K51:O51"/>
     <mergeCell ref="K38:O38"/>
     <mergeCell ref="J77:O77"/>
-    <mergeCell ref="B96:G96"/>
+    <mergeCell ref="B98:G98"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="D2:F2"/>
     <mergeCell ref="B102:F102"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="B100:F100"/>
     <mergeCell ref="J4:O4"/>
     <mergeCell ref="J21:O21"/>
     <mergeCell ref="J26:O26"/>
     <mergeCell ref="J36:N36"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B44:G44"/>
     <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B98:G98"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B100:G100"/>
     <mergeCell ref="J40:O40"/>
     <mergeCell ref="J46:O46"/>
     <mergeCell ref="J63:O63"/>
@@ -5623,13 +5498,13 @@
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{182E6AD4-2BF8-453D-8168-0C5471656634}"/>
     <hyperlink ref="C16" r:id="rId2" xr:uid="{C0F4C0B5-36EF-43C3-B339-AACD5F5C72D4}"/>
-    <hyperlink ref="C48" r:id="rId3" xr:uid="{4723D3D0-CD4D-4359-8424-14CD9D28018C}"/>
+    <hyperlink ref="C50" r:id="rId3" xr:uid="{4723D3D0-CD4D-4359-8424-14CD9D28018C}"/>
     <hyperlink ref="C13" r:id="rId4" xr:uid="{7199B3E1-AB52-4D30-8183-99799A857909}"/>
-    <hyperlink ref="C52" r:id="rId5" xr:uid="{EFD4686C-AD95-420F-B095-B339D96CC0D7}"/>
+    <hyperlink ref="C54" r:id="rId5" xr:uid="{EFD4686C-AD95-420F-B095-B339D96CC0D7}"/>
     <hyperlink ref="C24" r:id="rId6" xr:uid="{5BD6981B-839D-4A2C-87F6-A3A00277C1E1}"/>
     <hyperlink ref="C25" r:id="rId7" xr:uid="{83DDA003-7213-4872-9D45-C4AF554BCA16}"/>
     <hyperlink ref="C27" r:id="rId8" display="https://www.amazon.com/AccusizeTools-Precision-Screwless-Hardened-0235-0303/dp/B00UCHGLUO/ref=sr_1_4?crid=WNIAUY5BPIE9&amp;dib=eyJ2IjoiMSJ9.Alni0qKZidsPooyk9GGkscfUQZ9tprkI4ET4wZoa_sbmUZzmmHVhxG7QmPDJX0AgSAHOykns84uDryc6E7grIuMWH375GMdVZCsMAZ8LQWFZfsy0ap0IiyiakunP6-_Y_ZcDHD9KuT9yk_DQjq9f6gKLk67aPwlGKsH16OBIZkb21bcZCjyEa7uJSWibaAc10B_8EIUViXEP_aCH2N7ITGBqK5oE8fgWj9yQaBwlw3DGARF2vyT4HE9hjWenKAVNJo79vmFegHMaPvq3QdGLRmFHCoGTuR7VlvFRIoLSNQs.7Kq1hNBbhFLTD57n8wr2lu-XKNLhMjGU5tZpFHisrPo&amp;dib_tag=se&amp;keywords=tool+maker+vice&amp;qid=1730493392&amp;sprefix=tool+maker+vice%2Caps%2C116&amp;sr=8-4" xr:uid="{4D66E69B-DE62-4D72-8B93-7F2E10874F91}"/>
-    <hyperlink ref="C51" r:id="rId9" xr:uid="{195A8F65-5906-4CC2-8230-372547AF30BC}"/>
+    <hyperlink ref="C53" r:id="rId9" xr:uid="{195A8F65-5906-4CC2-8230-372547AF30BC}"/>
     <hyperlink ref="C12" r:id="rId10" xr:uid="{68F00171-2727-43C8-B806-6B84C0184221}"/>
     <hyperlink ref="C11" r:id="rId11" location="customerReviews" xr:uid="{1A30128C-4F39-476D-97A8-AD250362EF88}"/>
     <hyperlink ref="K6" r:id="rId12" display="https://www.amazon.com/Fidioto-Terminals-Connector-Insulated-Industrial/dp/B09XQN3J6N/ref=sr_1_4?crid=9H73LST8YIJ5&amp;dib=eyJ2IjoiMSJ9.4GqBP1GBFaFPA0ydu3pf4E3drhrQBaiW09s5HBTixU2FjpaI-lQCi05VuNttif5SPyO5YPMQmiMI-Ln0MgmDooCOP2eZFsGw34JeesE9saSZOv5prr2QOuSwWgN7ynmhHAEYIJ6rP0v3XZOHMXrilaL9CJsYk1y2eURr1MMMAhbgUoFnWKVdPCzgToUNb0MRAeHQXIr7ACGFcGoEVjd41Ivpp40V3XA73Tx9HJAH-hM0laKEit0D2ZIkjTH3O1SpLc4K0_0SeSSXBSoAnNmqBXvG80iOUVvPuEP2oq_QBik.b-Wv2CuNpmfovLWKkfygBpQaQ9DDjyppvviR9L2qfRw&amp;dib_tag=se&amp;keywords=ferrule+connectors&amp;qid=1712253462&amp;s=industrial&amp;sprefix=ferr%2Cindustrial%2C158&amp;sr=1-4" xr:uid="{505E1876-1438-44B0-8CE3-B5857B28634C}"/>
@@ -5639,46 +5514,46 @@
     <hyperlink ref="C21" r:id="rId16" xr:uid="{BA6B4435-5F59-4C51-B877-F6D2850A5686}"/>
     <hyperlink ref="C20" r:id="rId17" xr:uid="{A44AC21F-D9EC-4BA8-8CB3-CDF163864C7A}"/>
     <hyperlink ref="C26" r:id="rId18" xr:uid="{3ACBC04B-80B5-483C-B223-DCC06D04EB43}"/>
-    <hyperlink ref="C47" r:id="rId19" xr:uid="{AB2A0A29-8665-4F12-85CA-729F9AEF1954}"/>
-    <hyperlink ref="C53" r:id="rId20" xr:uid="{DF72ED0E-A6AE-405C-A831-47EAF4A0978E}"/>
+    <hyperlink ref="C49" r:id="rId19" xr:uid="{AB2A0A29-8665-4F12-85CA-729F9AEF1954}"/>
+    <hyperlink ref="C55" r:id="rId20" xr:uid="{DF72ED0E-A6AE-405C-A831-47EAF4A0978E}"/>
     <hyperlink ref="C29" r:id="rId21" xr:uid="{3D2201C7-6C8A-4773-B48C-DEC55AB9CE5D}"/>
     <hyperlink ref="C28" r:id="rId22" xr:uid="{A7E3198B-4B0E-463C-BC5D-907882FF4F1D}"/>
     <hyperlink ref="C31" r:id="rId23" display="https://www.amazon.com/TYUMEN-Hookup-Electrical-Strips-Extension/dp/B07SLBD1FY?crid=3DSOPLHQPDC41&amp;dib=eyJ2IjoiMSJ9.LbfmNeaOMKQc2NnauqoG3ikk9ANZN_ur4lUWCOCW1O50UvTYKXmiV3AA8Ril1fLOmFRcVVCi_eXXhqwFcZtIW8vmaESTdy6oz8DZxn_URYzZU9OQiHvftwQ3KnaAl6ba-cfRNhMbR7Fpx7tqwarEMqmVU0t2BYcH56emRvXvgV1aTOFyjOYBpkeQMF4SwuInBmgz7WD_t5spHjwSbDYPmshu2rmE36AdUCByV1ie631jZjWBFXP_gl822MkqR8EixD-piO5IZ22jBqlSbpf0TcMJdhRwDpP5zuWzH47ITPk.AI3vrrrkl4uXviMH51NrHs3QtR7dKc_HTTFAhHq9paA&amp;dib_tag=se&amp;keywords=22+awg+wire&amp;qid=1733387088&amp;s=industrial&amp;sprefix=22+awg%2Cindustrial%2C149&amp;sr=1-8" xr:uid="{E82B0C83-0745-457F-853F-CF7C98A9BBAF}"/>
     <hyperlink ref="K18" r:id="rId24" display="https://www.amazon.com/HUAREW-Values-Ferrite-Suppressor-Diameter/dp/B09SWNPY2Y?crid=25SF4JZN6UMCO&amp;dib=eyJ2IjoiMSJ9.BECN3Z-pnF_DHO20UYNRh-xF2WQPuabKc-oibkz7-5pf-LFqEqaxgUTsjAY9NMHye5H2wuD5X3xZHc2XF6v_ZmAzcFy34lVzkGSEseb_JQsXhQ_lHx78wyV8_2Bl5O2FXq_OPNVVnus4XAq2V7L8dtacsFGCRlHZwgnYlurEB2URoEWdU24JZSoJOdjnTKoB-Nm2-vu6eTFFOKyg0bYDhkvLpIooINxXg8mYy1zuu90.aHjsj2UYUYYX1n4w2EmKBChz9hsqz6bpyNaSrZmD_Pc&amp;dib_tag=se&amp;keywords=ferrite%2Bcore%2Bbead&amp;qid=1733391188&amp;sprefix=ferrite%2Bcore%2Bbead%2Caps%2C148&amp;sr=8-3&amp;th=1 " xr:uid="{3624AB78-BD37-43C7-ABBC-ABDD2D49F1BD}"/>
-    <hyperlink ref="C54" r:id="rId25" xr:uid="{32DB5FB3-622F-4B80-98A2-9D63982309B9}"/>
-    <hyperlink ref="C70" r:id="rId26" xr:uid="{E95793D2-E192-4066-88A4-5B88C4EB6441}"/>
-    <hyperlink ref="C69" r:id="rId27" xr:uid="{89E89EFA-A33B-49E7-9CA3-3AA3F3B2419C}"/>
-    <hyperlink ref="C81" r:id="rId28" xr:uid="{C0887221-10A6-49C9-9592-F29719AB1146}"/>
-    <hyperlink ref="C82" r:id="rId29" xr:uid="{5D432ACC-1036-40C7-BAF5-8E7A9DEE269C}"/>
-    <hyperlink ref="C83" r:id="rId30" xr:uid="{373A1D9B-E52A-4919-BF46-F0054AD0383E}"/>
-    <hyperlink ref="C84" r:id="rId31" xr:uid="{67F0F7A2-8F53-4145-AE23-1984596864D2}"/>
-    <hyperlink ref="C86" r:id="rId32" xr:uid="{0AE9CA58-FE72-4AAA-B4AE-ED28FC16E141}"/>
-    <hyperlink ref="C87" r:id="rId33" xr:uid="{649DFB24-658E-46D9-8DD3-8968123090EE}"/>
-    <hyperlink ref="C88" r:id="rId34" xr:uid="{41AC74BE-2B55-4941-9CA1-1FB8B496080B}"/>
-    <hyperlink ref="C89" r:id="rId35" xr:uid="{673DF358-F6E2-431B-8C25-0F1712C2A5BE}"/>
+    <hyperlink ref="C56" r:id="rId25" xr:uid="{32DB5FB3-622F-4B80-98A2-9D63982309B9}"/>
+    <hyperlink ref="C72" r:id="rId26" xr:uid="{E95793D2-E192-4066-88A4-5B88C4EB6441}"/>
+    <hyperlink ref="C71" r:id="rId27" xr:uid="{89E89EFA-A33B-49E7-9CA3-3AA3F3B2419C}"/>
+    <hyperlink ref="C83" r:id="rId28" xr:uid="{C0887221-10A6-49C9-9592-F29719AB1146}"/>
+    <hyperlink ref="C84" r:id="rId29" xr:uid="{5D432ACC-1036-40C7-BAF5-8E7A9DEE269C}"/>
+    <hyperlink ref="C85" r:id="rId30" xr:uid="{373A1D9B-E52A-4919-BF46-F0054AD0383E}"/>
+    <hyperlink ref="C86" r:id="rId31" xr:uid="{67F0F7A2-8F53-4145-AE23-1984596864D2}"/>
+    <hyperlink ref="C88" r:id="rId32" xr:uid="{0AE9CA58-FE72-4AAA-B4AE-ED28FC16E141}"/>
+    <hyperlink ref="C89" r:id="rId33" xr:uid="{649DFB24-658E-46D9-8DD3-8968123090EE}"/>
+    <hyperlink ref="C90" r:id="rId34" xr:uid="{41AC74BE-2B55-4941-9CA1-1FB8B496080B}"/>
+    <hyperlink ref="C91" r:id="rId35" xr:uid="{673DF358-F6E2-431B-8C25-0F1712C2A5BE}"/>
     <hyperlink ref="K35" r:id="rId36" xr:uid="{F7DD1C65-60DD-46DD-9FE7-6744F8BA03E7}"/>
-    <hyperlink ref="C57" r:id="rId37" xr:uid="{EF358443-AF57-40E1-92E1-8BF6DD299077}"/>
-    <hyperlink ref="C59" r:id="rId38" xr:uid="{12762096-DC6B-44F2-8ADB-0F58C1B3AEEF}"/>
-    <hyperlink ref="C58" r:id="rId39" xr:uid="{3EFF0D79-73FC-4F62-B070-424FEA2B0998}"/>
-    <hyperlink ref="C61" r:id="rId40" xr:uid="{4C882C61-8A3D-4FF6-8AA2-3CFEBE6A8E31}"/>
-    <hyperlink ref="C55" r:id="rId41" xr:uid="{8C08A008-7728-44D3-BA67-48DB3EEFA7BB}"/>
-    <hyperlink ref="C63" r:id="rId42" xr:uid="{1E69FF1B-0FFD-4B85-B8D4-6662499D5EC6}"/>
-    <hyperlink ref="C65" r:id="rId43" xr:uid="{7C60CB7E-E2C1-46DC-BD3E-B770093F52D5}"/>
-    <hyperlink ref="C66" r:id="rId44" xr:uid="{3FB0574C-FDA6-4DB0-863A-DD9D050D7C39}"/>
-    <hyperlink ref="C56" r:id="rId45" xr:uid="{CFDEAC1B-A32C-4050-8273-2439C47581BB}"/>
-    <hyperlink ref="C60" r:id="rId46" xr:uid="{9A55F38E-8B5A-4A95-8F81-373F25553D76}"/>
-    <hyperlink ref="C62" r:id="rId47" xr:uid="{78F0AA91-375E-4C85-9A3E-A171D50577BA}"/>
+    <hyperlink ref="C59" r:id="rId37" xr:uid="{EF358443-AF57-40E1-92E1-8BF6DD299077}"/>
+    <hyperlink ref="C61" r:id="rId38" xr:uid="{12762096-DC6B-44F2-8ADB-0F58C1B3AEEF}"/>
+    <hyperlink ref="C60" r:id="rId39" xr:uid="{3EFF0D79-73FC-4F62-B070-424FEA2B0998}"/>
+    <hyperlink ref="C63" r:id="rId40" xr:uid="{4C882C61-8A3D-4FF6-8AA2-3CFEBE6A8E31}"/>
+    <hyperlink ref="C57" r:id="rId41" xr:uid="{8C08A008-7728-44D3-BA67-48DB3EEFA7BB}"/>
+    <hyperlink ref="C65" r:id="rId42" xr:uid="{1E69FF1B-0FFD-4B85-B8D4-6662499D5EC6}"/>
+    <hyperlink ref="C67" r:id="rId43" xr:uid="{7C60CB7E-E2C1-46DC-BD3E-B770093F52D5}"/>
+    <hyperlink ref="C68" r:id="rId44" xr:uid="{3FB0574C-FDA6-4DB0-863A-DD9D050D7C39}"/>
+    <hyperlink ref="C58" r:id="rId45" xr:uid="{CFDEAC1B-A32C-4050-8273-2439C47581BB}"/>
+    <hyperlink ref="C62" r:id="rId46" xr:uid="{9A55F38E-8B5A-4A95-8F81-373F25553D76}"/>
+    <hyperlink ref="C64" r:id="rId47" xr:uid="{78F0AA91-375E-4C85-9A3E-A171D50577BA}"/>
     <hyperlink ref="C6" r:id="rId48" xr:uid="{AED92118-DDB2-4EF3-AC67-4C4C07E0C841}"/>
     <hyperlink ref="C9" r:id="rId49" xr:uid="{FE9C3C2A-AF4A-4E14-BBDB-335DF3BC0F13}"/>
     <hyperlink ref="C18" r:id="rId50" xr:uid="{94451722-66BC-4F98-8B43-3E0FC394E5EA}"/>
     <hyperlink ref="C23" r:id="rId51" xr:uid="{8B80B60C-F876-4871-8577-DC9ACEA588AC}"/>
     <hyperlink ref="C30" r:id="rId52" xr:uid="{0492A76A-498E-4001-829F-D792C40ACDBA}"/>
-    <hyperlink ref="C50" r:id="rId53" xr:uid="{D6C0DDCE-AD68-4B51-98DF-B171BC702B91}"/>
-    <hyperlink ref="C67" r:id="rId54" xr:uid="{68484166-BD87-4E39-9BD4-46B04DB0A082}"/>
+    <hyperlink ref="C52" r:id="rId53" xr:uid="{D6C0DDCE-AD68-4B51-98DF-B171BC702B91}"/>
+    <hyperlink ref="C69" r:id="rId54" xr:uid="{68484166-BD87-4E39-9BD4-46B04DB0A082}"/>
     <hyperlink ref="C38" r:id="rId55" display="https://www.amazon.com/Universal-Regulated-Switching-Converter-Transformer/dp/B07PPPF1R5/ref=sr_1_6?dib=eyJ2IjoiMSJ9.ghI_8NCu8MWYClVH1bcXae0-G1NHsVMPKXgQ-q9tD7DBjxsd-n2e4GXZyzhj32lWCmUMKNTvmGLgthtkozNnkvRJfBHn4VuSCeTc5lP748T7kJtgdQqg9MH80QXTBMNWupAT-RBnmpw_wBXBO26SKIbj1k64fqcpbisodWHH80xxJPdJFOijPa1IA51xm60Wi2aU2vCne6MmqM3RncHLRYr931SD1UNb9aMjXyOF6U4.dija8_tU-NIlFsudkA1tvV6C6mk8gUO-_lwM8li1rMY&amp;dib_tag=se&amp;keywords=5v%2Bpower%2Bsupply&amp;qid=1743186298&amp;sr=8-6&amp;th=1 " xr:uid="{88BB23CD-312A-41E1-B370-C0D92A466099}"/>
     <hyperlink ref="C32" r:id="rId56" display="https://www.amazon.com/HiLetgo-Channels-Converter-Bi-Directional-3-3V-5V/dp/B07F7W91LC/ref=sr_1_2?crid=2O7B6QA8ZSPZK&amp;dib=eyJ2IjoiMSJ9.hg1xpaR1IOVH3e6fV4tFyZB8elQluWDLIScr-WIbHEosPLIRhqXG5AnMJTwgM0K6TrBGR457D8AftNCas1RwwWglHyp8zMGTpS2Jwm4xa_uAl0aEMGjby7ffGvEP4lloYctRt9gX4TE3gjllm6sYLU-fsW7zpvcw5ZYESHBPOBCKcQrbrqb3arWPwpjMs7PwokFja-obLRKIr-SuthVfiG0yGem5Rc41xB6eDkr3AZehwq0tgYmv9VxxVa-jlxf9M9Jmhd8G9HvRemxc8IltnV6CNWKiDi1dgnDBhhj15Hs.b7q4qr8rSADKOOdi-2C89QYAixVQ_S86lTmLM2WBijs&amp;dib_tag=se&amp;keywords=logic+converter&amp;qid=1732221329&amp;s=industrial&amp;sprefix=logic+convertyer%2Cindustrial%2C103&amp;sr=1-2" xr:uid="{AA94D625-0126-47B8-979E-9BE236BAD9AD}"/>
     <hyperlink ref="K17" r:id="rId57" xr:uid="{0F474C1B-53F3-45D5-A2EC-5FEABEC629CC}"/>
-    <hyperlink ref="C45" r:id="rId58" display="https://www.digikey.com/en/products/detail/w-rth-elektronik/691210910002/10668428?gclsrc=aw.ds&amp;&amp;utm_adgroup=&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=PMax%20Supplier_Focus%20Supplier&amp;utm_term=&amp;utm_content=&amp;utm_id=go_cmp-20243063242_adg-_ad-__dev-c_ext-_prd-10668428_sig-CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gad_source=1&amp;gclid=CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gclsrc=aw.ds " xr:uid="{DCE5683A-0BC1-49BA-8FB0-36DC1C1C9A9C}"/>
+    <hyperlink ref="C47" r:id="rId58" display="https://www.digikey.com/en/products/detail/w-rth-elektronik/691210910002/10668428?gclsrc=aw.ds&amp;&amp;utm_adgroup=&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=PMax%20Supplier_Focus%20Supplier&amp;utm_term=&amp;utm_content=&amp;utm_id=go_cmp-20243063242_adg-_ad-__dev-c_ext-_prd-10668428_sig-CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gad_source=1&amp;gclid=CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gclsrc=aw.ds " xr:uid="{DCE5683A-0BC1-49BA-8FB0-36DC1C1C9A9C}"/>
     <hyperlink ref="C34" r:id="rId59" xr:uid="{A29FBA48-6899-42FA-AA59-0FC1E2A5A45B}"/>
     <hyperlink ref="K5" r:id="rId60" display="https://www.amazon.com/Klein-Tools-34056-Adjustable-Electrical/dp/B0D98N52HS/ref=sr_1_1?crid=2OB42YRNYW5S8&amp;dib=eyJ2IjoiMSJ9.55eyclIvGQBRs_G9kszoUlEHRgUtyYkcxabPk-sLw5mt7xuGNeudbfTW8xclKppzTejqidNByQBdPqeEXGg2aJrgDuRoxPddnr7un1KzGrHylGN5yiKL4ycDLAz23bHXFS35VarXoP5Hhq810Sdco6qhSeWGVplSUIYpl56zvRZNrenZvPGmvYU7Y6nsIMihDbf5RoNPi8sUcALPKWZoFyR-Fs3jx2RBJISOeui_PdRPNKnGLGC0Uz395rIEcZ1F9icIwzDBX00JzMC1ZjD_KvEf_nXltgLaawa8vee6Efs.PDGEHgTlQjY0Jz82g_64nVgHTsayEsuiw1VPN9n4cXc&amp;dib_tag=se&amp;keywords=klein%2Bferrule%2Bcrimper&amp;qid=1730823384&amp;sprefix=klein%2Bferrule%2Bcrimper%2Caps%2C132&amp;sr=8-1&amp;th=1 " xr:uid="{CEBE3ECF-00C1-476F-B5EA-6B34F3C440E0}"/>
     <hyperlink ref="K9" r:id="rId61" display="https://www.amazon.com/Ginsco-580-pcs-Assorted-Sleeving/dp/B01MFA3OFA/ref=sr_1_3?crid=19V7T4IBHC5QO&amp;dib=eyJ2IjoiMSJ9.afAtOFc0AWv7IewHnY-SsmFPIWDeFgvxv7nXELH8Q5qH5K9drWIEjyb4PZCDtpgcSjO1zJt_d_d3Bzwc58g899uhvXzTWNoWa7P0XxuvXztW-5Tc85nP2v3ZP7OVkL9CptCT1e2fAdSg9fifPtR8m9aUVniGOD_xVLXrYdiBq6lh_RbbHkqSMJ69bG3sHk4HbEXsrxggq5C19I64px1H3_Ik8TcJWmowUEtAS4Q9W-qfDLzF-ZeqrhVHbQsdU60_CMcyHcb-SzXuOkdEyVk4hxnhYPkE9DVIFlnwUZ_gnFs.KYnfl9oSznG3OdVCEMra_IGu5ndQOaOh0V01hKDX2Cg&amp;dib_tag=se&amp;keywords=heat+shrink&amp;qid=1730826521&amp;s=industrial&amp;sprefix=heat+shrink%2Cindustrial%2C153&amp;sr=1-3" xr:uid="{332F4161-5937-4DDE-ABA6-DACEB1F4794A}"/>
@@ -5702,14 +5577,14 @@
     <hyperlink ref="K28" r:id="rId79" xr:uid="{5F7730D8-6AC1-4AFC-BDF9-357875FD1123}"/>
     <hyperlink ref="K29" r:id="rId80" xr:uid="{7D645F8A-33CD-418D-8D23-F32705DFD52D}"/>
     <hyperlink ref="K32" r:id="rId81" xr:uid="{72352CC7-698C-4AF0-BCF4-715EF6461852}"/>
-    <hyperlink ref="C74" r:id="rId82" xr:uid="{D0BFB25A-21DF-4F2E-8B59-E3DD05C3B098}"/>
-    <hyperlink ref="C73" r:id="rId83" xr:uid="{D5A5F088-A84E-4368-83A3-93B6A7392B62}"/>
-    <hyperlink ref="C75" r:id="rId84" xr:uid="{03C53325-8F52-47AD-98AA-5B3BD79FCDF7}"/>
-    <hyperlink ref="C76" r:id="rId85" xr:uid="{BC613FBE-2FF7-47F4-BA8F-9A2B780CBF4D}"/>
-    <hyperlink ref="C77" r:id="rId86" xr:uid="{18524F55-8313-44A2-98E0-8D3476379625}"/>
-    <hyperlink ref="C78" r:id="rId87" xr:uid="{C5B457D0-EBF2-4473-8DE5-A2CBF0192FC7}"/>
-    <hyperlink ref="C80" r:id="rId88" xr:uid="{E9EBC0D2-18CA-4009-92BF-AA4627474036}"/>
-    <hyperlink ref="C79" r:id="rId89" xr:uid="{F9DC2B0F-6CC2-4333-B6A0-4C461C26A42D}"/>
+    <hyperlink ref="C76" r:id="rId82" xr:uid="{D0BFB25A-21DF-4F2E-8B59-E3DD05C3B098}"/>
+    <hyperlink ref="C75" r:id="rId83" xr:uid="{D5A5F088-A84E-4368-83A3-93B6A7392B62}"/>
+    <hyperlink ref="C77" r:id="rId84" xr:uid="{03C53325-8F52-47AD-98AA-5B3BD79FCDF7}"/>
+    <hyperlink ref="C78" r:id="rId85" xr:uid="{BC613FBE-2FF7-47F4-BA8F-9A2B780CBF4D}"/>
+    <hyperlink ref="C79" r:id="rId86" xr:uid="{18524F55-8313-44A2-98E0-8D3476379625}"/>
+    <hyperlink ref="C80" r:id="rId87" xr:uid="{C5B457D0-EBF2-4473-8DE5-A2CBF0192FC7}"/>
+    <hyperlink ref="C82" r:id="rId88" xr:uid="{E9EBC0D2-18CA-4009-92BF-AA4627474036}"/>
+    <hyperlink ref="C81" r:id="rId89" xr:uid="{F9DC2B0F-6CC2-4333-B6A0-4C461C26A42D}"/>
     <hyperlink ref="C35" r:id="rId90" xr:uid="{B350E38A-0704-49E3-B0A0-6AC64705FFA8}"/>
     <hyperlink ref="K24" r:id="rId91" xr:uid="{38DE31D1-83D2-44D7-B2DB-47B0912A74D8}"/>
     <hyperlink ref="K42" r:id="rId92" xr:uid="{99DE23E2-FB55-46E7-81C4-10D9C3F12704}"/>
@@ -5720,62 +5595,52 @@
     <hyperlink ref="K54" r:id="rId97" xr:uid="{08CDA0A7-76D0-4386-8DF9-D40020E4F6BB}"/>
     <hyperlink ref="K56" r:id="rId98" xr:uid="{B817C2C0-888A-41EE-BB96-AA202FF7D26F}"/>
     <hyperlink ref="K7" r:id="rId99" xr:uid="{403CBC77-BB8E-482D-ADB0-566010CFFBFE}"/>
-    <hyperlink ref="C39" r:id="rId100" display="https://www.amazon.com/Ethernet-Kit-for-Teensy-4-1/dp/B08CTM1L64/ref=sr_1_5?dib=eyJ2IjoiMSJ9.SbX6rnuR22BHW7UQV6IYcckSiyAyB1ZWr3cUVGCpjmoe8u9La0C4CnpYOniX7CwAfqWVpgmjNbJjLT76DhWe4ldG5P2p4WMYyJenE908txxUrz8DSqOHEjh3oVZE2stHV0rzuhfvuwF3CawGYaDmSg.85Xw8ylPJeTNJvqmoxZDt0Th8_d0wMGVyuH5z7GC-TU&amp;dib_tag=se&amp;qid=1752729706&amp;refinements=p_89%3APJRC&amp;sr=8-5&amp;srs=36931437011 " xr:uid="{E3DAB6D6-41C5-4F47-B4DE-A540D085825C}"/>
-    <hyperlink ref="C99" r:id="rId101" xr:uid="{66B61CB6-8DEE-47E0-8F58-13DFE696A594}"/>
-    <hyperlink ref="C19" r:id="rId102" xr:uid="{25851340-5A38-4A26-A3FC-843A61F946D3}"/>
-    <hyperlink ref="C43" r:id="rId103" xr:uid="{21E4C4A3-A6F2-4A9D-B5C5-679DA6006B33}"/>
-    <hyperlink ref="C41" r:id="rId104" xr:uid="{E912526C-B82A-4A44-8481-EFACD695EA8D}"/>
-    <hyperlink ref="C42" r:id="rId105" xr:uid="{E865141B-878A-4CD6-B122-3ADC6852D520}"/>
-    <hyperlink ref="K58" r:id="rId106" location="tabbed-customerreviews " xr:uid="{24F44932-6634-42FE-8337-20CA3C2EC1E4}"/>
-    <hyperlink ref="C72" r:id="rId107" xr:uid="{326567BB-9D82-4E92-ACC4-530A6BCCFC38}"/>
-    <hyperlink ref="C17" r:id="rId108" display="https://www.amazon.com/Amazon-Basics-Ethernet-High-Speed-Snagless/dp/B089MGH8W3/ref=sr_1_6?crid=15O99JJ9VZUDS&amp;dib=eyJ2IjoiMSJ9.Qrm0YFmTEww5DZc4mrTYoBW2ITYU8YDRmdb4HE4nmukqEngrlTfGgHLb5uoFzqyB8DY16yxmWqTI2jhY13tKSS_gVPXMFmLrV8CwN6seDqr3fe6RoYGbAYOThLs_GPXGD9BG1xBtpSbQCaOmPeX6onzLKT90VpHEp8g8rhIrccYIWeUVb1y9yQszCgP-aLtJNIsqNx1o-8aHQGBnXQxbEdINQFklL4UDCld4WzwhnXy0xN-YFaHdxcyM5kmfmoYQEhD8UEUeVcULGl7eYpTBQi8RxGrjeWwsXTnPG7oVA4s.SJ0prHAqUML_3kLplif-xyTccwFoBx4GiK1cGmdOyLI&amp;dib_tag=se&amp;keywords=ethernet%2Bcable&amp;qid=1752782277&amp;s=electronics&amp;sprefix=ethernet%2Celectronics%2C124&amp;sr=1-6&amp;th=1 " xr:uid="{83A0A177-ED38-4C3C-B1E2-6D1A2C00DD2C}"/>
-    <hyperlink ref="C10" r:id="rId109" xr:uid="{5EF2B5FA-9EB9-4ED3-A87B-DB000918746C}"/>
-    <hyperlink ref="K13" r:id="rId110" display="https://www.amazon.com/Powerbuilt-Piece-Stubby-Long-Wrench/dp/B07N8F7W7K/ref=sr_1_19?dib=eyJ2IjoiMSJ9.URwdEPQXxCMLBhxvS9K5ftG6hwdCaLy_xWZ0vGXOdbuaNrb8XAmO4DQhIxovkvuXsRHPo7oCqjy9Wwt6H6QvZeRYOqVzaLjKkETlnA83OkSSXLxlPpzMt1Qy3kJt-T7GsO_Bq0c0QItERYLb6VTtZmMQdlqDEtc5mdwZiAksW1Y2IKpS2cr-V_j1_L0qMFZKPy2WuoytvNj5MEhK80MOfMrjnaTsJLpB9Io2Jt4xFodm6EN5AwCetZhDdsJTY6jdeOdEdPi6COl5b1RI-6XJHwylh2H13M74HgAUrEaRfoY.bAaypnaW3mj6ulkwXEha2QJSRXBFsgrmQMhuIwb4S2o&amp;dib_tag=se&amp;keywords=stubby%2Ballen%2Bwrench%2Bset&amp;qid=1752911269&amp;sr=8-19&amp;th=1 " xr:uid="{F2200CD7-83CF-497A-91E0-EF5B6CA80C0C}"/>
-    <hyperlink ref="K44" r:id="rId111" xr:uid="{F40A70E6-7F31-454F-9558-A7291A2A2DCF}"/>
-    <hyperlink ref="K45" r:id="rId112" xr:uid="{4A6F6959-0930-44EE-A971-B3EF13DA9390}"/>
-    <hyperlink ref="C49" r:id="rId113" xr:uid="{7963F571-8F62-4D9F-BEF7-F802CD4D18FC}"/>
-    <hyperlink ref="C91" r:id="rId114" xr:uid="{5A200CB5-C655-478F-B00B-2E82D8CC5C77}"/>
-    <hyperlink ref="C92:C93" r:id="rId115" display="https://8020.net/20-2020.html " xr:uid="{94C82CF7-4209-49DE-A286-0E429370F935}"/>
-    <hyperlink ref="C94" r:id="rId116" xr:uid="{3653483D-B8D7-4970-8BE1-067F3CE7FF42}"/>
-    <hyperlink ref="C85" r:id="rId117" xr:uid="{E1AC3FAD-797D-4D40-89E1-E0B078028B08}"/>
-    <hyperlink ref="C64" r:id="rId118" xr:uid="{8B53B0C9-AEB9-4C25-B4D5-D709A9909BD6}"/>
-    <hyperlink ref="C68" r:id="rId119" xr:uid="{2521E3A3-9809-485D-8952-C732415A0425}"/>
-    <hyperlink ref="K41" r:id="rId120" xr:uid="{BE5F57C8-C44E-47CF-B992-FEB02C6C001F}"/>
-    <hyperlink ref="K72" r:id="rId121" xr:uid="{A8E5D7AD-E110-498C-AD66-4031E7159275}"/>
-    <hyperlink ref="K74" r:id="rId122" xr:uid="{686F1C5B-AD14-408B-9AF5-1B4D26D75248}"/>
-    <hyperlink ref="K78" r:id="rId123" xr:uid="{A8336809-C542-4E15-9187-DB4F43D26933}"/>
-    <hyperlink ref="K79" r:id="rId124" xr:uid="{49B9B422-CDDA-427C-82B9-729F2266C333}"/>
-    <hyperlink ref="K80" r:id="rId125" xr:uid="{3E0AC7C3-82FC-4B11-AD25-3DE1DD9499EF}"/>
-    <hyperlink ref="C95" r:id="rId126" xr:uid="{2C6B41AF-87E5-4DA5-9686-67EEDF628339}"/>
-    <hyperlink ref="C36" r:id="rId127" xr:uid="{1800FA32-51EA-41AB-8A1C-BCA281C1CA6B}"/>
-    <hyperlink ref="K75" r:id="rId128" xr:uid="{D1950805-AAE5-4A33-803E-9858D08F12A2}"/>
-    <hyperlink ref="K73" r:id="rId129" xr:uid="{01D963BB-A0C2-4C40-BA01-8B0B76381716}"/>
-    <hyperlink ref="K76" r:id="rId130" xr:uid="{D9B5F8EE-01B9-4AA5-9918-F987CA2D7884}"/>
-    <hyperlink ref="C97" r:id="rId131" display="https://czh-labs.com/products/terminal-block-breakout-board-module-for-teensy-41-screw-mount-version?gad_source=1&amp;gad_campaignid=17335691898&amp;gbraid=0AAAAADQKSWrLA97xSr9gmMM99UCSLmr58&amp;gclid=CjwKCAjwp_LDBhBCEiwAK7FnklUhjhvxFgmMMu0XiWu80nKxdv4QNWNVcUvZhioyk86weMe15LnzoRoClR4QAvD_BwE " xr:uid="{944A4911-F6CF-4EB3-82C2-8B8DAFBE56E9}"/>
-    <hyperlink ref="C37" r:id="rId132" xr:uid="{737F7509-05EB-4CE3-AA5B-929CB63FC161}"/>
-    <hyperlink ref="W16" r:id="rId133" xr:uid="{8B918A02-0CA6-4A4E-AA77-82C812145661}"/>
-    <hyperlink ref="W15" r:id="rId134" xr:uid="{1BBD1B38-BB9C-4FBE-A797-58DECC2562DA}"/>
-    <hyperlink ref="C8" r:id="rId135" xr:uid="{4755A74A-BAA1-4451-A83C-5F6302BF9DF2}"/>
+    <hyperlink ref="C101" r:id="rId100" xr:uid="{66B61CB6-8DEE-47E0-8F58-13DFE696A594}"/>
+    <hyperlink ref="C19" r:id="rId101" xr:uid="{25851340-5A38-4A26-A3FC-843A61F946D3}"/>
+    <hyperlink ref="C40" r:id="rId102" xr:uid="{E912526C-B82A-4A44-8481-EFACD695EA8D}"/>
+    <hyperlink ref="C44" r:id="rId103" xr:uid="{E865141B-878A-4CD6-B122-3ADC6852D520}"/>
+    <hyperlink ref="K58" r:id="rId104" location="tabbed-customerreviews " xr:uid="{24F44932-6634-42FE-8337-20CA3C2EC1E4}"/>
+    <hyperlink ref="C74" r:id="rId105" xr:uid="{326567BB-9D82-4E92-ACC4-530A6BCCFC38}"/>
+    <hyperlink ref="C17" r:id="rId106" display="https://www.amazon.com/Amazon-Basics-Ethernet-High-Speed-Snagless/dp/B089MGH8W3/ref=sr_1_6?crid=15O99JJ9VZUDS&amp;dib=eyJ2IjoiMSJ9.Qrm0YFmTEww5DZc4mrTYoBW2ITYU8YDRmdb4HE4nmukqEngrlTfGgHLb5uoFzqyB8DY16yxmWqTI2jhY13tKSS_gVPXMFmLrV8CwN6seDqr3fe6RoYGbAYOThLs_GPXGD9BG1xBtpSbQCaOmPeX6onzLKT90VpHEp8g8rhIrccYIWeUVb1y9yQszCgP-aLtJNIsqNx1o-8aHQGBnXQxbEdINQFklL4UDCld4WzwhnXy0xN-YFaHdxcyM5kmfmoYQEhD8UEUeVcULGl7eYpTBQi8RxGrjeWwsXTnPG7oVA4s.SJ0prHAqUML_3kLplif-xyTccwFoBx4GiK1cGmdOyLI&amp;dib_tag=se&amp;keywords=ethernet%2Bcable&amp;qid=1752782277&amp;s=electronics&amp;sprefix=ethernet%2Celectronics%2C124&amp;sr=1-6&amp;th=1 " xr:uid="{83A0A177-ED38-4C3C-B1E2-6D1A2C00DD2C}"/>
+    <hyperlink ref="C10" r:id="rId107" xr:uid="{5EF2B5FA-9EB9-4ED3-A87B-DB000918746C}"/>
+    <hyperlink ref="K13" r:id="rId108" display="https://www.amazon.com/Powerbuilt-Piece-Stubby-Long-Wrench/dp/B07N8F7W7K/ref=sr_1_19?dib=eyJ2IjoiMSJ9.URwdEPQXxCMLBhxvS9K5ftG6hwdCaLy_xWZ0vGXOdbuaNrb8XAmO4DQhIxovkvuXsRHPo7oCqjy9Wwt6H6QvZeRYOqVzaLjKkETlnA83OkSSXLxlPpzMt1Qy3kJt-T7GsO_Bq0c0QItERYLb6VTtZmMQdlqDEtc5mdwZiAksW1Y2IKpS2cr-V_j1_L0qMFZKPy2WuoytvNj5MEhK80MOfMrjnaTsJLpB9Io2Jt4xFodm6EN5AwCetZhDdsJTY6jdeOdEdPi6COl5b1RI-6XJHwylh2H13M74HgAUrEaRfoY.bAaypnaW3mj6ulkwXEha2QJSRXBFsgrmQMhuIwb4S2o&amp;dib_tag=se&amp;keywords=stubby%2Ballen%2Bwrench%2Bset&amp;qid=1752911269&amp;sr=8-19&amp;th=1 " xr:uid="{F2200CD7-83CF-497A-91E0-EF5B6CA80C0C}"/>
+    <hyperlink ref="K44" r:id="rId109" xr:uid="{F40A70E6-7F31-454F-9558-A7291A2A2DCF}"/>
+    <hyperlink ref="K45" r:id="rId110" xr:uid="{4A6F6959-0930-44EE-A971-B3EF13DA9390}"/>
+    <hyperlink ref="C51" r:id="rId111" xr:uid="{7963F571-8F62-4D9F-BEF7-F802CD4D18FC}"/>
+    <hyperlink ref="C93" r:id="rId112" xr:uid="{5A200CB5-C655-478F-B00B-2E82D8CC5C77}"/>
+    <hyperlink ref="C94:C95" r:id="rId113" display="https://8020.net/20-2020.html " xr:uid="{94C82CF7-4209-49DE-A286-0E429370F935}"/>
+    <hyperlink ref="C96" r:id="rId114" xr:uid="{3653483D-B8D7-4970-8BE1-067F3CE7FF42}"/>
+    <hyperlink ref="C87" r:id="rId115" xr:uid="{E1AC3FAD-797D-4D40-89E1-E0B078028B08}"/>
+    <hyperlink ref="C66" r:id="rId116" xr:uid="{8B53B0C9-AEB9-4C25-B4D5-D709A9909BD6}"/>
+    <hyperlink ref="C70" r:id="rId117" xr:uid="{2521E3A3-9809-485D-8952-C732415A0425}"/>
+    <hyperlink ref="K41" r:id="rId118" xr:uid="{BE5F57C8-C44E-47CF-B992-FEB02C6C001F}"/>
+    <hyperlink ref="K72" r:id="rId119" xr:uid="{A8E5D7AD-E110-498C-AD66-4031E7159275}"/>
+    <hyperlink ref="K74" r:id="rId120" xr:uid="{686F1C5B-AD14-408B-9AF5-1B4D26D75248}"/>
+    <hyperlink ref="K78" r:id="rId121" xr:uid="{A8336809-C542-4E15-9187-DB4F43D26933}"/>
+    <hyperlink ref="K79" r:id="rId122" xr:uid="{49B9B422-CDDA-427C-82B9-729F2266C333}"/>
+    <hyperlink ref="K80" r:id="rId123" xr:uid="{3E0AC7C3-82FC-4B11-AD25-3DE1DD9499EF}"/>
+    <hyperlink ref="C97" r:id="rId124" xr:uid="{2C6B41AF-87E5-4DA5-9686-67EEDF628339}"/>
+    <hyperlink ref="C36" r:id="rId125" xr:uid="{1800FA32-51EA-41AB-8A1C-BCA281C1CA6B}"/>
+    <hyperlink ref="K75" r:id="rId126" xr:uid="{D1950805-AAE5-4A33-803E-9858D08F12A2}"/>
+    <hyperlink ref="K73" r:id="rId127" xr:uid="{01D963BB-A0C2-4C40-BA01-8B0B76381716}"/>
+    <hyperlink ref="K76" r:id="rId128" xr:uid="{D9B5F8EE-01B9-4AA5-9918-F987CA2D7884}"/>
+    <hyperlink ref="C99" r:id="rId129" display="https://czh-labs.com/products/terminal-block-breakout-board-module-for-teensy-41-screw-mount-version?gad_source=1&amp;gad_campaignid=17335691898&amp;gbraid=0AAAAADQKSWrLA97xSr9gmMM99UCSLmr58&amp;gclid=CjwKCAjwp_LDBhBCEiwAK7FnklUhjhvxFgmMMu0XiWu80nKxdv4QNWNVcUvZhioyk86weMe15LnzoRoClR4QAvD_BwE " xr:uid="{944A4911-F6CF-4EB3-82C2-8B8DAFBE56E9}"/>
+    <hyperlink ref="C37" r:id="rId130" xr:uid="{737F7509-05EB-4CE3-AA5B-929CB63FC161}"/>
+    <hyperlink ref="C8" r:id="rId131" xr:uid="{64F7CD2D-21CD-4075-A33B-B33CA2888693}"/>
+    <hyperlink ref="C41" r:id="rId132" xr:uid="{C902CDD9-1F9D-452D-9583-852C1F7B1429}"/>
+    <hyperlink ref="C45" r:id="rId133" xr:uid="{7DA2E625-AACF-4DED-9279-AA3DDE590F85}"/>
+    <hyperlink ref="C42" r:id="rId134" xr:uid="{EA50026D-4CC0-4262-AA82-1A8C4D553DA4}"/>
+    <hyperlink ref="C43" r:id="rId135" xr:uid="{21A1C6AF-63D2-4FA9-AD9E-D674C1D15883}"/>
+    <hyperlink ref="C39" r:id="rId136" xr:uid="{63D3DD15-6374-4167-9E3E-2CFCBF201E30}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId136"/>
+  <pageSetup orientation="portrait" r:id="rId137"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="fb0bfce0-b493-4733-b695-336371de64d4" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a816e368-bd7d-4e73-ae60-f7bbf4d187c7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="09e37f2ef9bef24154c689c9241203a8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c23ee64ebe9444b24c4b4ef6420ff96" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="71752533c218a459f0bd7314a8d27046">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56df45e61c8cd6f396207a6803100ce0" ns2:_="" ns3:_="">
     <xsd:import namespace="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
     <xsd:import namespace="fb0bfce0-b493-4733-b695-336371de64d4"/>
     <xsd:element name="properties">
@@ -5986,7 +5851,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5995,19 +5860,19 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD534FFF-F9D4-45E9-B4A8-C5178968AA79}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fb0bfce0-b493-4733-b695-336371de64d4"/>
-    <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="fb0bfce0-b493-4733-b695-336371de64d4" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a816e368-bd7d-4e73-ae60-f7bbf4d187c7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30F3C9A4-0D35-4985-9741-8479EE24B4B4}">
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5B4CFA9-3BF7-4410-A240-4C3EA4FF6CE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -6025,10 +5890,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD534FFF-F9D4-45E9-B4A8-C5178968AA79}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fb0bfce0-b493-4733-b695-336371de64d4"/>
+    <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/LC-CNC-BoM.xlsx
+++ b/LC-CNC-BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk.sharepoint.com/sites/UT_DesktopMillingMachine/Shared Documents/General/GitHub-LC_CNC/LC-CNC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1157" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C299951-1E5D-482B-8ECC-EC4B1A01A7AD}"/>
+  <xr:revisionPtr revIDLastSave="1179" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E288FA8-4855-4458-9FDF-A6624BACA694}"/>
   <bookViews>
-    <workbookView xWindow="4575" yWindow="1650" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="312">
   <si>
     <t>Item</t>
   </si>
@@ -203,24 +203,6 @@
     <t xml:space="preserve">https://www.mcmaster.com/5537T651/ </t>
   </si>
   <si>
-    <t>300mm Linear rails</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/dp/B08HC8ZKGB?ref=ppx_yo2ov_dt_b_product_details&amp;th=1</t>
-  </si>
-  <si>
-    <t>400mm Linear rails</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/dp/B08HCQDF6X?ref=ppx_yo2ov_dt_b_product_details&amp;th=1</t>
-  </si>
-  <si>
-    <t>500mm Linear rails</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/dp/B0BKGDT455?psc=1&amp;ref=ppx_yo2ov_dt_b_product_details</t>
-  </si>
-  <si>
     <t>22awg wire</t>
   </si>
   <si>
@@ -422,9 +404,6 @@
     <t>16 In Stock (4-13-25)</t>
   </si>
   <si>
-    <t>11 In Stock</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.mcmaster.com/1416K41/ </t>
   </si>
   <si>
@@ -668,9 +647,6 @@
     <t xml:space="preserve">https://www.mcmaster.com/7566K205/ </t>
   </si>
   <si>
-    <t>Thread forming M3 screws</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.mcmaster.com/99461A942/ </t>
   </si>
   <si>
@@ -774,12 +750,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.amazon.com/Amazon-Basics-Ethernet-High-Speed-Snagless/dp/B089MGH8W3/ref=sr_1_6?crid=15O99JJ9VZUDS&amp;dib=eyJ2IjoiMSJ9.Qrm0YFmTEww5DZc4mrTYoBW2ITYU8YDRmdb4HE4nmukqEngrlTfGgHLb5uoFzqyB8DY16yxmWqTI2jhY13tKSS_gVPXMFmLrV8CwN6seDqr3fe6RoYGbAYOThLs_GPXGD9BG1xBtpSbQCaOmPeX6onzLKT90VpHEp8g8rhIrccYIWeUVb1y9yQszCgP-aLtJNIsqNx1o-8aHQGBnXQxbEdINQFklL4UDCld4WzwhnXy0xN-YFaHdxcyM5kmfmoYQEhD8UEUeVcULGl7eYpTBQi8RxGrjeWwsXTnPG7oVA4s.SJ0prHAqUML_3kLplif-xyTccwFoBx4GiK1cGmdOyLI&amp;dib_tag=se&amp;keywords=ethernet%2Bcable&amp;qid=1752782277&amp;s=electronics&amp;sprefix=ethernet%2Celectronics%2C124&amp;sr=1-6&amp;th=1 </t>
-  </si>
-  <si>
-    <t>Electrical box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.amazon.com/Gratury-Waterproof-Enclosure-Electrical-510%C3%97410%C3%97200mm/dp/B0BFPW79LS?ref_=ast_sto_dp&amp;th=1 </t>
   </si>
   <si>
     <t>Breakout board</t>
@@ -1061,6 +1031,12 @@
   </si>
   <si>
     <t xml:space="preserve">https://a.co/d/07VW1Jxs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://a.co/d/0cbCCCRe </t>
+  </si>
+  <si>
+    <t>Roller arm Limit Switches</t>
   </si>
 </sst>
 </file>
@@ -1739,23 +1715,14 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1769,22 +1736,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2082,26 +2058,26 @@
     <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D2" s="58" t="s">
-        <v>187</v>
-      </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="60"/>
+        <v>179</v>
+      </c>
+      <c r="D2" s="72" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2" s="73"/>
+      <c r="F2" s="74"/>
       <c r="G2" s="19">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="K2" s="71" t="s">
-        <v>274</v>
-      </c>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="73"/>
+        <v>135</v>
+      </c>
+      <c r="K2" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="57"/>
     </row>
     <row r="3" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="43" t="s">
@@ -2142,7 +2118,7 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="58" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="67"/>
@@ -2150,14 +2126,14 @@
       <c r="E4" s="67"/>
       <c r="F4" s="67"/>
       <c r="G4" s="68"/>
-      <c r="J4" s="61" t="s">
+      <c r="J4" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="60"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
@@ -2181,10 +2157,10 @@
         <v>49.95</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>9</v>
@@ -2205,7 +2181,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>9</v>
@@ -2241,19 +2217,19 @@
       </c>
     </row>
     <row r="7" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="60"/>
       <c r="J7" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>9</v>
@@ -2271,10 +2247,10 @@
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>9</v>
@@ -2291,10 +2267,10 @@
         <v>359.99</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>9</v>
@@ -2312,10 +2288,10 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>9</v>
@@ -2332,10 +2308,10 @@
         <v>30.99</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>9</v>
@@ -2352,31 +2328,17 @@
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F10" s="5">
-        <v>129.49</v>
-      </c>
-      <c r="G10" s="6">
-        <f t="shared" si="2"/>
-        <v>129.49</v>
-      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="6"/>
       <c r="J10" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>9</v>
@@ -2414,10 +2376,10 @@
         <v>80.72</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>9</v>
@@ -2455,10 +2417,10 @@
         <v>18.88</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>9</v>
@@ -2496,10 +2458,10 @@
         <v>16.989999999999998</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>9</v>
@@ -2537,10 +2499,10 @@
         <v>16.989999999999998</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>9</v>
@@ -2558,7 +2520,7 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>22</v>
@@ -2578,10 +2540,10 @@
         <v>7.24</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>9</v>
@@ -2619,10 +2581,10 @@
         <v>67.989999999999995</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>9</v>
@@ -2640,10 +2602,10 @@
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>9</v>
@@ -2660,10 +2622,10 @@
         <v>6.39</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>9</v>
@@ -2684,7 +2646,7 @@
         <v>26</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>9</v>
@@ -2701,10 +2663,10 @@
         <v>12.99</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>9</v>
@@ -2725,27 +2687,26 @@
         <v>27</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="20">
-        <f>G2*2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5">
         <v>9.99</v>
       </c>
       <c r="G19" s="6">
         <f t="shared" si="4"/>
-        <v>19.98</v>
+        <v>9.99</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>9</v>
@@ -2783,10 +2744,10 @@
         <v>39.99</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="L20" s="34" t="s">
         <v>9</v>
@@ -2810,7 +2771,7 @@
         <v>31</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E21" s="20">
         <f>G2*2</f>
@@ -2823,14 +2784,14 @@
         <f t="shared" si="4"/>
         <v>69.38</v>
       </c>
-      <c r="J21" s="61" t="s">
+      <c r="J21" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="62"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="63"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="60"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
@@ -2840,7 +2801,7 @@
         <v>33</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E22" s="20">
         <f>G2*1</f>
@@ -2854,10 +2815,10 @@
         <v>40.39</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L22" s="4" t="s">
         <v>9</v>
@@ -2878,7 +2839,7 @@
         <v>34</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>9</v>
@@ -2895,10 +2856,10 @@
         <v>16.989999999999998</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="L23" s="4" t="s">
         <v>9</v>
@@ -2936,10 +2897,10 @@
         <v>8.99</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="L24" s="4" t="s">
         <v>9</v>
@@ -2963,7 +2924,7 @@
         <v>38</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E25" s="20">
         <f>G2*1</f>
@@ -2977,10 +2938,10 @@
         <v>48.99</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="L25" s="34" t="s">
         <v>9</v>
@@ -2996,7 +2957,7 @@
         <v>7.55</v>
       </c>
       <c r="R25" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3020,14 +2981,14 @@
         <f t="shared" si="6"/>
         <v>8.99</v>
       </c>
-      <c r="J26" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="K26" s="62"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="63"/>
+      <c r="J26" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="60"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
@@ -3037,7 +2998,7 @@
         <v>42</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E27" s="20">
         <f>G2*1</f>
@@ -3051,10 +3012,10 @@
         <v>124</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>9</v>
@@ -3072,30 +3033,28 @@
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>56</v>
+        <v>311</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>310</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="E28" s="20">
-        <f>G2*1</f>
         <v>1</v>
       </c>
       <c r="F28" s="5">
-        <v>45.34</v>
-      </c>
-      <c r="G28" s="6">
-        <f t="shared" si="6"/>
-        <v>45.34</v>
+        <v>8.99</v>
+      </c>
+      <c r="G28" s="5">
+        <v>8.99</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>9</v>
@@ -3112,31 +3071,17 @@
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F29" s="5">
-        <v>48.58</v>
-      </c>
-      <c r="G29" s="6">
-        <f>E29*F29</f>
-        <v>48.58</v>
-      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
       <c r="J29" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>9</v>
@@ -3153,31 +3098,17 @@
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F30" s="5">
-        <v>51.74</v>
-      </c>
-      <c r="G30" s="6">
-        <f t="shared" ref="G30" si="8">E30*F30</f>
-        <v>51.74</v>
-      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6"/>
       <c r="J30" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>9</v>
@@ -3195,10 +3126,10 @@
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>9</v>
@@ -3215,10 +3146,10 @@
         <v>15.99</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>9</v>
@@ -3236,10 +3167,10 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>9</v>
@@ -3256,10 +3187,10 @@
         <v>7.69</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>9</v>
@@ -3277,10 +3208,10 @@
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>9</v>
@@ -3297,10 +3228,10 @@
         <v>11.47</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>9</v>
@@ -3318,10 +3249,10 @@
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>9</v>
@@ -3334,14 +3265,14 @@
         <v>12.99</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" ref="G34" si="9">E34*F34</f>
+        <f t="shared" ref="G34" si="8">E34*F34</f>
         <v>12.99</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>9</v>
@@ -3353,16 +3284,16 @@
         <v>84.66</v>
       </c>
       <c r="O34" s="6">
-        <f t="shared" ref="O34" si="10">M34*N34</f>
+        <f t="shared" ref="O34" si="9">M34*N34</f>
         <v>84.66</v>
       </c>
     </row>
     <row r="35" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>9</v>
@@ -3379,10 +3310,10 @@
         <v>7.99</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>9</v>
@@ -3394,16 +3325,16 @@
         <v>102.36</v>
       </c>
       <c r="O35" s="6">
-        <f t="shared" ref="O35" si="11">M35*N35</f>
+        <f t="shared" ref="O35" si="10">M35*N35</f>
         <v>102.36</v>
       </c>
     </row>
     <row r="36" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>9</v>
@@ -3415,16 +3346,16 @@
         <v>13.99</v>
       </c>
       <c r="G36" s="6">
-        <f t="shared" ref="G36:G37" si="12">E36*F36</f>
+        <f t="shared" ref="G36:G37" si="11">E36*F36</f>
         <v>13.99</v>
       </c>
-      <c r="J36" s="64" t="s">
-        <v>196</v>
-      </c>
-      <c r="K36" s="65"/>
-      <c r="L36" s="65"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="66"/>
+      <c r="J36" s="61" t="s">
+        <v>189</v>
+      </c>
+      <c r="K36" s="62"/>
+      <c r="L36" s="62"/>
+      <c r="M36" s="62"/>
+      <c r="N36" s="63"/>
       <c r="O36" s="14">
         <f>SUM(O5:O35)</f>
         <v>1259.6799999999998</v>
@@ -3432,10 +3363,10 @@
     </row>
     <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>9</v>
@@ -3448,16 +3379,16 @@
         <v>19.989999999999998</v>
       </c>
       <c r="G37" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>39.979999999999997</v>
       </c>
     </row>
     <row r="38" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>9</v>
@@ -3474,22 +3405,22 @@
         <v>10.07</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="K38" s="71" t="s">
-        <v>276</v>
-      </c>
-      <c r="L38" s="72"/>
-      <c r="M38" s="72"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="73"/>
+        <v>213</v>
+      </c>
+      <c r="K38" s="55" t="s">
+        <v>266</v>
+      </c>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="57"/>
     </row>
     <row r="39" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>9</v>
@@ -3502,7 +3433,7 @@
         <v>9.99</v>
       </c>
       <c r="G39" s="6">
-        <f t="shared" ref="G39:G44" si="13">E39*F39</f>
+        <f t="shared" ref="G39:G44" si="12">E39*F39</f>
         <v>9.99</v>
       </c>
       <c r="J39" s="46" t="s">
@@ -3526,10 +3457,10 @@
     </row>
     <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>9</v>
@@ -3542,11 +3473,11 @@
         <v>39.99</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>39.99</v>
       </c>
-      <c r="J40" s="61" t="s">
-        <v>217</v>
+      <c r="J40" s="58" t="s">
+        <v>209</v>
       </c>
       <c r="K40" s="67"/>
       <c r="L40" s="67"/>
@@ -3556,10 +3487,10 @@
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>9</v>
@@ -3572,14 +3503,14 @@
         <v>25.99</v>
       </c>
       <c r="G41" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>51.98</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>9</v>
@@ -3591,16 +3522,16 @@
         <v>77.319999999999993</v>
       </c>
       <c r="O41" s="39">
-        <f t="shared" ref="O41:O42" si="14">M41*N41</f>
+        <f t="shared" ref="O41:O42" si="13">M41*N41</f>
         <v>77.319999999999993</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>9</v>
@@ -3613,14 +3544,14 @@
         <v>12.99</v>
       </c>
       <c r="G42" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>12.99</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>9</v>
@@ -3632,16 +3563,16 @@
         <v>22.81</v>
       </c>
       <c r="O42" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>22.81</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>9</v>
@@ -3654,14 +3585,14 @@
         <v>13.95</v>
       </c>
       <c r="G43" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>13.95</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>9</v>
@@ -3679,10 +3610,10 @@
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>9</v>
@@ -3695,14 +3626,14 @@
         <v>44.15</v>
       </c>
       <c r="G44" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>44.15</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>9</v>
@@ -3720,10 +3651,10 @@
     </row>
     <row r="45" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>9</v>
@@ -3740,10 +3671,10 @@
         <v>12.99</v>
       </c>
       <c r="J45" s="16" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="K45" s="22" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="L45" s="34" t="s">
         <v>9</v>
@@ -3760,7 +3691,7 @@
       </c>
     </row>
     <row r="46" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="61" t="s">
+      <c r="B46" s="58" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="67"/>
@@ -3768,8 +3699,8 @@
       <c r="E46" s="67"/>
       <c r="F46" s="67"/>
       <c r="G46" s="68"/>
-      <c r="J46" s="61" t="s">
-        <v>106</v>
+      <c r="J46" s="58" t="s">
+        <v>100</v>
       </c>
       <c r="K46" s="67"/>
       <c r="L46" s="67"/>
@@ -3779,10 +3710,10 @@
     </row>
     <row r="47" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="16" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D47" s="34" t="s">
         <v>9</v>
@@ -3799,10 +3730,10 @@
         <v>8.8559999999999999</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>9</v>
@@ -3818,19 +3749,19 @@
       </c>
     </row>
     <row r="48" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="61" t="s">
+      <c r="B48" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="62"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="63"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="60"/>
       <c r="J48" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="K48" s="12" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>9</v>
@@ -3863,16 +3794,16 @@
         <v>14.77</v>
       </c>
       <c r="G49" s="39">
-        <f t="shared" ref="G49:G101" si="15">E49*F49</f>
+        <f t="shared" ref="G49:G101" si="14">E49*F49</f>
         <v>29.54</v>
       </c>
-      <c r="J49" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="K49" s="65"/>
-      <c r="L49" s="65"/>
-      <c r="M49" s="65"/>
-      <c r="N49" s="66"/>
+      <c r="J49" s="61" t="s">
+        <v>181</v>
+      </c>
+      <c r="K49" s="62"/>
+      <c r="L49" s="62"/>
+      <c r="M49" s="62"/>
+      <c r="N49" s="63"/>
       <c r="O49" s="14">
         <f>SUM(O40:O48)</f>
         <v>319.13</v>
@@ -3896,16 +3827,16 @@
         <v>7.8</v>
       </c>
       <c r="G50" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>15.6</v>
       </c>
     </row>
     <row r="51" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>9</v>
@@ -3918,26 +3849,26 @@
         <v>13.05</v>
       </c>
       <c r="G51" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>26.1</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="K51" s="71" t="s">
-        <v>287</v>
-      </c>
-      <c r="L51" s="72"/>
-      <c r="M51" s="72"/>
-      <c r="N51" s="72"/>
-      <c r="O51" s="73"/>
+        <v>216</v>
+      </c>
+      <c r="K51" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="L51" s="56"/>
+      <c r="M51" s="56"/>
+      <c r="N51" s="56"/>
+      <c r="O51" s="57"/>
     </row>
     <row r="52" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>9</v>
@@ -3950,7 +3881,7 @@
         <v>9.01</v>
       </c>
       <c r="G52" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>9.01</v>
       </c>
       <c r="J52" s="46" t="s">
@@ -3990,11 +3921,11 @@
         <v>3.81</v>
       </c>
       <c r="G53" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>15.24</v>
       </c>
-      <c r="J53" s="61" t="s">
-        <v>217</v>
+      <c r="J53" s="58" t="s">
+        <v>209</v>
       </c>
       <c r="K53" s="67"/>
       <c r="L53" s="67"/>
@@ -4004,7 +3935,7 @@
     </row>
     <row r="54" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>52</v>
@@ -4020,14 +3951,14 @@
         <v>5.29</v>
       </c>
       <c r="G54" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>5.29</v>
       </c>
       <c r="J54" s="16" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="K54" s="22" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="L54" s="34" t="s">
         <v>9</v>
@@ -4039,7 +3970,7 @@
         <v>721.96</v>
       </c>
       <c r="O54" s="41">
-        <f t="shared" ref="O54:O56" si="16">M54*N54</f>
+        <f t="shared" ref="O54:O56" si="15">M54*N54</f>
         <v>721.96</v>
       </c>
     </row>
@@ -4061,11 +3992,11 @@
         <v>4.18</v>
       </c>
       <c r="G55" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>41.8</v>
       </c>
-      <c r="J55" s="61" t="s">
-        <v>106</v>
+      <c r="J55" s="58" t="s">
+        <v>100</v>
       </c>
       <c r="K55" s="67"/>
       <c r="L55" s="67"/>
@@ -4075,10 +4006,10 @@
     </row>
     <row r="56" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>9</v>
@@ -4091,14 +4022,14 @@
         <v>30.67</v>
       </c>
       <c r="G56" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>61.34</v>
       </c>
       <c r="J56" s="16" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="K56" s="42" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="L56" s="34" t="s">
         <v>9</v>
@@ -4110,16 +4041,16 @@
         <v>367.84</v>
       </c>
       <c r="O56" s="41">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>367.84</v>
       </c>
     </row>
     <row r="57" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>9</v>
@@ -4132,11 +4063,11 @@
         <v>9.5500000000000007</v>
       </c>
       <c r="G57" s="6">
-        <f t="shared" ref="G57:G64" si="17">E57*F57</f>
+        <f t="shared" ref="G57:G64" si="16">E57*F57</f>
         <v>19.100000000000001</v>
       </c>
-      <c r="J57" s="61" t="s">
-        <v>238</v>
+      <c r="J57" s="58" t="s">
+        <v>230</v>
       </c>
       <c r="K57" s="67"/>
       <c r="L57" s="67"/>
@@ -4146,10 +4077,10 @@
     </row>
     <row r="58" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>9</v>
@@ -4162,14 +4093,14 @@
         <v>16.87</v>
       </c>
       <c r="G58" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>16.87</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="K58" s="12" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L58" s="4" t="s">
         <v>9</v>
@@ -4181,16 +4112,16 @@
         <v>239.99</v>
       </c>
       <c r="O58" s="39">
-        <f t="shared" ref="O58" si="18">M58*N58</f>
+        <f t="shared" ref="O58" si="17">M58*N58</f>
         <v>239.99</v>
       </c>
     </row>
     <row r="59" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>9</v>
@@ -4203,16 +4134,16 @@
         <v>8.33</v>
       </c>
       <c r="G59" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>8.33</v>
       </c>
-      <c r="J59" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="K59" s="65"/>
-      <c r="L59" s="65"/>
-      <c r="M59" s="65"/>
-      <c r="N59" s="66"/>
+      <c r="J59" s="61" t="s">
+        <v>181</v>
+      </c>
+      <c r="K59" s="62"/>
+      <c r="L59" s="62"/>
+      <c r="M59" s="62"/>
+      <c r="N59" s="63"/>
       <c r="O59" s="14">
         <f>SUM(O54,O58)</f>
         <v>961.95</v>
@@ -4220,10 +4151,10 @@
     </row>
     <row r="60" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="13" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>9</v>
@@ -4236,16 +4167,16 @@
         <v>20.87</v>
       </c>
       <c r="G60" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>20.87</v>
       </c>
     </row>
     <row r="61" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>9</v>
@@ -4258,26 +4189,26 @@
         <v>11.38</v>
       </c>
       <c r="G61" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>22.76</v>
       </c>
       <c r="J61" s="33" t="s">
-        <v>260</v>
-      </c>
-      <c r="K61" s="71" t="s">
-        <v>296</v>
-      </c>
-      <c r="L61" s="72"/>
-      <c r="M61" s="72"/>
-      <c r="N61" s="72"/>
-      <c r="O61" s="73"/>
+        <v>250</v>
+      </c>
+      <c r="K61" s="55" t="s">
+        <v>286</v>
+      </c>
+      <c r="L61" s="56"/>
+      <c r="M61" s="56"/>
+      <c r="N61" s="56"/>
+      <c r="O61" s="57"/>
     </row>
     <row r="62" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="16" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>9</v>
@@ -4290,7 +4221,7 @@
         <v>10.71</v>
       </c>
       <c r="G62" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>10.71</v>
       </c>
       <c r="J62" s="47" t="s">
@@ -4314,10 +4245,10 @@
     </row>
     <row r="63" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>9</v>
@@ -4330,24 +4261,24 @@
         <v>12.36</v>
       </c>
       <c r="G63" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>12.36</v>
       </c>
-      <c r="J63" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="K63" s="69"/>
-      <c r="L63" s="69"/>
-      <c r="M63" s="69"/>
-      <c r="N63" s="69"/>
-      <c r="O63" s="70"/>
+      <c r="J63" s="58" t="s">
+        <v>246</v>
+      </c>
+      <c r="K63" s="75"/>
+      <c r="L63" s="75"/>
+      <c r="M63" s="75"/>
+      <c r="N63" s="75"/>
+      <c r="O63" s="76"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>9</v>
@@ -4360,14 +4291,14 @@
         <v>7.78</v>
       </c>
       <c r="G64" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>7.78</v>
       </c>
       <c r="J64" s="24" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="K64" s="25" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="L64" s="4" t="s">
         <v>9</v>
@@ -4379,16 +4310,16 @@
         <v>135</v>
       </c>
       <c r="O64" s="50">
-        <f t="shared" ref="O64:O65" si="19">M64*N64</f>
+        <f t="shared" ref="O64:O65" si="18">M64*N64</f>
         <v>135</v>
       </c>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>9</v>
@@ -4401,14 +4332,14 @@
         <v>12.92</v>
       </c>
       <c r="G65" s="6">
-        <f t="shared" ref="G65:G70" si="20">E65*F65</f>
+        <f t="shared" ref="G65:G70" si="19">E65*F65</f>
         <v>12.92</v>
       </c>
       <c r="J65" s="24" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="K65" s="25" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>9</v>
@@ -4420,16 +4351,16 @@
         <v>280</v>
       </c>
       <c r="O65" s="26">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>280</v>
       </c>
     </row>
     <row r="66" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>9</v>
@@ -4442,14 +4373,14 @@
         <v>8</v>
       </c>
       <c r="G66" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>8</v>
       </c>
       <c r="J66" s="27" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="K66" s="28" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="L66" s="29" t="s">
         <v>9</v>
@@ -4467,10 +4398,10 @@
     </row>
     <row r="67" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>9</v>
@@ -4483,16 +4414,16 @@
         <v>13.4</v>
       </c>
       <c r="G67" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>13.4</v>
       </c>
-      <c r="J67" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="K67" s="65"/>
-      <c r="L67" s="65"/>
-      <c r="M67" s="65"/>
-      <c r="N67" s="66"/>
+      <c r="J67" s="61" t="s">
+        <v>181</v>
+      </c>
+      <c r="K67" s="62"/>
+      <c r="L67" s="62"/>
+      <c r="M67" s="62"/>
+      <c r="N67" s="63"/>
       <c r="O67" s="32">
         <f>SUM(O64:O66)</f>
         <v>517</v>
@@ -4500,10 +4431,10 @@
     </row>
     <row r="68" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>9</v>
@@ -4516,16 +4447,16 @@
         <v>3.11</v>
       </c>
       <c r="G68" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3.11</v>
       </c>
     </row>
     <row r="69" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>9</v>
@@ -4538,26 +4469,26 @@
         <v>3.56</v>
       </c>
       <c r="G69" s="6">
-        <f t="shared" ref="G69" si="21">E69*F69</f>
+        <f t="shared" ref="G69" si="20">E69*F69</f>
         <v>3.56</v>
       </c>
       <c r="J69" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="K69" s="71" t="s">
-        <v>286</v>
-      </c>
-      <c r="L69" s="72"/>
-      <c r="M69" s="72"/>
-      <c r="N69" s="72"/>
-      <c r="O69" s="73"/>
+        <v>278</v>
+      </c>
+      <c r="K69" s="55" t="s">
+        <v>276</v>
+      </c>
+      <c r="L69" s="56"/>
+      <c r="M69" s="56"/>
+      <c r="N69" s="56"/>
+      <c r="O69" s="57"/>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>9</v>
@@ -4570,7 +4501,7 @@
         <v>6.69</v>
       </c>
       <c r="G70" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>6.69</v>
       </c>
       <c r="J70" s="47" t="s">
@@ -4594,10 +4525,10 @@
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>9</v>
@@ -4610,24 +4541,24 @@
         <v>27.76</v>
       </c>
       <c r="G71" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>27.76</v>
       </c>
-      <c r="J71" s="74" t="s">
-        <v>285</v>
-      </c>
-      <c r="K71" s="75"/>
-      <c r="L71" s="75"/>
-      <c r="M71" s="75"/>
-      <c r="N71" s="75"/>
-      <c r="O71" s="76"/>
+      <c r="J71" s="69" t="s">
+        <v>275</v>
+      </c>
+      <c r="K71" s="70"/>
+      <c r="L71" s="70"/>
+      <c r="M71" s="70"/>
+      <c r="N71" s="70"/>
+      <c r="O71" s="71"/>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>9</v>
@@ -4640,14 +4571,14 @@
         <v>15.31</v>
       </c>
       <c r="G72" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>15.31</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="K72" s="12" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="L72" s="4" t="s">
         <v>9</v>
@@ -4659,16 +4590,16 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="O72" s="6">
-        <f t="shared" ref="O72:O76" si="22">M72*N72</f>
+        <f t="shared" ref="O72:O76" si="21">M72*N72</f>
         <v>34.799999999999997</v>
       </c>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>9</v>
@@ -4681,14 +4612,14 @@
         <v>20</v>
       </c>
       <c r="G73" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="K73" s="12" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="L73" s="4" t="s">
         <v>9</v>
@@ -4700,16 +4631,16 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="O73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>34.799999999999997</v>
       </c>
     </row>
     <row r="74" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>9</v>
@@ -4722,14 +4653,14 @@
         <v>3.9</v>
       </c>
       <c r="G74" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.9</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="K74" s="12" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="L74" s="29" t="s">
         <v>9</v>
@@ -4741,16 +4672,16 @@
         <v>1.79</v>
       </c>
       <c r="O74" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>42.96</v>
       </c>
     </row>
     <row r="75" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>9</v>
@@ -4763,14 +4694,14 @@
         <v>2.34</v>
       </c>
       <c r="G75" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>4.68</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="K75" s="12" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="L75" s="4" t="s">
         <v>9</v>
@@ -4782,16 +4713,16 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="O75" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>34.799999999999997</v>
       </c>
     </row>
     <row r="76" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B76" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>9</v>
@@ -4804,14 +4735,14 @@
         <v>2.34</v>
       </c>
       <c r="G76" s="6">
-        <f t="shared" ref="G76:G82" si="23">E76*F76</f>
+        <f t="shared" ref="G76:G82" si="22">E76*F76</f>
         <v>7.02</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="K76" s="12" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="L76" s="4" t="s">
         <v>9</v>
@@ -4823,16 +4754,16 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="O76" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>26.64</v>
       </c>
     </row>
     <row r="77" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B77" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>9</v>
@@ -4845,24 +4776,24 @@
         <v>2.34</v>
       </c>
       <c r="G77" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>7.02</v>
       </c>
-      <c r="J77" s="74" t="s">
-        <v>293</v>
-      </c>
-      <c r="K77" s="75"/>
-      <c r="L77" s="75"/>
-      <c r="M77" s="75"/>
-      <c r="N77" s="75"/>
-      <c r="O77" s="76"/>
+      <c r="J77" s="69" t="s">
+        <v>283</v>
+      </c>
+      <c r="K77" s="70"/>
+      <c r="L77" s="70"/>
+      <c r="M77" s="70"/>
+      <c r="N77" s="70"/>
+      <c r="O77" s="71"/>
     </row>
     <row r="78" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>9</v>
@@ -4875,14 +4806,14 @@
         <v>2.34</v>
       </c>
       <c r="G78" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>4.68</v>
       </c>
       <c r="J78" s="16" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="L78" s="29" t="s">
         <v>9</v>
@@ -4900,10 +4831,10 @@
     </row>
     <row r="79" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>9</v>
@@ -4916,14 +4847,14 @@
         <v>23.68</v>
       </c>
       <c r="G79" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>23.68</v>
       </c>
       <c r="J79" s="16" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="L79" s="29" t="s">
         <v>9</v>
@@ -4941,10 +4872,10 @@
     </row>
     <row r="80" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>9</v>
@@ -4957,14 +4888,14 @@
         <v>15.54</v>
       </c>
       <c r="G80" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>15.54</v>
       </c>
       <c r="J80" s="16" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="L80" s="29" t="s">
         <v>9</v>
@@ -4982,65 +4913,50 @@
     </row>
     <row r="81" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E81" s="20">
-        <f>G2*1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="5">
         <v>4.79</v>
       </c>
       <c r="G81" s="6">
-        <f t="shared" si="23"/>
-        <v>4.79</v>
-      </c>
-      <c r="J81" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="K81" s="65"/>
-      <c r="L81" s="65"/>
-      <c r="M81" s="65"/>
-      <c r="N81" s="65"/>
+        <f t="shared" si="22"/>
+        <v>9.58</v>
+      </c>
+      <c r="J81" s="61" t="s">
+        <v>181</v>
+      </c>
+      <c r="K81" s="62"/>
+      <c r="L81" s="62"/>
+      <c r="M81" s="62"/>
+      <c r="N81" s="62"/>
       <c r="O81" s="54">
         <f>SUM(O72:O80)</f>
         <v>411.5</v>
       </c>
     </row>
     <row r="82" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B82" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E82" s="20">
-        <f>G2*1</f>
-        <v>1</v>
-      </c>
-      <c r="F82" s="5">
-        <v>8</v>
-      </c>
-      <c r="G82" s="6">
-        <f t="shared" si="23"/>
-        <v>8</v>
-      </c>
+      <c r="B82" s="2"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="6"/>
     </row>
     <row r="83" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B83" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>9</v>
@@ -5053,16 +4969,16 @@
         <v>3.64</v>
       </c>
       <c r="G83" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.64</v>
       </c>
     </row>
     <row r="84" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B84" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>9</v>
@@ -5075,16 +4991,16 @@
         <v>3.64</v>
       </c>
       <c r="G84" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.64</v>
       </c>
     </row>
     <row r="85" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B85" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>9</v>
@@ -5097,16 +5013,16 @@
         <v>3.64</v>
       </c>
       <c r="G85" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.64</v>
       </c>
     </row>
     <row r="86" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B86" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>9</v>
@@ -5119,16 +5035,16 @@
         <v>3.64</v>
       </c>
       <c r="G86" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.64</v>
       </c>
     </row>
     <row r="87" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B87" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>9</v>
@@ -5141,16 +5057,16 @@
         <v>15.26</v>
       </c>
       <c r="G87" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>15.26</v>
       </c>
     </row>
     <row r="88" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B88" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>9</v>
@@ -5163,16 +5079,16 @@
         <v>8.16</v>
       </c>
       <c r="G88" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>8.16</v>
       </c>
     </row>
     <row r="89" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B89" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>9</v>
@@ -5185,16 +5101,16 @@
         <v>8.16</v>
       </c>
       <c r="G89" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>8.16</v>
       </c>
     </row>
     <row r="90" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B90" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>9</v>
@@ -5207,16 +5123,16 @@
         <v>8.16</v>
       </c>
       <c r="G90" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>8.16</v>
       </c>
     </row>
     <row r="91" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="16" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D91" s="34" t="s">
         <v>9</v>
@@ -5234,21 +5150,21 @@
       </c>
     </row>
     <row r="92" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="61" t="s">
-        <v>264</v>
-      </c>
-      <c r="C92" s="62"/>
-      <c r="D92" s="62"/>
-      <c r="E92" s="62"/>
-      <c r="F92" s="62"/>
-      <c r="G92" s="63"/>
+      <c r="B92" s="58" t="s">
+        <v>254</v>
+      </c>
+      <c r="C92" s="59"/>
+      <c r="D92" s="59"/>
+      <c r="E92" s="59"/>
+      <c r="F92" s="59"/>
+      <c r="G92" s="60"/>
     </row>
     <row r="93" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B93" s="16" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D93" s="34" t="s">
         <v>9</v>
@@ -5267,10 +5183,10 @@
     </row>
     <row r="94" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B94" s="16" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D94" s="34" t="s">
         <v>9</v>
@@ -5289,10 +5205,10 @@
     </row>
     <row r="95" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B95" s="16" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C95" s="22" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D95" s="34" t="s">
         <v>9</v>
@@ -5311,10 +5227,10 @@
     </row>
     <row r="96" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B96" s="16" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C96" s="22" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D96" s="34" t="s">
         <v>9</v>
@@ -5333,10 +5249,10 @@
     </row>
     <row r="97" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B97" s="16" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D97" s="34" t="s">
         <v>9</v>
@@ -5354,21 +5270,21 @@
       </c>
     </row>
     <row r="98" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="61" t="s">
-        <v>308</v>
-      </c>
-      <c r="C98" s="62"/>
-      <c r="D98" s="62"/>
-      <c r="E98" s="62"/>
-      <c r="F98" s="62"/>
-      <c r="G98" s="63"/>
+      <c r="B98" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="C98" s="59"/>
+      <c r="D98" s="59"/>
+      <c r="E98" s="59"/>
+      <c r="F98" s="59"/>
+      <c r="G98" s="60"/>
     </row>
     <row r="99" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="2" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>9</v>
@@ -5386,21 +5302,21 @@
       </c>
     </row>
     <row r="100" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="61" t="s">
-        <v>243</v>
-      </c>
-      <c r="C100" s="62"/>
-      <c r="D100" s="62"/>
-      <c r="E100" s="62"/>
-      <c r="F100" s="62"/>
-      <c r="G100" s="63"/>
+      <c r="B100" s="58" t="s">
+        <v>235</v>
+      </c>
+      <c r="C100" s="59"/>
+      <c r="D100" s="59"/>
+      <c r="E100" s="59"/>
+      <c r="F100" s="59"/>
+      <c r="G100" s="60"/>
     </row>
     <row r="101" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>23</v>
@@ -5413,47 +5329,47 @@
         <v>30.21</v>
       </c>
       <c r="G101" s="39">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>30.21</v>
       </c>
     </row>
     <row r="102" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="C102" s="56"/>
-      <c r="D102" s="56"/>
-      <c r="E102" s="56"/>
-      <c r="F102" s="57"/>
+      <c r="B102" s="64" t="s">
+        <v>269</v>
+      </c>
+      <c r="C102" s="65"/>
+      <c r="D102" s="65"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="66"/>
       <c r="G102" s="21">
         <f>SUM(G5:G101)</f>
-        <v>2540.4259999999981</v>
+        <v>2261.0660000000007</v>
       </c>
     </row>
     <row r="103" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="55" t="s">
-        <v>280</v>
-      </c>
-      <c r="C103" s="56"/>
-      <c r="D103" s="56"/>
-      <c r="E103" s="56"/>
-      <c r="F103" s="57"/>
+      <c r="B103" s="64" t="s">
+        <v>270</v>
+      </c>
+      <c r="C103" s="65"/>
+      <c r="D103" s="65"/>
+      <c r="E103" s="65"/>
+      <c r="F103" s="66"/>
       <c r="G103" s="52">
         <f>(SUM(G5:G101))/G2</f>
-        <v>2540.4259999999981</v>
+        <v>2261.0660000000007</v>
       </c>
     </row>
     <row r="104" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="55" t="s">
-        <v>270</v>
-      </c>
-      <c r="C104" s="56"/>
-      <c r="D104" s="56"/>
-      <c r="E104" s="56"/>
-      <c r="F104" s="57"/>
+      <c r="B104" s="64" t="s">
+        <v>260</v>
+      </c>
+      <c r="C104" s="65"/>
+      <c r="D104" s="65"/>
+      <c r="E104" s="65"/>
+      <c r="F104" s="66"/>
       <c r="G104" s="53">
         <f>G103+O67</f>
-        <v>3057.4259999999981</v>
+        <v>2778.0660000000007</v>
       </c>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
@@ -5462,6 +5378,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J21:O21"/>
+    <mergeCell ref="J26:O26"/>
+    <mergeCell ref="J36:N36"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B100:G100"/>
+    <mergeCell ref="J40:O40"/>
+    <mergeCell ref="J46:O46"/>
+    <mergeCell ref="J63:O63"/>
+    <mergeCell ref="K61:O61"/>
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="B92:G92"/>
     <mergeCell ref="J67:N67"/>
@@ -5478,22 +5410,6 @@
     <mergeCell ref="K38:O38"/>
     <mergeCell ref="J77:O77"/>
     <mergeCell ref="B98:G98"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="B102:F102"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J21:O21"/>
-    <mergeCell ref="J26:O26"/>
-    <mergeCell ref="J36:N36"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="B100:G100"/>
-    <mergeCell ref="J40:O40"/>
-    <mergeCell ref="J46:O46"/>
-    <mergeCell ref="J63:O63"/>
-    <mergeCell ref="K61:O61"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{182E6AD4-2BF8-453D-8168-0C5471656634}"/>
@@ -5516,125 +5432,121 @@
     <hyperlink ref="C26" r:id="rId18" xr:uid="{3ACBC04B-80B5-483C-B223-DCC06D04EB43}"/>
     <hyperlink ref="C49" r:id="rId19" xr:uid="{AB2A0A29-8665-4F12-85CA-729F9AEF1954}"/>
     <hyperlink ref="C55" r:id="rId20" xr:uid="{DF72ED0E-A6AE-405C-A831-47EAF4A0978E}"/>
-    <hyperlink ref="C29" r:id="rId21" xr:uid="{3D2201C7-6C8A-4773-B48C-DEC55AB9CE5D}"/>
-    <hyperlink ref="C28" r:id="rId22" xr:uid="{A7E3198B-4B0E-463C-BC5D-907882FF4F1D}"/>
-    <hyperlink ref="C31" r:id="rId23" display="https://www.amazon.com/TYUMEN-Hookup-Electrical-Strips-Extension/dp/B07SLBD1FY?crid=3DSOPLHQPDC41&amp;dib=eyJ2IjoiMSJ9.LbfmNeaOMKQc2NnauqoG3ikk9ANZN_ur4lUWCOCW1O50UvTYKXmiV3AA8Ril1fLOmFRcVVCi_eXXhqwFcZtIW8vmaESTdy6oz8DZxn_URYzZU9OQiHvftwQ3KnaAl6ba-cfRNhMbR7Fpx7tqwarEMqmVU0t2BYcH56emRvXvgV1aTOFyjOYBpkeQMF4SwuInBmgz7WD_t5spHjwSbDYPmshu2rmE36AdUCByV1ie631jZjWBFXP_gl822MkqR8EixD-piO5IZ22jBqlSbpf0TcMJdhRwDpP5zuWzH47ITPk.AI3vrrrkl4uXviMH51NrHs3QtR7dKc_HTTFAhHq9paA&amp;dib_tag=se&amp;keywords=22+awg+wire&amp;qid=1733387088&amp;s=industrial&amp;sprefix=22+awg%2Cindustrial%2C149&amp;sr=1-8" xr:uid="{E82B0C83-0745-457F-853F-CF7C98A9BBAF}"/>
-    <hyperlink ref="K18" r:id="rId24" display="https://www.amazon.com/HUAREW-Values-Ferrite-Suppressor-Diameter/dp/B09SWNPY2Y?crid=25SF4JZN6UMCO&amp;dib=eyJ2IjoiMSJ9.BECN3Z-pnF_DHO20UYNRh-xF2WQPuabKc-oibkz7-5pf-LFqEqaxgUTsjAY9NMHye5H2wuD5X3xZHc2XF6v_ZmAzcFy34lVzkGSEseb_JQsXhQ_lHx78wyV8_2Bl5O2FXq_OPNVVnus4XAq2V7L8dtacsFGCRlHZwgnYlurEB2URoEWdU24JZSoJOdjnTKoB-Nm2-vu6eTFFOKyg0bYDhkvLpIooINxXg8mYy1zuu90.aHjsj2UYUYYX1n4w2EmKBChz9hsqz6bpyNaSrZmD_Pc&amp;dib_tag=se&amp;keywords=ferrite%2Bcore%2Bbead&amp;qid=1733391188&amp;sprefix=ferrite%2Bcore%2Bbead%2Caps%2C148&amp;sr=8-3&amp;th=1 " xr:uid="{3624AB78-BD37-43C7-ABBC-ABDD2D49F1BD}"/>
-    <hyperlink ref="C56" r:id="rId25" xr:uid="{32DB5FB3-622F-4B80-98A2-9D63982309B9}"/>
-    <hyperlink ref="C72" r:id="rId26" xr:uid="{E95793D2-E192-4066-88A4-5B88C4EB6441}"/>
-    <hyperlink ref="C71" r:id="rId27" xr:uid="{89E89EFA-A33B-49E7-9CA3-3AA3F3B2419C}"/>
-    <hyperlink ref="C83" r:id="rId28" xr:uid="{C0887221-10A6-49C9-9592-F29719AB1146}"/>
-    <hyperlink ref="C84" r:id="rId29" xr:uid="{5D432ACC-1036-40C7-BAF5-8E7A9DEE269C}"/>
-    <hyperlink ref="C85" r:id="rId30" xr:uid="{373A1D9B-E52A-4919-BF46-F0054AD0383E}"/>
-    <hyperlink ref="C86" r:id="rId31" xr:uid="{67F0F7A2-8F53-4145-AE23-1984596864D2}"/>
-    <hyperlink ref="C88" r:id="rId32" xr:uid="{0AE9CA58-FE72-4AAA-B4AE-ED28FC16E141}"/>
-    <hyperlink ref="C89" r:id="rId33" xr:uid="{649DFB24-658E-46D9-8DD3-8968123090EE}"/>
-    <hyperlink ref="C90" r:id="rId34" xr:uid="{41AC74BE-2B55-4941-9CA1-1FB8B496080B}"/>
-    <hyperlink ref="C91" r:id="rId35" xr:uid="{673DF358-F6E2-431B-8C25-0F1712C2A5BE}"/>
-    <hyperlink ref="K35" r:id="rId36" xr:uid="{F7DD1C65-60DD-46DD-9FE7-6744F8BA03E7}"/>
-    <hyperlink ref="C59" r:id="rId37" xr:uid="{EF358443-AF57-40E1-92E1-8BF6DD299077}"/>
-    <hyperlink ref="C61" r:id="rId38" xr:uid="{12762096-DC6B-44F2-8ADB-0F58C1B3AEEF}"/>
-    <hyperlink ref="C60" r:id="rId39" xr:uid="{3EFF0D79-73FC-4F62-B070-424FEA2B0998}"/>
-    <hyperlink ref="C63" r:id="rId40" xr:uid="{4C882C61-8A3D-4FF6-8AA2-3CFEBE6A8E31}"/>
-    <hyperlink ref="C57" r:id="rId41" xr:uid="{8C08A008-7728-44D3-BA67-48DB3EEFA7BB}"/>
-    <hyperlink ref="C65" r:id="rId42" xr:uid="{1E69FF1B-0FFD-4B85-B8D4-6662499D5EC6}"/>
-    <hyperlink ref="C67" r:id="rId43" xr:uid="{7C60CB7E-E2C1-46DC-BD3E-B770093F52D5}"/>
-    <hyperlink ref="C68" r:id="rId44" xr:uid="{3FB0574C-FDA6-4DB0-863A-DD9D050D7C39}"/>
-    <hyperlink ref="C58" r:id="rId45" xr:uid="{CFDEAC1B-A32C-4050-8273-2439C47581BB}"/>
-    <hyperlink ref="C62" r:id="rId46" xr:uid="{9A55F38E-8B5A-4A95-8F81-373F25553D76}"/>
-    <hyperlink ref="C64" r:id="rId47" xr:uid="{78F0AA91-375E-4C85-9A3E-A171D50577BA}"/>
-    <hyperlink ref="C6" r:id="rId48" xr:uid="{AED92118-DDB2-4EF3-AC67-4C4C07E0C841}"/>
-    <hyperlink ref="C9" r:id="rId49" xr:uid="{FE9C3C2A-AF4A-4E14-BBDB-335DF3BC0F13}"/>
-    <hyperlink ref="C18" r:id="rId50" xr:uid="{94451722-66BC-4F98-8B43-3E0FC394E5EA}"/>
-    <hyperlink ref="C23" r:id="rId51" xr:uid="{8B80B60C-F876-4871-8577-DC9ACEA588AC}"/>
-    <hyperlink ref="C30" r:id="rId52" xr:uid="{0492A76A-498E-4001-829F-D792C40ACDBA}"/>
-    <hyperlink ref="C52" r:id="rId53" xr:uid="{D6C0DDCE-AD68-4B51-98DF-B171BC702B91}"/>
-    <hyperlink ref="C69" r:id="rId54" xr:uid="{68484166-BD87-4E39-9BD4-46B04DB0A082}"/>
-    <hyperlink ref="C38" r:id="rId55" display="https://www.amazon.com/Universal-Regulated-Switching-Converter-Transformer/dp/B07PPPF1R5/ref=sr_1_6?dib=eyJ2IjoiMSJ9.ghI_8NCu8MWYClVH1bcXae0-G1NHsVMPKXgQ-q9tD7DBjxsd-n2e4GXZyzhj32lWCmUMKNTvmGLgthtkozNnkvRJfBHn4VuSCeTc5lP748T7kJtgdQqg9MH80QXTBMNWupAT-RBnmpw_wBXBO26SKIbj1k64fqcpbisodWHH80xxJPdJFOijPa1IA51xm60Wi2aU2vCne6MmqM3RncHLRYr931SD1UNb9aMjXyOF6U4.dija8_tU-NIlFsudkA1tvV6C6mk8gUO-_lwM8li1rMY&amp;dib_tag=se&amp;keywords=5v%2Bpower%2Bsupply&amp;qid=1743186298&amp;sr=8-6&amp;th=1 " xr:uid="{88BB23CD-312A-41E1-B370-C0D92A466099}"/>
-    <hyperlink ref="C32" r:id="rId56" display="https://www.amazon.com/HiLetgo-Channels-Converter-Bi-Directional-3-3V-5V/dp/B07F7W91LC/ref=sr_1_2?crid=2O7B6QA8ZSPZK&amp;dib=eyJ2IjoiMSJ9.hg1xpaR1IOVH3e6fV4tFyZB8elQluWDLIScr-WIbHEosPLIRhqXG5AnMJTwgM0K6TrBGR457D8AftNCas1RwwWglHyp8zMGTpS2Jwm4xa_uAl0aEMGjby7ffGvEP4lloYctRt9gX4TE3gjllm6sYLU-fsW7zpvcw5ZYESHBPOBCKcQrbrqb3arWPwpjMs7PwokFja-obLRKIr-SuthVfiG0yGem5Rc41xB6eDkr3AZehwq0tgYmv9VxxVa-jlxf9M9Jmhd8G9HvRemxc8IltnV6CNWKiDi1dgnDBhhj15Hs.b7q4qr8rSADKOOdi-2C89QYAixVQ_S86lTmLM2WBijs&amp;dib_tag=se&amp;keywords=logic+converter&amp;qid=1732221329&amp;s=industrial&amp;sprefix=logic+convertyer%2Cindustrial%2C103&amp;sr=1-2" xr:uid="{AA94D625-0126-47B8-979E-9BE236BAD9AD}"/>
-    <hyperlink ref="K17" r:id="rId57" xr:uid="{0F474C1B-53F3-45D5-A2EC-5FEABEC629CC}"/>
-    <hyperlink ref="C47" r:id="rId58" display="https://www.digikey.com/en/products/detail/w-rth-elektronik/691210910002/10668428?gclsrc=aw.ds&amp;&amp;utm_adgroup=&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=PMax%20Supplier_Focus%20Supplier&amp;utm_term=&amp;utm_content=&amp;utm_id=go_cmp-20243063242_adg-_ad-__dev-c_ext-_prd-10668428_sig-CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gad_source=1&amp;gclid=CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gclsrc=aw.ds " xr:uid="{DCE5683A-0BC1-49BA-8FB0-36DC1C1C9A9C}"/>
-    <hyperlink ref="C34" r:id="rId59" xr:uid="{A29FBA48-6899-42FA-AA59-0FC1E2A5A45B}"/>
-    <hyperlink ref="K5" r:id="rId60" display="https://www.amazon.com/Klein-Tools-34056-Adjustable-Electrical/dp/B0D98N52HS/ref=sr_1_1?crid=2OB42YRNYW5S8&amp;dib=eyJ2IjoiMSJ9.55eyclIvGQBRs_G9kszoUlEHRgUtyYkcxabPk-sLw5mt7xuGNeudbfTW8xclKppzTejqidNByQBdPqeEXGg2aJrgDuRoxPddnr7un1KzGrHylGN5yiKL4ycDLAz23bHXFS35VarXoP5Hhq810Sdco6qhSeWGVplSUIYpl56zvRZNrenZvPGmvYU7Y6nsIMihDbf5RoNPi8sUcALPKWZoFyR-Fs3jx2RBJISOeui_PdRPNKnGLGC0Uz395rIEcZ1F9icIwzDBX00JzMC1ZjD_KvEf_nXltgLaawa8vee6Efs.PDGEHgTlQjY0Jz82g_64nVgHTsayEsuiw1VPN9n4cXc&amp;dib_tag=se&amp;keywords=klein%2Bferrule%2Bcrimper&amp;qid=1730823384&amp;sprefix=klein%2Bferrule%2Bcrimper%2Caps%2C132&amp;sr=8-1&amp;th=1 " xr:uid="{CEBE3ECF-00C1-476F-B5EA-6B34F3C440E0}"/>
-    <hyperlink ref="K9" r:id="rId61" display="https://www.amazon.com/Ginsco-580-pcs-Assorted-Sleeving/dp/B01MFA3OFA/ref=sr_1_3?crid=19V7T4IBHC5QO&amp;dib=eyJ2IjoiMSJ9.afAtOFc0AWv7IewHnY-SsmFPIWDeFgvxv7nXELH8Q5qH5K9drWIEjyb4PZCDtpgcSjO1zJt_d_d3Bzwc58g899uhvXzTWNoWa7P0XxuvXztW-5Tc85nP2v3ZP7OVkL9CptCT1e2fAdSg9fifPtR8m9aUVniGOD_xVLXrYdiBq6lh_RbbHkqSMJ69bG3sHk4HbEXsrxggq5C19I64px1H3_Ik8TcJWmowUEtAS4Q9W-qfDLzF-ZeqrhVHbQsdU60_CMcyHcb-SzXuOkdEyVk4hxnhYPkE9DVIFlnwUZ_gnFs.KYnfl9oSznG3OdVCEMra_IGu5ndQOaOh0V01hKDX2Cg&amp;dib_tag=se&amp;keywords=heat+shrink&amp;qid=1730826521&amp;s=industrial&amp;sprefix=heat+shrink%2Cindustrial%2C153&amp;sr=1-3" xr:uid="{332F4161-5937-4DDE-ABA6-DACEB1F4794A}"/>
-    <hyperlink ref="K10" r:id="rId62" display="https://www.amazon.com/Wagner-Spraytech-2417344-Included-Settings/dp/B08RHDWTW1/ref=sr_1_11?crid=3ARWBH2CNL2VG&amp;dib=eyJ2IjoiMSJ9.5gm2Lb5w7VJN8eZBOb3sMfrdDu3W3L85PQTIzxzBZJ1vf-jvbS2FqK77wFjT6OZzl6K6ZPfKPxF69vtZoEGLBwa33pNDuaQFZ5d56VcK6EA5FFGA1--hdSnEw3fLJDXu1T8506U6B4hwJnuMIowuy-pqGmMYEgrUzJgewq75UPRynteSSx1o9beXWRFOtetN7sJ8ZCvbI6SIQRS66FWPs_vl_TxDCTjrDPQKyFweQxdffM2MmYMu_eO5yjQidk2oyLK141Wm02_P7ByEzVHzBvW8fuHA4c3B_Zu46wWCCoI.0J-_R-51Hafm74iaH4iqwhrkZ5Q1Y_KjRNfLvM8jnYc&amp;dib_tag=se&amp;keywords=heat+gun&amp;qid=1730826612&amp;s=industrial&amp;sprefix=heat+gun%2Cindustrial%2C132&amp;sr=1-11" xr:uid="{F5E05831-9E24-43B9-94F1-B4BC1AC96D82}"/>
-    <hyperlink ref="K11" r:id="rId63" display="https://www.amazon.com/VISE-GRIP-Stripping-Cutter-8-Inch-2078309/dp/B000JNNWQ2/ref=sr_1_2?crid=2SRELAQ0SJSSX&amp;dib=eyJ2IjoiMSJ9.nG7mDlLX3e8OY6I2TjYCT2FSzLyODDpPex6UnS9dB8ZSP-3DZSkQVn-yGInthfRJK_Of8xmDaaqhT4jhLXSvHyO6EI69a6virDvTLdlxbf1ngpiAjQs3-bOHwDe7vb6w90nbwCbO1LttItJjb9iHGoultOHeluZLJlLzJk4xzY5UfDhbWwEhFaLgMgB_5i5TLu5qOUnejGHsV4K5nAYlFqF68IiAuQ8kcCpQK-0dTqQun1akqTS4dgx4cP2W-BbkYxyu_SpIm9cpJrv_m28fAnH0ydJPD5gvv0pU6kc5380.MnLh1rZQ5i8y79mo0RvgZquA_sAp_v-KzSZImycUxdo&amp;dib_tag=se&amp;keywords=irwin+wire+stripper&amp;qid=1730826958&amp;s=industrial&amp;sprefix=irwin+wire+stipper%2Cindustrial%2C91&amp;sr=1-2" xr:uid="{CD595E57-DC94-4850-8524-5A1DEB057175}"/>
-    <hyperlink ref="K12" r:id="rId64" display="https://www.amazon.com/Haisstronica-Electrical-Connectors-AWG-Tools-Racheting-Tools-Available/dp/B08F3JKDD3/ref=sr_1_5?crid=1UC6EBL5V8RZ&amp;dib=eyJ2IjoiMSJ9.fViKUMP--aXWyr_VSPqdFihmmRK82p3-xep_6UgQhjDmE4EGGDd0-VEfAWJH_2mkTtPo3hrn-Xjo7ioxvPrUX0cyXLrCA085qarrwngsgJhVZKWjQdCGzM1VtfnKeWQyPkH1l5eFuRy8m-gggxen_-oBrfY57oEGfJPVl_9QkByDRNqlbX7ayxV95AD9q55o-eUJR0byooY9wqq8VXvLclS6gejWED1xpqlQe_Yi-hdIUKvw2g17SKPIJFYpOUh-aUsmMh7lBM3Rn7ZnY6d1lU1h65gSrMFxrFAzXbBxYpI.2fSr4cew3Mlijb7rQiZIXFl97Cz8Kq21oEmZlfD39QA&amp;dib_tag=se&amp;keywords=crimping%2Btool&amp;qid=1730827014&amp;s=industrial&amp;sprefix=crimp%2Cindustrial%2C124&amp;sr=1-5&amp;th=1" xr:uid="{85E51D7B-B8E9-4DCD-BD2E-91CCEC064732}"/>
-    <hyperlink ref="K15" r:id="rId65" display="https://www.amazon.com/WEICON-Stripper-Adjustable-0-2-6-0-Stripping/dp/B001NUMVHQ/ref=sr_1_5?crid=1SSXPMUMUE8CN&amp;dib=eyJ2IjoiMSJ9.dlOqGoMqoa_J0KSIP8b8Qbu_4eK_g9aMoAPXb0geqceQW-YR7aelaKVCxL2tekl_qTBB43ciINtSLHJSQG6Y7PoXsAKTjR0Vo6bTGJrFUiXXhUkg96MaCEz8OnQ8WY-HcVJ2TOCkWjl8zYWb8igBh3vDa65alauML_lvmK4sNW2Hajnj_eGwldJ1C1nnfpdJB6Z8Xff_a30CAQlvA6QxYKJyBTg1alIgilMrQafgNCcujVp2rrIHnhGbFmSlwltAwRIe1eQiGTCgM3PWN_795FsBQ6j93SaJkyflOtfucF8.Tb3cTlKfvm5Cy0Fp4c7TNNFBEcYGjRD7YrqefRf77g4&amp;dib_tag=se&amp;keywords=weicon+wire+stripping+tool&amp;qid=1732209102&amp;sprefix=weicon+wire+stripping+tool%2Caps%2C104&amp;sr=8-5" xr:uid="{861EFE74-739C-4CD2-9085-6EFE07B3481C}"/>
-    <hyperlink ref="K34" r:id="rId66" xr:uid="{77D63543-B36B-4B98-A73E-F3857D81E695}"/>
-    <hyperlink ref="K30" r:id="rId67" xr:uid="{1BB7CBF3-BD44-4F4B-8FC4-904F64FC7D13}"/>
-    <hyperlink ref="K27" r:id="rId68" xr:uid="{FF699E51-8F2F-483B-80C4-2D079998FED3}"/>
-    <hyperlink ref="K31" r:id="rId69" xr:uid="{A1F8AA51-ED01-4671-ADB1-5036FF8B669F}"/>
-    <hyperlink ref="K23" r:id="rId70" xr:uid="{B44ED290-8CBF-48A9-8EFB-3CB4B0760A72}"/>
-    <hyperlink ref="K25" r:id="rId71" xr:uid="{EDDA737D-4038-4DB0-B323-C2D73FD73576}"/>
-    <hyperlink ref="K20" r:id="rId72" display="https://www.amazon.com/Klein-Tools-MM325-Multimeter-Manual-Ranging/dp/B0B57L9FNL?dib=eyJ2IjoiMSJ9.XOXQgFuugT7fSqk2JXgR554EvBn03HSeasFjjzBAbBJ0lnoLvn4AnJEthmy5GYMbfcc-d9gjjvtPqgpSKu3iK9JyBR2HwE_gjWGN0MWg07nigXvQ43521m39rI3_AeWTBSKvCArU06kfWba8iPBP_q6kwcBoJ0bKGpUibs7qIEz0JBvM_m3cfmO2PytEFbWld5CguH1PB6VdvsJfuMeUCKj1nctG-6zPVqUdWNu5gjviDmequn_waQEOMR665LW-ucWCwNcug5d1Rem35c7HMDSqCAqTXvos7iSVccjXJ1I.tr3V0PDK2DnUmPDVm8XLG7GKOVNrAFyMQ0FWyT43FtA&amp;dib_tag=se&amp;keywords=multi%2Bmeter&amp;qid=1733388969&amp;sr=8-7&amp;th=1 " xr:uid="{6844E477-F27E-4A9B-B552-C8FC9B6A7C36}"/>
-    <hyperlink ref="K14" r:id="rId73" display="https://www.amazon.com/Amazon-Basics-Ratcheting-Electronics-Screwdriver/dp/B07V4TFWFZ/ref=sr_1_5?crid=5FDDKZ08W2XH&amp;dib=eyJ2IjoiMSJ9.A3n1jTNvIcpz61ypsmX9MBC_oUMTAhq1t44j_1J2e-nP5QHjm-pYiYJpVEusn6bIqa3PCg3Wthb6yyUmN9i-KhuNmdX26_MOiWL-RM2nz3ddQW5BbA2A3qcnpi5yby99hcMeEY3ZtnVl8snxyRqqeIoYNiIK2Dh6dIkqu7FTlrOT6cZz3UlOXKTjSAhmdZxjc5rvX9_XaSQgv_geb0S7uFEpcu9cLsoPGXJ3e7MoxcAQBeBsPPNbonfZ3TR-ewlb8XIDRBg0v7Zivipx5bQT51QYOTQBfPiJ4ix71GX2imo.4o19nzIzWNm0dO5IQWSfMam_e1TDYdj-YMl6nwuPwfw&amp;dib_tag=se&amp;keywords=small%2Belectronics%2Bscrew%2Bdriver%2Bset&amp;qid=1732221537&amp;s=industrial&amp;sprefix=small%2Belectronics%2Bscrew%2Bdriver%2Bset%2Cindustrial%2C100&amp;sr=1-5&amp;th=1" xr:uid="{998DFED7-FD15-4152-BFA6-54275B60F63A}"/>
-    <hyperlink ref="K8" r:id="rId74" display="https://www.amazon.com/MAIYUM-63-37-Solder-Electrical-Soldering/dp/B075WB98FJ/ref=sr_1_4?crid=FUL9XTKIEH0Q&amp;dib=eyJ2IjoiMSJ9.SSzB0hv2YBXV9gPCxCyydd5S_u5flP9lHY5GxroTHXWE-O_gYdIn4eeIMj1MxksAaIi1XAIo_B_iaJ4XYEW_46uVfck5Fk-qgWP2zm2sViFlUXR1GlRH2Jxryx5KdgBpWLBjxrFU6KkL22wi1mdGe0nLo4hcc14I1IP5ZsyRv-C8oUQPfZciMrOodLex43BGja33E0IkuYqS3dCAs3Y-oD3ghP974Cu5_ptNdl8G1-wMVZ3eIVDorhDZX5_grSmX0xlP_xCphsipUCLxmC7mEFWguLxG_b8EZ0OO87S_9Fw.KsUflA4BP63mIa38we7VsxqUAglWv377w8Y-exq7TQQ&amp;dib_tag=se&amp;keywords=solder%2Bwith%2Bflux&amp;qid=1730823776&amp;s=hi&amp;sprefix=solder%2Bwith%2Bflux%2Ctools%2C101&amp;sr=1-4&amp;th=1" xr:uid="{0357DF8A-D0E5-42BB-92C4-6DBD9C45345F}"/>
-    <hyperlink ref="K33" r:id="rId75" xr:uid="{99D8A20C-917E-4522-83A0-C319C991F299}"/>
-    <hyperlink ref="K22" r:id="rId76" xr:uid="{294EC5C0-0591-4D84-BD56-9ACE6CDE80BA}"/>
-    <hyperlink ref="K19" r:id="rId77" xr:uid="{CF48C670-F50C-4DF9-B593-ED5D439D7822}"/>
-    <hyperlink ref="K16" r:id="rId78" display="https://www.amazon.com/Milwaukee-M12-Lithium-Ion-Cordless-Kit/dp/B07J1DCM59/ref=sr_1_2?crid=T8KHPS70XKI2&amp;dib=eyJ2IjoiMSJ9.dfyp5QTjupoTHgodWAHsGfuOMaTLJm7DDsIUr11ufFsYHAn0rfuv6naAjnMC5JCAroszQI_218d92cwRA7Ob-4Lz7I6szZUCh4V-Z7ZiJOviGsbGMlQhVkePjD_JzUhnHe9X52TEY5FQ5E-T-ddnBDoRgmHk7PcZexXQFtEwAZ2Pznq8Er2Mt_hRvOwk3S6nx8NxhBgztopKhQS32-QfrY9DEWxtJCzDil2auIQ4NeaU4I50CIlwfKO22MPlLHgcgGcWC-4jnHwziasnQpWdtp0eitiu74YKIoY56dKatdI.1UJ1NUvjpquCkQiTSeXnAjDQCRrcaDytyoSPdwmhfho&amp;dib_tag=se&amp;keywords=milwaukee+compressor+m12&amp;qid=1744600915&amp;s=hi&amp;sprefix=milwaukee+compressor+m12%2Ctools%2C78&amp;sr=1-2 " xr:uid="{1D205F97-D9EF-4167-A62C-09373C316758}"/>
-    <hyperlink ref="K28" r:id="rId79" xr:uid="{5F7730D8-6AC1-4AFC-BDF9-357875FD1123}"/>
-    <hyperlink ref="K29" r:id="rId80" xr:uid="{7D645F8A-33CD-418D-8D23-F32705DFD52D}"/>
-    <hyperlink ref="K32" r:id="rId81" xr:uid="{72352CC7-698C-4AF0-BCF4-715EF6461852}"/>
-    <hyperlink ref="C76" r:id="rId82" xr:uid="{D0BFB25A-21DF-4F2E-8B59-E3DD05C3B098}"/>
-    <hyperlink ref="C75" r:id="rId83" xr:uid="{D5A5F088-A84E-4368-83A3-93B6A7392B62}"/>
-    <hyperlink ref="C77" r:id="rId84" xr:uid="{03C53325-8F52-47AD-98AA-5B3BD79FCDF7}"/>
-    <hyperlink ref="C78" r:id="rId85" xr:uid="{BC613FBE-2FF7-47F4-BA8F-9A2B780CBF4D}"/>
-    <hyperlink ref="C79" r:id="rId86" xr:uid="{18524F55-8313-44A2-98E0-8D3476379625}"/>
-    <hyperlink ref="C80" r:id="rId87" xr:uid="{C5B457D0-EBF2-4473-8DE5-A2CBF0192FC7}"/>
-    <hyperlink ref="C82" r:id="rId88" xr:uid="{E9EBC0D2-18CA-4009-92BF-AA4627474036}"/>
-    <hyperlink ref="C81" r:id="rId89" xr:uid="{F9DC2B0F-6CC2-4333-B6A0-4C461C26A42D}"/>
-    <hyperlink ref="C35" r:id="rId90" xr:uid="{B350E38A-0704-49E3-B0A0-6AC64705FFA8}"/>
-    <hyperlink ref="K24" r:id="rId91" xr:uid="{38DE31D1-83D2-44D7-B2DB-47B0912A74D8}"/>
-    <hyperlink ref="K42" r:id="rId92" xr:uid="{99DE23E2-FB55-46E7-81C4-10D9C3F12704}"/>
-    <hyperlink ref="K43" r:id="rId93" xr:uid="{C65D4C28-A0F4-4162-A2A5-E142AED72659}"/>
-    <hyperlink ref="K47" r:id="rId94" xr:uid="{DAB44B0A-B63A-4471-ADE7-6D09C28FFC68}"/>
-    <hyperlink ref="K48" r:id="rId95" xr:uid="{D3082204-ACAD-465A-B054-F2BD8FB8F1EB}"/>
-    <hyperlink ref="C33" r:id="rId96" xr:uid="{DD69F44F-F79E-4411-A5F6-7F4820E93E7C}"/>
-    <hyperlink ref="K54" r:id="rId97" xr:uid="{08CDA0A7-76D0-4386-8DF9-D40020E4F6BB}"/>
-    <hyperlink ref="K56" r:id="rId98" xr:uid="{B817C2C0-888A-41EE-BB96-AA202FF7D26F}"/>
-    <hyperlink ref="K7" r:id="rId99" xr:uid="{403CBC77-BB8E-482D-ADB0-566010CFFBFE}"/>
-    <hyperlink ref="C101" r:id="rId100" xr:uid="{66B61CB6-8DEE-47E0-8F58-13DFE696A594}"/>
-    <hyperlink ref="C19" r:id="rId101" xr:uid="{25851340-5A38-4A26-A3FC-843A61F946D3}"/>
-    <hyperlink ref="C40" r:id="rId102" xr:uid="{E912526C-B82A-4A44-8481-EFACD695EA8D}"/>
-    <hyperlink ref="C44" r:id="rId103" xr:uid="{E865141B-878A-4CD6-B122-3ADC6852D520}"/>
-    <hyperlink ref="K58" r:id="rId104" location="tabbed-customerreviews " xr:uid="{24F44932-6634-42FE-8337-20CA3C2EC1E4}"/>
-    <hyperlink ref="C74" r:id="rId105" xr:uid="{326567BB-9D82-4E92-ACC4-530A6BCCFC38}"/>
-    <hyperlink ref="C17" r:id="rId106" display="https://www.amazon.com/Amazon-Basics-Ethernet-High-Speed-Snagless/dp/B089MGH8W3/ref=sr_1_6?crid=15O99JJ9VZUDS&amp;dib=eyJ2IjoiMSJ9.Qrm0YFmTEww5DZc4mrTYoBW2ITYU8YDRmdb4HE4nmukqEngrlTfGgHLb5uoFzqyB8DY16yxmWqTI2jhY13tKSS_gVPXMFmLrV8CwN6seDqr3fe6RoYGbAYOThLs_GPXGD9BG1xBtpSbQCaOmPeX6onzLKT90VpHEp8g8rhIrccYIWeUVb1y9yQszCgP-aLtJNIsqNx1o-8aHQGBnXQxbEdINQFklL4UDCld4WzwhnXy0xN-YFaHdxcyM5kmfmoYQEhD8UEUeVcULGl7eYpTBQi8RxGrjeWwsXTnPG7oVA4s.SJ0prHAqUML_3kLplif-xyTccwFoBx4GiK1cGmdOyLI&amp;dib_tag=se&amp;keywords=ethernet%2Bcable&amp;qid=1752782277&amp;s=electronics&amp;sprefix=ethernet%2Celectronics%2C124&amp;sr=1-6&amp;th=1 " xr:uid="{83A0A177-ED38-4C3C-B1E2-6D1A2C00DD2C}"/>
-    <hyperlink ref="C10" r:id="rId107" xr:uid="{5EF2B5FA-9EB9-4ED3-A87B-DB000918746C}"/>
-    <hyperlink ref="K13" r:id="rId108" display="https://www.amazon.com/Powerbuilt-Piece-Stubby-Long-Wrench/dp/B07N8F7W7K/ref=sr_1_19?dib=eyJ2IjoiMSJ9.URwdEPQXxCMLBhxvS9K5ftG6hwdCaLy_xWZ0vGXOdbuaNrb8XAmO4DQhIxovkvuXsRHPo7oCqjy9Wwt6H6QvZeRYOqVzaLjKkETlnA83OkSSXLxlPpzMt1Qy3kJt-T7GsO_Bq0c0QItERYLb6VTtZmMQdlqDEtc5mdwZiAksW1Y2IKpS2cr-V_j1_L0qMFZKPy2WuoytvNj5MEhK80MOfMrjnaTsJLpB9Io2Jt4xFodm6EN5AwCetZhDdsJTY6jdeOdEdPi6COl5b1RI-6XJHwylh2H13M74HgAUrEaRfoY.bAaypnaW3mj6ulkwXEha2QJSRXBFsgrmQMhuIwb4S2o&amp;dib_tag=se&amp;keywords=stubby%2Ballen%2Bwrench%2Bset&amp;qid=1752911269&amp;sr=8-19&amp;th=1 " xr:uid="{F2200CD7-83CF-497A-91E0-EF5B6CA80C0C}"/>
-    <hyperlink ref="K44" r:id="rId109" xr:uid="{F40A70E6-7F31-454F-9558-A7291A2A2DCF}"/>
-    <hyperlink ref="K45" r:id="rId110" xr:uid="{4A6F6959-0930-44EE-A971-B3EF13DA9390}"/>
-    <hyperlink ref="C51" r:id="rId111" xr:uid="{7963F571-8F62-4D9F-BEF7-F802CD4D18FC}"/>
-    <hyperlink ref="C93" r:id="rId112" xr:uid="{5A200CB5-C655-478F-B00B-2E82D8CC5C77}"/>
-    <hyperlink ref="C94:C95" r:id="rId113" display="https://8020.net/20-2020.html " xr:uid="{94C82CF7-4209-49DE-A286-0E429370F935}"/>
-    <hyperlink ref="C96" r:id="rId114" xr:uid="{3653483D-B8D7-4970-8BE1-067F3CE7FF42}"/>
-    <hyperlink ref="C87" r:id="rId115" xr:uid="{E1AC3FAD-797D-4D40-89E1-E0B078028B08}"/>
-    <hyperlink ref="C66" r:id="rId116" xr:uid="{8B53B0C9-AEB9-4C25-B4D5-D709A9909BD6}"/>
-    <hyperlink ref="C70" r:id="rId117" xr:uid="{2521E3A3-9809-485D-8952-C732415A0425}"/>
-    <hyperlink ref="K41" r:id="rId118" xr:uid="{BE5F57C8-C44E-47CF-B992-FEB02C6C001F}"/>
-    <hyperlink ref="K72" r:id="rId119" xr:uid="{A8E5D7AD-E110-498C-AD66-4031E7159275}"/>
-    <hyperlink ref="K74" r:id="rId120" xr:uid="{686F1C5B-AD14-408B-9AF5-1B4D26D75248}"/>
-    <hyperlink ref="K78" r:id="rId121" xr:uid="{A8336809-C542-4E15-9187-DB4F43D26933}"/>
-    <hyperlink ref="K79" r:id="rId122" xr:uid="{49B9B422-CDDA-427C-82B9-729F2266C333}"/>
-    <hyperlink ref="K80" r:id="rId123" xr:uid="{3E0AC7C3-82FC-4B11-AD25-3DE1DD9499EF}"/>
-    <hyperlink ref="C97" r:id="rId124" xr:uid="{2C6B41AF-87E5-4DA5-9686-67EEDF628339}"/>
-    <hyperlink ref="C36" r:id="rId125" xr:uid="{1800FA32-51EA-41AB-8A1C-BCA281C1CA6B}"/>
-    <hyperlink ref="K75" r:id="rId126" xr:uid="{D1950805-AAE5-4A33-803E-9858D08F12A2}"/>
-    <hyperlink ref="K73" r:id="rId127" xr:uid="{01D963BB-A0C2-4C40-BA01-8B0B76381716}"/>
-    <hyperlink ref="K76" r:id="rId128" xr:uid="{D9B5F8EE-01B9-4AA5-9918-F987CA2D7884}"/>
-    <hyperlink ref="C99" r:id="rId129" display="https://czh-labs.com/products/terminal-block-breakout-board-module-for-teensy-41-screw-mount-version?gad_source=1&amp;gad_campaignid=17335691898&amp;gbraid=0AAAAADQKSWrLA97xSr9gmMM99UCSLmr58&amp;gclid=CjwKCAjwp_LDBhBCEiwAK7FnklUhjhvxFgmMMu0XiWu80nKxdv4QNWNVcUvZhioyk86weMe15LnzoRoClR4QAvD_BwE " xr:uid="{944A4911-F6CF-4EB3-82C2-8B8DAFBE56E9}"/>
-    <hyperlink ref="C37" r:id="rId130" xr:uid="{737F7509-05EB-4CE3-AA5B-929CB63FC161}"/>
-    <hyperlink ref="C8" r:id="rId131" xr:uid="{64F7CD2D-21CD-4075-A33B-B33CA2888693}"/>
-    <hyperlink ref="C41" r:id="rId132" xr:uid="{C902CDD9-1F9D-452D-9583-852C1F7B1429}"/>
-    <hyperlink ref="C45" r:id="rId133" xr:uid="{7DA2E625-AACF-4DED-9279-AA3DDE590F85}"/>
-    <hyperlink ref="C42" r:id="rId134" xr:uid="{EA50026D-4CC0-4262-AA82-1A8C4D553DA4}"/>
-    <hyperlink ref="C43" r:id="rId135" xr:uid="{21A1C6AF-63D2-4FA9-AD9E-D674C1D15883}"/>
-    <hyperlink ref="C39" r:id="rId136" xr:uid="{63D3DD15-6374-4167-9E3E-2CFCBF201E30}"/>
+    <hyperlink ref="C31" r:id="rId21" display="https://www.amazon.com/TYUMEN-Hookup-Electrical-Strips-Extension/dp/B07SLBD1FY?crid=3DSOPLHQPDC41&amp;dib=eyJ2IjoiMSJ9.LbfmNeaOMKQc2NnauqoG3ikk9ANZN_ur4lUWCOCW1O50UvTYKXmiV3AA8Ril1fLOmFRcVVCi_eXXhqwFcZtIW8vmaESTdy6oz8DZxn_URYzZU9OQiHvftwQ3KnaAl6ba-cfRNhMbR7Fpx7tqwarEMqmVU0t2BYcH56emRvXvgV1aTOFyjOYBpkeQMF4SwuInBmgz7WD_t5spHjwSbDYPmshu2rmE36AdUCByV1ie631jZjWBFXP_gl822MkqR8EixD-piO5IZ22jBqlSbpf0TcMJdhRwDpP5zuWzH47ITPk.AI3vrrrkl4uXviMH51NrHs3QtR7dKc_HTTFAhHq9paA&amp;dib_tag=se&amp;keywords=22+awg+wire&amp;qid=1733387088&amp;s=industrial&amp;sprefix=22+awg%2Cindustrial%2C149&amp;sr=1-8" xr:uid="{E82B0C83-0745-457F-853F-CF7C98A9BBAF}"/>
+    <hyperlink ref="K18" r:id="rId22" display="https://www.amazon.com/HUAREW-Values-Ferrite-Suppressor-Diameter/dp/B09SWNPY2Y?crid=25SF4JZN6UMCO&amp;dib=eyJ2IjoiMSJ9.BECN3Z-pnF_DHO20UYNRh-xF2WQPuabKc-oibkz7-5pf-LFqEqaxgUTsjAY9NMHye5H2wuD5X3xZHc2XF6v_ZmAzcFy34lVzkGSEseb_JQsXhQ_lHx78wyV8_2Bl5O2FXq_OPNVVnus4XAq2V7L8dtacsFGCRlHZwgnYlurEB2URoEWdU24JZSoJOdjnTKoB-Nm2-vu6eTFFOKyg0bYDhkvLpIooINxXg8mYy1zuu90.aHjsj2UYUYYX1n4w2EmKBChz9hsqz6bpyNaSrZmD_Pc&amp;dib_tag=se&amp;keywords=ferrite%2Bcore%2Bbead&amp;qid=1733391188&amp;sprefix=ferrite%2Bcore%2Bbead%2Caps%2C148&amp;sr=8-3&amp;th=1 " xr:uid="{3624AB78-BD37-43C7-ABBC-ABDD2D49F1BD}"/>
+    <hyperlink ref="C56" r:id="rId23" xr:uid="{32DB5FB3-622F-4B80-98A2-9D63982309B9}"/>
+    <hyperlink ref="C72" r:id="rId24" xr:uid="{E95793D2-E192-4066-88A4-5B88C4EB6441}"/>
+    <hyperlink ref="C71" r:id="rId25" xr:uid="{89E89EFA-A33B-49E7-9CA3-3AA3F3B2419C}"/>
+    <hyperlink ref="C83" r:id="rId26" xr:uid="{C0887221-10A6-49C9-9592-F29719AB1146}"/>
+    <hyperlink ref="C84" r:id="rId27" xr:uid="{5D432ACC-1036-40C7-BAF5-8E7A9DEE269C}"/>
+    <hyperlink ref="C85" r:id="rId28" xr:uid="{373A1D9B-E52A-4919-BF46-F0054AD0383E}"/>
+    <hyperlink ref="C86" r:id="rId29" xr:uid="{67F0F7A2-8F53-4145-AE23-1984596864D2}"/>
+    <hyperlink ref="C88" r:id="rId30" xr:uid="{0AE9CA58-FE72-4AAA-B4AE-ED28FC16E141}"/>
+    <hyperlink ref="C89" r:id="rId31" xr:uid="{649DFB24-658E-46D9-8DD3-8968123090EE}"/>
+    <hyperlink ref="C90" r:id="rId32" xr:uid="{41AC74BE-2B55-4941-9CA1-1FB8B496080B}"/>
+    <hyperlink ref="C91" r:id="rId33" xr:uid="{673DF358-F6E2-431B-8C25-0F1712C2A5BE}"/>
+    <hyperlink ref="K35" r:id="rId34" xr:uid="{F7DD1C65-60DD-46DD-9FE7-6744F8BA03E7}"/>
+    <hyperlink ref="C59" r:id="rId35" xr:uid="{EF358443-AF57-40E1-92E1-8BF6DD299077}"/>
+    <hyperlink ref="C61" r:id="rId36" xr:uid="{12762096-DC6B-44F2-8ADB-0F58C1B3AEEF}"/>
+    <hyperlink ref="C60" r:id="rId37" xr:uid="{3EFF0D79-73FC-4F62-B070-424FEA2B0998}"/>
+    <hyperlink ref="C63" r:id="rId38" xr:uid="{4C882C61-8A3D-4FF6-8AA2-3CFEBE6A8E31}"/>
+    <hyperlink ref="C57" r:id="rId39" xr:uid="{8C08A008-7728-44D3-BA67-48DB3EEFA7BB}"/>
+    <hyperlink ref="C65" r:id="rId40" xr:uid="{1E69FF1B-0FFD-4B85-B8D4-6662499D5EC6}"/>
+    <hyperlink ref="C67" r:id="rId41" xr:uid="{7C60CB7E-E2C1-46DC-BD3E-B770093F52D5}"/>
+    <hyperlink ref="C68" r:id="rId42" xr:uid="{3FB0574C-FDA6-4DB0-863A-DD9D050D7C39}"/>
+    <hyperlink ref="C58" r:id="rId43" xr:uid="{CFDEAC1B-A32C-4050-8273-2439C47581BB}"/>
+    <hyperlink ref="C62" r:id="rId44" xr:uid="{9A55F38E-8B5A-4A95-8F81-373F25553D76}"/>
+    <hyperlink ref="C64" r:id="rId45" xr:uid="{78F0AA91-375E-4C85-9A3E-A171D50577BA}"/>
+    <hyperlink ref="C6" r:id="rId46" xr:uid="{AED92118-DDB2-4EF3-AC67-4C4C07E0C841}"/>
+    <hyperlink ref="C9" r:id="rId47" xr:uid="{FE9C3C2A-AF4A-4E14-BBDB-335DF3BC0F13}"/>
+    <hyperlink ref="C18" r:id="rId48" xr:uid="{94451722-66BC-4F98-8B43-3E0FC394E5EA}"/>
+    <hyperlink ref="C23" r:id="rId49" xr:uid="{8B80B60C-F876-4871-8577-DC9ACEA588AC}"/>
+    <hyperlink ref="C52" r:id="rId50" xr:uid="{D6C0DDCE-AD68-4B51-98DF-B171BC702B91}"/>
+    <hyperlink ref="C69" r:id="rId51" xr:uid="{68484166-BD87-4E39-9BD4-46B04DB0A082}"/>
+    <hyperlink ref="C38" r:id="rId52" display="https://www.amazon.com/Universal-Regulated-Switching-Converter-Transformer/dp/B07PPPF1R5/ref=sr_1_6?dib=eyJ2IjoiMSJ9.ghI_8NCu8MWYClVH1bcXae0-G1NHsVMPKXgQ-q9tD7DBjxsd-n2e4GXZyzhj32lWCmUMKNTvmGLgthtkozNnkvRJfBHn4VuSCeTc5lP748T7kJtgdQqg9MH80QXTBMNWupAT-RBnmpw_wBXBO26SKIbj1k64fqcpbisodWHH80xxJPdJFOijPa1IA51xm60Wi2aU2vCne6MmqM3RncHLRYr931SD1UNb9aMjXyOF6U4.dija8_tU-NIlFsudkA1tvV6C6mk8gUO-_lwM8li1rMY&amp;dib_tag=se&amp;keywords=5v%2Bpower%2Bsupply&amp;qid=1743186298&amp;sr=8-6&amp;th=1 " xr:uid="{88BB23CD-312A-41E1-B370-C0D92A466099}"/>
+    <hyperlink ref="C32" r:id="rId53" display="https://www.amazon.com/HiLetgo-Channels-Converter-Bi-Directional-3-3V-5V/dp/B07F7W91LC/ref=sr_1_2?crid=2O7B6QA8ZSPZK&amp;dib=eyJ2IjoiMSJ9.hg1xpaR1IOVH3e6fV4tFyZB8elQluWDLIScr-WIbHEosPLIRhqXG5AnMJTwgM0K6TrBGR457D8AftNCas1RwwWglHyp8zMGTpS2Jwm4xa_uAl0aEMGjby7ffGvEP4lloYctRt9gX4TE3gjllm6sYLU-fsW7zpvcw5ZYESHBPOBCKcQrbrqb3arWPwpjMs7PwokFja-obLRKIr-SuthVfiG0yGem5Rc41xB6eDkr3AZehwq0tgYmv9VxxVa-jlxf9M9Jmhd8G9HvRemxc8IltnV6CNWKiDi1dgnDBhhj15Hs.b7q4qr8rSADKOOdi-2C89QYAixVQ_S86lTmLM2WBijs&amp;dib_tag=se&amp;keywords=logic+converter&amp;qid=1732221329&amp;s=industrial&amp;sprefix=logic+convertyer%2Cindustrial%2C103&amp;sr=1-2" xr:uid="{AA94D625-0126-47B8-979E-9BE236BAD9AD}"/>
+    <hyperlink ref="K17" r:id="rId54" xr:uid="{0F474C1B-53F3-45D5-A2EC-5FEABEC629CC}"/>
+    <hyperlink ref="C47" r:id="rId55" display="https://www.digikey.com/en/products/detail/w-rth-elektronik/691210910002/10668428?gclsrc=aw.ds&amp;&amp;utm_adgroup=&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=PMax%20Supplier_Focus%20Supplier&amp;utm_term=&amp;utm_content=&amp;utm_id=go_cmp-20243063242_adg-_ad-__dev-c_ext-_prd-10668428_sig-CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gad_source=1&amp;gclid=CjwKCAiAw5W-BhAhEiwApv4goNoIras4SeKTARwFArTyBg_WNViqSmUymBOFkEKXv0so_TaGIVohzBoCHrAQAvD_BwE&amp;gclsrc=aw.ds " xr:uid="{DCE5683A-0BC1-49BA-8FB0-36DC1C1C9A9C}"/>
+    <hyperlink ref="C34" r:id="rId56" xr:uid="{A29FBA48-6899-42FA-AA59-0FC1E2A5A45B}"/>
+    <hyperlink ref="K5" r:id="rId57" display="https://www.amazon.com/Klein-Tools-34056-Adjustable-Electrical/dp/B0D98N52HS/ref=sr_1_1?crid=2OB42YRNYW5S8&amp;dib=eyJ2IjoiMSJ9.55eyclIvGQBRs_G9kszoUlEHRgUtyYkcxabPk-sLw5mt7xuGNeudbfTW8xclKppzTejqidNByQBdPqeEXGg2aJrgDuRoxPddnr7un1KzGrHylGN5yiKL4ycDLAz23bHXFS35VarXoP5Hhq810Sdco6qhSeWGVplSUIYpl56zvRZNrenZvPGmvYU7Y6nsIMihDbf5RoNPi8sUcALPKWZoFyR-Fs3jx2RBJISOeui_PdRPNKnGLGC0Uz395rIEcZ1F9icIwzDBX00JzMC1ZjD_KvEf_nXltgLaawa8vee6Efs.PDGEHgTlQjY0Jz82g_64nVgHTsayEsuiw1VPN9n4cXc&amp;dib_tag=se&amp;keywords=klein%2Bferrule%2Bcrimper&amp;qid=1730823384&amp;sprefix=klein%2Bferrule%2Bcrimper%2Caps%2C132&amp;sr=8-1&amp;th=1 " xr:uid="{CEBE3ECF-00C1-476F-B5EA-6B34F3C440E0}"/>
+    <hyperlink ref="K9" r:id="rId58" display="https://www.amazon.com/Ginsco-580-pcs-Assorted-Sleeving/dp/B01MFA3OFA/ref=sr_1_3?crid=19V7T4IBHC5QO&amp;dib=eyJ2IjoiMSJ9.afAtOFc0AWv7IewHnY-SsmFPIWDeFgvxv7nXELH8Q5qH5K9drWIEjyb4PZCDtpgcSjO1zJt_d_d3Bzwc58g899uhvXzTWNoWa7P0XxuvXztW-5Tc85nP2v3ZP7OVkL9CptCT1e2fAdSg9fifPtR8m9aUVniGOD_xVLXrYdiBq6lh_RbbHkqSMJ69bG3sHk4HbEXsrxggq5C19I64px1H3_Ik8TcJWmowUEtAS4Q9W-qfDLzF-ZeqrhVHbQsdU60_CMcyHcb-SzXuOkdEyVk4hxnhYPkE9DVIFlnwUZ_gnFs.KYnfl9oSznG3OdVCEMra_IGu5ndQOaOh0V01hKDX2Cg&amp;dib_tag=se&amp;keywords=heat+shrink&amp;qid=1730826521&amp;s=industrial&amp;sprefix=heat+shrink%2Cindustrial%2C153&amp;sr=1-3" xr:uid="{332F4161-5937-4DDE-ABA6-DACEB1F4794A}"/>
+    <hyperlink ref="K10" r:id="rId59" display="https://www.amazon.com/Wagner-Spraytech-2417344-Included-Settings/dp/B08RHDWTW1/ref=sr_1_11?crid=3ARWBH2CNL2VG&amp;dib=eyJ2IjoiMSJ9.5gm2Lb5w7VJN8eZBOb3sMfrdDu3W3L85PQTIzxzBZJ1vf-jvbS2FqK77wFjT6OZzl6K6ZPfKPxF69vtZoEGLBwa33pNDuaQFZ5d56VcK6EA5FFGA1--hdSnEw3fLJDXu1T8506U6B4hwJnuMIowuy-pqGmMYEgrUzJgewq75UPRynteSSx1o9beXWRFOtetN7sJ8ZCvbI6SIQRS66FWPs_vl_TxDCTjrDPQKyFweQxdffM2MmYMu_eO5yjQidk2oyLK141Wm02_P7ByEzVHzBvW8fuHA4c3B_Zu46wWCCoI.0J-_R-51Hafm74iaH4iqwhrkZ5Q1Y_KjRNfLvM8jnYc&amp;dib_tag=se&amp;keywords=heat+gun&amp;qid=1730826612&amp;s=industrial&amp;sprefix=heat+gun%2Cindustrial%2C132&amp;sr=1-11" xr:uid="{F5E05831-9E24-43B9-94F1-B4BC1AC96D82}"/>
+    <hyperlink ref="K11" r:id="rId60" display="https://www.amazon.com/VISE-GRIP-Stripping-Cutter-8-Inch-2078309/dp/B000JNNWQ2/ref=sr_1_2?crid=2SRELAQ0SJSSX&amp;dib=eyJ2IjoiMSJ9.nG7mDlLX3e8OY6I2TjYCT2FSzLyODDpPex6UnS9dB8ZSP-3DZSkQVn-yGInthfRJK_Of8xmDaaqhT4jhLXSvHyO6EI69a6virDvTLdlxbf1ngpiAjQs3-bOHwDe7vb6w90nbwCbO1LttItJjb9iHGoultOHeluZLJlLzJk4xzY5UfDhbWwEhFaLgMgB_5i5TLu5qOUnejGHsV4K5nAYlFqF68IiAuQ8kcCpQK-0dTqQun1akqTS4dgx4cP2W-BbkYxyu_SpIm9cpJrv_m28fAnH0ydJPD5gvv0pU6kc5380.MnLh1rZQ5i8y79mo0RvgZquA_sAp_v-KzSZImycUxdo&amp;dib_tag=se&amp;keywords=irwin+wire+stripper&amp;qid=1730826958&amp;s=industrial&amp;sprefix=irwin+wire+stipper%2Cindustrial%2C91&amp;sr=1-2" xr:uid="{CD595E57-DC94-4850-8524-5A1DEB057175}"/>
+    <hyperlink ref="K12" r:id="rId61" display="https://www.amazon.com/Haisstronica-Electrical-Connectors-AWG-Tools-Racheting-Tools-Available/dp/B08F3JKDD3/ref=sr_1_5?crid=1UC6EBL5V8RZ&amp;dib=eyJ2IjoiMSJ9.fViKUMP--aXWyr_VSPqdFihmmRK82p3-xep_6UgQhjDmE4EGGDd0-VEfAWJH_2mkTtPo3hrn-Xjo7ioxvPrUX0cyXLrCA085qarrwngsgJhVZKWjQdCGzM1VtfnKeWQyPkH1l5eFuRy8m-gggxen_-oBrfY57oEGfJPVl_9QkByDRNqlbX7ayxV95AD9q55o-eUJR0byooY9wqq8VXvLclS6gejWED1xpqlQe_Yi-hdIUKvw2g17SKPIJFYpOUh-aUsmMh7lBM3Rn7ZnY6d1lU1h65gSrMFxrFAzXbBxYpI.2fSr4cew3Mlijb7rQiZIXFl97Cz8Kq21oEmZlfD39QA&amp;dib_tag=se&amp;keywords=crimping%2Btool&amp;qid=1730827014&amp;s=industrial&amp;sprefix=crimp%2Cindustrial%2C124&amp;sr=1-5&amp;th=1" xr:uid="{85E51D7B-B8E9-4DCD-BD2E-91CCEC064732}"/>
+    <hyperlink ref="K15" r:id="rId62" display="https://www.amazon.com/WEICON-Stripper-Adjustable-0-2-6-0-Stripping/dp/B001NUMVHQ/ref=sr_1_5?crid=1SSXPMUMUE8CN&amp;dib=eyJ2IjoiMSJ9.dlOqGoMqoa_J0KSIP8b8Qbu_4eK_g9aMoAPXb0geqceQW-YR7aelaKVCxL2tekl_qTBB43ciINtSLHJSQG6Y7PoXsAKTjR0Vo6bTGJrFUiXXhUkg96MaCEz8OnQ8WY-HcVJ2TOCkWjl8zYWb8igBh3vDa65alauML_lvmK4sNW2Hajnj_eGwldJ1C1nnfpdJB6Z8Xff_a30CAQlvA6QxYKJyBTg1alIgilMrQafgNCcujVp2rrIHnhGbFmSlwltAwRIe1eQiGTCgM3PWN_795FsBQ6j93SaJkyflOtfucF8.Tb3cTlKfvm5Cy0Fp4c7TNNFBEcYGjRD7YrqefRf77g4&amp;dib_tag=se&amp;keywords=weicon+wire+stripping+tool&amp;qid=1732209102&amp;sprefix=weicon+wire+stripping+tool%2Caps%2C104&amp;sr=8-5" xr:uid="{861EFE74-739C-4CD2-9085-6EFE07B3481C}"/>
+    <hyperlink ref="K34" r:id="rId63" xr:uid="{77D63543-B36B-4B98-A73E-F3857D81E695}"/>
+    <hyperlink ref="K30" r:id="rId64" xr:uid="{1BB7CBF3-BD44-4F4B-8FC4-904F64FC7D13}"/>
+    <hyperlink ref="K27" r:id="rId65" xr:uid="{FF699E51-8F2F-483B-80C4-2D079998FED3}"/>
+    <hyperlink ref="K31" r:id="rId66" xr:uid="{A1F8AA51-ED01-4671-ADB1-5036FF8B669F}"/>
+    <hyperlink ref="K23" r:id="rId67" xr:uid="{B44ED290-8CBF-48A9-8EFB-3CB4B0760A72}"/>
+    <hyperlink ref="K25" r:id="rId68" xr:uid="{EDDA737D-4038-4DB0-B323-C2D73FD73576}"/>
+    <hyperlink ref="K20" r:id="rId69" display="https://www.amazon.com/Klein-Tools-MM325-Multimeter-Manual-Ranging/dp/B0B57L9FNL?dib=eyJ2IjoiMSJ9.XOXQgFuugT7fSqk2JXgR554EvBn03HSeasFjjzBAbBJ0lnoLvn4AnJEthmy5GYMbfcc-d9gjjvtPqgpSKu3iK9JyBR2HwE_gjWGN0MWg07nigXvQ43521m39rI3_AeWTBSKvCArU06kfWba8iPBP_q6kwcBoJ0bKGpUibs7qIEz0JBvM_m3cfmO2PytEFbWld5CguH1PB6VdvsJfuMeUCKj1nctG-6zPVqUdWNu5gjviDmequn_waQEOMR665LW-ucWCwNcug5d1Rem35c7HMDSqCAqTXvos7iSVccjXJ1I.tr3V0PDK2DnUmPDVm8XLG7GKOVNrAFyMQ0FWyT43FtA&amp;dib_tag=se&amp;keywords=multi%2Bmeter&amp;qid=1733388969&amp;sr=8-7&amp;th=1 " xr:uid="{6844E477-F27E-4A9B-B552-C8FC9B6A7C36}"/>
+    <hyperlink ref="K14" r:id="rId70" display="https://www.amazon.com/Amazon-Basics-Ratcheting-Electronics-Screwdriver/dp/B07V4TFWFZ/ref=sr_1_5?crid=5FDDKZ08W2XH&amp;dib=eyJ2IjoiMSJ9.A3n1jTNvIcpz61ypsmX9MBC_oUMTAhq1t44j_1J2e-nP5QHjm-pYiYJpVEusn6bIqa3PCg3Wthb6yyUmN9i-KhuNmdX26_MOiWL-RM2nz3ddQW5BbA2A3qcnpi5yby99hcMeEY3ZtnVl8snxyRqqeIoYNiIK2Dh6dIkqu7FTlrOT6cZz3UlOXKTjSAhmdZxjc5rvX9_XaSQgv_geb0S7uFEpcu9cLsoPGXJ3e7MoxcAQBeBsPPNbonfZ3TR-ewlb8XIDRBg0v7Zivipx5bQT51QYOTQBfPiJ4ix71GX2imo.4o19nzIzWNm0dO5IQWSfMam_e1TDYdj-YMl6nwuPwfw&amp;dib_tag=se&amp;keywords=small%2Belectronics%2Bscrew%2Bdriver%2Bset&amp;qid=1732221537&amp;s=industrial&amp;sprefix=small%2Belectronics%2Bscrew%2Bdriver%2Bset%2Cindustrial%2C100&amp;sr=1-5&amp;th=1" xr:uid="{998DFED7-FD15-4152-BFA6-54275B60F63A}"/>
+    <hyperlink ref="K8" r:id="rId71" display="https://www.amazon.com/MAIYUM-63-37-Solder-Electrical-Soldering/dp/B075WB98FJ/ref=sr_1_4?crid=FUL9XTKIEH0Q&amp;dib=eyJ2IjoiMSJ9.SSzB0hv2YBXV9gPCxCyydd5S_u5flP9lHY5GxroTHXWE-O_gYdIn4eeIMj1MxksAaIi1XAIo_B_iaJ4XYEW_46uVfck5Fk-qgWP2zm2sViFlUXR1GlRH2Jxryx5KdgBpWLBjxrFU6KkL22wi1mdGe0nLo4hcc14I1IP5ZsyRv-C8oUQPfZciMrOodLex43BGja33E0IkuYqS3dCAs3Y-oD3ghP974Cu5_ptNdl8G1-wMVZ3eIVDorhDZX5_grSmX0xlP_xCphsipUCLxmC7mEFWguLxG_b8EZ0OO87S_9Fw.KsUflA4BP63mIa38we7VsxqUAglWv377w8Y-exq7TQQ&amp;dib_tag=se&amp;keywords=solder%2Bwith%2Bflux&amp;qid=1730823776&amp;s=hi&amp;sprefix=solder%2Bwith%2Bflux%2Ctools%2C101&amp;sr=1-4&amp;th=1" xr:uid="{0357DF8A-D0E5-42BB-92C4-6DBD9C45345F}"/>
+    <hyperlink ref="K33" r:id="rId72" xr:uid="{99D8A20C-917E-4522-83A0-C319C991F299}"/>
+    <hyperlink ref="K22" r:id="rId73" xr:uid="{294EC5C0-0591-4D84-BD56-9ACE6CDE80BA}"/>
+    <hyperlink ref="K19" r:id="rId74" xr:uid="{CF48C670-F50C-4DF9-B593-ED5D439D7822}"/>
+    <hyperlink ref="K16" r:id="rId75" display="https://www.amazon.com/Milwaukee-M12-Lithium-Ion-Cordless-Kit/dp/B07J1DCM59/ref=sr_1_2?crid=T8KHPS70XKI2&amp;dib=eyJ2IjoiMSJ9.dfyp5QTjupoTHgodWAHsGfuOMaTLJm7DDsIUr11ufFsYHAn0rfuv6naAjnMC5JCAroszQI_218d92cwRA7Ob-4Lz7I6szZUCh4V-Z7ZiJOviGsbGMlQhVkePjD_JzUhnHe9X52TEY5FQ5E-T-ddnBDoRgmHk7PcZexXQFtEwAZ2Pznq8Er2Mt_hRvOwk3S6nx8NxhBgztopKhQS32-QfrY9DEWxtJCzDil2auIQ4NeaU4I50CIlwfKO22MPlLHgcgGcWC-4jnHwziasnQpWdtp0eitiu74YKIoY56dKatdI.1UJ1NUvjpquCkQiTSeXnAjDQCRrcaDytyoSPdwmhfho&amp;dib_tag=se&amp;keywords=milwaukee+compressor+m12&amp;qid=1744600915&amp;s=hi&amp;sprefix=milwaukee+compressor+m12%2Ctools%2C78&amp;sr=1-2 " xr:uid="{1D205F97-D9EF-4167-A62C-09373C316758}"/>
+    <hyperlink ref="K28" r:id="rId76" xr:uid="{5F7730D8-6AC1-4AFC-BDF9-357875FD1123}"/>
+    <hyperlink ref="K29" r:id="rId77" xr:uid="{7D645F8A-33CD-418D-8D23-F32705DFD52D}"/>
+    <hyperlink ref="K32" r:id="rId78" xr:uid="{72352CC7-698C-4AF0-BCF4-715EF6461852}"/>
+    <hyperlink ref="C76" r:id="rId79" xr:uid="{D0BFB25A-21DF-4F2E-8B59-E3DD05C3B098}"/>
+    <hyperlink ref="C75" r:id="rId80" xr:uid="{D5A5F088-A84E-4368-83A3-93B6A7392B62}"/>
+    <hyperlink ref="C77" r:id="rId81" xr:uid="{03C53325-8F52-47AD-98AA-5B3BD79FCDF7}"/>
+    <hyperlink ref="C78" r:id="rId82" xr:uid="{BC613FBE-2FF7-47F4-BA8F-9A2B780CBF4D}"/>
+    <hyperlink ref="C79" r:id="rId83" xr:uid="{18524F55-8313-44A2-98E0-8D3476379625}"/>
+    <hyperlink ref="C80" r:id="rId84" xr:uid="{C5B457D0-EBF2-4473-8DE5-A2CBF0192FC7}"/>
+    <hyperlink ref="C81" r:id="rId85" xr:uid="{F9DC2B0F-6CC2-4333-B6A0-4C461C26A42D}"/>
+    <hyperlink ref="C35" r:id="rId86" xr:uid="{B350E38A-0704-49E3-B0A0-6AC64705FFA8}"/>
+    <hyperlink ref="K24" r:id="rId87" xr:uid="{38DE31D1-83D2-44D7-B2DB-47B0912A74D8}"/>
+    <hyperlink ref="K42" r:id="rId88" xr:uid="{99DE23E2-FB55-46E7-81C4-10D9C3F12704}"/>
+    <hyperlink ref="K43" r:id="rId89" xr:uid="{C65D4C28-A0F4-4162-A2A5-E142AED72659}"/>
+    <hyperlink ref="K47" r:id="rId90" xr:uid="{DAB44B0A-B63A-4471-ADE7-6D09C28FFC68}"/>
+    <hyperlink ref="K48" r:id="rId91" xr:uid="{D3082204-ACAD-465A-B054-F2BD8FB8F1EB}"/>
+    <hyperlink ref="C33" r:id="rId92" xr:uid="{DD69F44F-F79E-4411-A5F6-7F4820E93E7C}"/>
+    <hyperlink ref="K54" r:id="rId93" xr:uid="{08CDA0A7-76D0-4386-8DF9-D40020E4F6BB}"/>
+    <hyperlink ref="K56" r:id="rId94" xr:uid="{B817C2C0-888A-41EE-BB96-AA202FF7D26F}"/>
+    <hyperlink ref="K7" r:id="rId95" xr:uid="{403CBC77-BB8E-482D-ADB0-566010CFFBFE}"/>
+    <hyperlink ref="C101" r:id="rId96" xr:uid="{66B61CB6-8DEE-47E0-8F58-13DFE696A594}"/>
+    <hyperlink ref="C40" r:id="rId97" xr:uid="{E912526C-B82A-4A44-8481-EFACD695EA8D}"/>
+    <hyperlink ref="C44" r:id="rId98" xr:uid="{E865141B-878A-4CD6-B122-3ADC6852D520}"/>
+    <hyperlink ref="K58" r:id="rId99" location="tabbed-customerreviews " xr:uid="{24F44932-6634-42FE-8337-20CA3C2EC1E4}"/>
+    <hyperlink ref="C74" r:id="rId100" xr:uid="{326567BB-9D82-4E92-ACC4-530A6BCCFC38}"/>
+    <hyperlink ref="C17" r:id="rId101" display="https://www.amazon.com/Amazon-Basics-Ethernet-High-Speed-Snagless/dp/B089MGH8W3/ref=sr_1_6?crid=15O99JJ9VZUDS&amp;dib=eyJ2IjoiMSJ9.Qrm0YFmTEww5DZc4mrTYoBW2ITYU8YDRmdb4HE4nmukqEngrlTfGgHLb5uoFzqyB8DY16yxmWqTI2jhY13tKSS_gVPXMFmLrV8CwN6seDqr3fe6RoYGbAYOThLs_GPXGD9BG1xBtpSbQCaOmPeX6onzLKT90VpHEp8g8rhIrccYIWeUVb1y9yQszCgP-aLtJNIsqNx1o-8aHQGBnXQxbEdINQFklL4UDCld4WzwhnXy0xN-YFaHdxcyM5kmfmoYQEhD8UEUeVcULGl7eYpTBQi8RxGrjeWwsXTnPG7oVA4s.SJ0prHAqUML_3kLplif-xyTccwFoBx4GiK1cGmdOyLI&amp;dib_tag=se&amp;keywords=ethernet%2Bcable&amp;qid=1752782277&amp;s=electronics&amp;sprefix=ethernet%2Celectronics%2C124&amp;sr=1-6&amp;th=1 " xr:uid="{83A0A177-ED38-4C3C-B1E2-6D1A2C00DD2C}"/>
+    <hyperlink ref="K13" r:id="rId102" display="https://www.amazon.com/Powerbuilt-Piece-Stubby-Long-Wrench/dp/B07N8F7W7K/ref=sr_1_19?dib=eyJ2IjoiMSJ9.URwdEPQXxCMLBhxvS9K5ftG6hwdCaLy_xWZ0vGXOdbuaNrb8XAmO4DQhIxovkvuXsRHPo7oCqjy9Wwt6H6QvZeRYOqVzaLjKkETlnA83OkSSXLxlPpzMt1Qy3kJt-T7GsO_Bq0c0QItERYLb6VTtZmMQdlqDEtc5mdwZiAksW1Y2IKpS2cr-V_j1_L0qMFZKPy2WuoytvNj5MEhK80MOfMrjnaTsJLpB9Io2Jt4xFodm6EN5AwCetZhDdsJTY6jdeOdEdPi6COl5b1RI-6XJHwylh2H13M74HgAUrEaRfoY.bAaypnaW3mj6ulkwXEha2QJSRXBFsgrmQMhuIwb4S2o&amp;dib_tag=se&amp;keywords=stubby%2Ballen%2Bwrench%2Bset&amp;qid=1752911269&amp;sr=8-19&amp;th=1 " xr:uid="{F2200CD7-83CF-497A-91E0-EF5B6CA80C0C}"/>
+    <hyperlink ref="K44" r:id="rId103" xr:uid="{F40A70E6-7F31-454F-9558-A7291A2A2DCF}"/>
+    <hyperlink ref="K45" r:id="rId104" xr:uid="{4A6F6959-0930-44EE-A971-B3EF13DA9390}"/>
+    <hyperlink ref="C51" r:id="rId105" xr:uid="{7963F571-8F62-4D9F-BEF7-F802CD4D18FC}"/>
+    <hyperlink ref="C93" r:id="rId106" xr:uid="{5A200CB5-C655-478F-B00B-2E82D8CC5C77}"/>
+    <hyperlink ref="C94:C95" r:id="rId107" display="https://8020.net/20-2020.html " xr:uid="{94C82CF7-4209-49DE-A286-0E429370F935}"/>
+    <hyperlink ref="C96" r:id="rId108" xr:uid="{3653483D-B8D7-4970-8BE1-067F3CE7FF42}"/>
+    <hyperlink ref="C87" r:id="rId109" xr:uid="{E1AC3FAD-797D-4D40-89E1-E0B078028B08}"/>
+    <hyperlink ref="C66" r:id="rId110" xr:uid="{8B53B0C9-AEB9-4C25-B4D5-D709A9909BD6}"/>
+    <hyperlink ref="C70" r:id="rId111" xr:uid="{2521E3A3-9809-485D-8952-C732415A0425}"/>
+    <hyperlink ref="K41" r:id="rId112" xr:uid="{BE5F57C8-C44E-47CF-B992-FEB02C6C001F}"/>
+    <hyperlink ref="K72" r:id="rId113" xr:uid="{A8E5D7AD-E110-498C-AD66-4031E7159275}"/>
+    <hyperlink ref="K74" r:id="rId114" xr:uid="{686F1C5B-AD14-408B-9AF5-1B4D26D75248}"/>
+    <hyperlink ref="K78" r:id="rId115" xr:uid="{A8336809-C542-4E15-9187-DB4F43D26933}"/>
+    <hyperlink ref="K79" r:id="rId116" xr:uid="{49B9B422-CDDA-427C-82B9-729F2266C333}"/>
+    <hyperlink ref="K80" r:id="rId117" xr:uid="{3E0AC7C3-82FC-4B11-AD25-3DE1DD9499EF}"/>
+    <hyperlink ref="C97" r:id="rId118" xr:uid="{2C6B41AF-87E5-4DA5-9686-67EEDF628339}"/>
+    <hyperlink ref="C36" r:id="rId119" xr:uid="{1800FA32-51EA-41AB-8A1C-BCA281C1CA6B}"/>
+    <hyperlink ref="K75" r:id="rId120" xr:uid="{D1950805-AAE5-4A33-803E-9858D08F12A2}"/>
+    <hyperlink ref="K73" r:id="rId121" xr:uid="{01D963BB-A0C2-4C40-BA01-8B0B76381716}"/>
+    <hyperlink ref="K76" r:id="rId122" xr:uid="{D9B5F8EE-01B9-4AA5-9918-F987CA2D7884}"/>
+    <hyperlink ref="C99" r:id="rId123" display="https://czh-labs.com/products/terminal-block-breakout-board-module-for-teensy-41-screw-mount-version?gad_source=1&amp;gad_campaignid=17335691898&amp;gbraid=0AAAAADQKSWrLA97xSr9gmMM99UCSLmr58&amp;gclid=CjwKCAjwp_LDBhBCEiwAK7FnklUhjhvxFgmMMu0XiWu80nKxdv4QNWNVcUvZhioyk86weMe15LnzoRoClR4QAvD_BwE " xr:uid="{944A4911-F6CF-4EB3-82C2-8B8DAFBE56E9}"/>
+    <hyperlink ref="C37" r:id="rId124" xr:uid="{737F7509-05EB-4CE3-AA5B-929CB63FC161}"/>
+    <hyperlink ref="C8" r:id="rId125" xr:uid="{64F7CD2D-21CD-4075-A33B-B33CA2888693}"/>
+    <hyperlink ref="C41" r:id="rId126" xr:uid="{C902CDD9-1F9D-452D-9583-852C1F7B1429}"/>
+    <hyperlink ref="C45" r:id="rId127" xr:uid="{7DA2E625-AACF-4DED-9279-AA3DDE590F85}"/>
+    <hyperlink ref="C42" r:id="rId128" xr:uid="{EA50026D-4CC0-4262-AA82-1A8C4D553DA4}"/>
+    <hyperlink ref="C43" r:id="rId129" xr:uid="{21A1C6AF-63D2-4FA9-AD9E-D674C1D15883}"/>
+    <hyperlink ref="C39" r:id="rId130" xr:uid="{63D3DD15-6374-4167-9E3E-2CFCBF201E30}"/>
+    <hyperlink ref="C19" r:id="rId131" xr:uid="{25851340-5A38-4A26-A3FC-843A61F946D3}"/>
+    <hyperlink ref="C28" r:id="rId132" xr:uid="{70E5CFA1-08D5-4DBE-A184-47152ED1625E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId137"/>
+  <pageSetup orientation="portrait" r:id="rId133"/>
 </worksheet>
 </file>
 
@@ -5852,15 +5764,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="fb0bfce0-b493-4733-b695-336371de64d4" xsi:nil="true"/>
@@ -5869,6 +5772,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5891,14 +5803,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD534FFF-F9D4-45E9-B4A8-C5178968AA79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5907,4 +5811,12 @@
     <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/LC-CNC-BoM.xlsx
+++ b/LC-CNC-BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk.sharepoint.com/sites/UT_DesktopMillingMachine/Shared Documents/General/GitHub-LC_CNC/LC-CNC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk.sharepoint.com/sites/UT_DesktopMillingMachine/Shared Documents/General/GitHub-Landon/LC-CNC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1179" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E288FA8-4855-4458-9FDF-A6624BACA694}"/>
+  <xr:revisionPtr revIDLastSave="1181" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03A9831F-5709-4459-843B-4295C5CE50DA}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1035" yWindow="1680" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1715,14 +1715,23 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1736,31 +1745,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2060,24 +2060,24 @@
       <c r="B2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="58" t="s">
         <v>180</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="74"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="19">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="55" t="s">
+      <c r="K2" s="71" t="s">
         <v>264</v>
       </c>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="57"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="73"/>
     </row>
     <row r="3" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="43" t="s">
@@ -2118,7 +2118,7 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="61" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="67"/>
@@ -2126,14 +2126,14 @@
       <c r="E4" s="67"/>
       <c r="F4" s="67"/>
       <c r="G4" s="68"/>
-      <c r="J4" s="58" t="s">
+      <c r="J4" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="60"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="63"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
@@ -2217,14 +2217,14 @@
       </c>
     </row>
     <row r="7" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="60"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63"/>
       <c r="J7" s="2" t="s">
         <v>171</v>
       </c>
@@ -2784,14 +2784,14 @@
         <f t="shared" si="4"/>
         <v>69.38</v>
       </c>
-      <c r="J21" s="58" t="s">
+      <c r="J21" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="60"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="63"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
@@ -2981,14 +2981,14 @@
         <f t="shared" si="6"/>
         <v>8.99</v>
       </c>
-      <c r="J26" s="58" t="s">
+      <c r="J26" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="59"/>
-      <c r="O26" s="60"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="63"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
@@ -3042,13 +3042,14 @@
         <v>9</v>
       </c>
       <c r="E28" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="5">
         <v>8.99</v>
       </c>
       <c r="G28" s="5">
-        <v>8.99</v>
+        <f>E28*F28</f>
+        <v>17.98</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>185</v>
@@ -3349,13 +3350,13 @@
         <f t="shared" ref="G36:G37" si="11">E36*F36</f>
         <v>13.99</v>
       </c>
-      <c r="J36" s="61" t="s">
+      <c r="J36" s="64" t="s">
         <v>189</v>
       </c>
-      <c r="K36" s="62"/>
-      <c r="L36" s="62"/>
-      <c r="M36" s="62"/>
-      <c r="N36" s="63"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="66"/>
       <c r="O36" s="14">
         <f>SUM(O5:O35)</f>
         <v>1259.6799999999998</v>
@@ -3407,13 +3408,13 @@
       <c r="J38" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="K38" s="55" t="s">
+      <c r="K38" s="71" t="s">
         <v>266</v>
       </c>
-      <c r="L38" s="56"/>
-      <c r="M38" s="56"/>
-      <c r="N38" s="56"/>
-      <c r="O38" s="57"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="73"/>
     </row>
     <row r="39" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
@@ -3476,7 +3477,7 @@
         <f t="shared" si="12"/>
         <v>39.99</v>
       </c>
-      <c r="J40" s="58" t="s">
+      <c r="J40" s="61" t="s">
         <v>209</v>
       </c>
       <c r="K40" s="67"/>
@@ -3691,7 +3692,7 @@
       </c>
     </row>
     <row r="46" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="58" t="s">
+      <c r="B46" s="61" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="67"/>
@@ -3699,7 +3700,7 @@
       <c r="E46" s="67"/>
       <c r="F46" s="67"/>
       <c r="G46" s="68"/>
-      <c r="J46" s="58" t="s">
+      <c r="J46" s="61" t="s">
         <v>100</v>
       </c>
       <c r="K46" s="67"/>
@@ -3749,14 +3750,14 @@
       </c>
     </row>
     <row r="48" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="58" t="s">
+      <c r="B48" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="60"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="63"/>
       <c r="J48" s="2" t="s">
         <v>169</v>
       </c>
@@ -3797,13 +3798,13 @@
         <f t="shared" ref="G49:G101" si="14">E49*F49</f>
         <v>29.54</v>
       </c>
-      <c r="J49" s="61" t="s">
+      <c r="J49" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="K49" s="62"/>
-      <c r="L49" s="62"/>
-      <c r="M49" s="62"/>
-      <c r="N49" s="63"/>
+      <c r="K49" s="65"/>
+      <c r="L49" s="65"/>
+      <c r="M49" s="65"/>
+      <c r="N49" s="66"/>
       <c r="O49" s="14">
         <f>SUM(O40:O48)</f>
         <v>319.13</v>
@@ -3855,13 +3856,13 @@
       <c r="J51" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K51" s="55" t="s">
+      <c r="K51" s="71" t="s">
         <v>277</v>
       </c>
-      <c r="L51" s="56"/>
-      <c r="M51" s="56"/>
-      <c r="N51" s="56"/>
-      <c r="O51" s="57"/>
+      <c r="L51" s="72"/>
+      <c r="M51" s="72"/>
+      <c r="N51" s="72"/>
+      <c r="O51" s="73"/>
     </row>
     <row r="52" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
@@ -3924,7 +3925,7 @@
         <f t="shared" si="14"/>
         <v>15.24</v>
       </c>
-      <c r="J53" s="58" t="s">
+      <c r="J53" s="61" t="s">
         <v>209</v>
       </c>
       <c r="K53" s="67"/>
@@ -3995,7 +3996,7 @@
         <f t="shared" si="14"/>
         <v>41.8</v>
       </c>
-      <c r="J55" s="58" t="s">
+      <c r="J55" s="61" t="s">
         <v>100</v>
       </c>
       <c r="K55" s="67"/>
@@ -4066,7 +4067,7 @@
         <f t="shared" ref="G57:G64" si="16">E57*F57</f>
         <v>19.100000000000001</v>
       </c>
-      <c r="J57" s="58" t="s">
+      <c r="J57" s="61" t="s">
         <v>230</v>
       </c>
       <c r="K57" s="67"/>
@@ -4137,13 +4138,13 @@
         <f t="shared" si="16"/>
         <v>8.33</v>
       </c>
-      <c r="J59" s="61" t="s">
+      <c r="J59" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="K59" s="62"/>
-      <c r="L59" s="62"/>
-      <c r="M59" s="62"/>
-      <c r="N59" s="63"/>
+      <c r="K59" s="65"/>
+      <c r="L59" s="65"/>
+      <c r="M59" s="65"/>
+      <c r="N59" s="66"/>
       <c r="O59" s="14">
         <f>SUM(O54,O58)</f>
         <v>961.95</v>
@@ -4195,13 +4196,13 @@
       <c r="J61" s="33" t="s">
         <v>250</v>
       </c>
-      <c r="K61" s="55" t="s">
+      <c r="K61" s="71" t="s">
         <v>286</v>
       </c>
-      <c r="L61" s="56"/>
-      <c r="M61" s="56"/>
-      <c r="N61" s="56"/>
-      <c r="O61" s="57"/>
+      <c r="L61" s="72"/>
+      <c r="M61" s="72"/>
+      <c r="N61" s="72"/>
+      <c r="O61" s="73"/>
     </row>
     <row r="62" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="16" t="s">
@@ -4264,14 +4265,14 @@
         <f t="shared" si="16"/>
         <v>12.36</v>
       </c>
-      <c r="J63" s="58" t="s">
+      <c r="J63" s="61" t="s">
         <v>246</v>
       </c>
-      <c r="K63" s="75"/>
-      <c r="L63" s="75"/>
-      <c r="M63" s="75"/>
-      <c r="N63" s="75"/>
-      <c r="O63" s="76"/>
+      <c r="K63" s="69"/>
+      <c r="L63" s="69"/>
+      <c r="M63" s="69"/>
+      <c r="N63" s="69"/>
+      <c r="O63" s="70"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
@@ -4417,13 +4418,13 @@
         <f t="shared" si="19"/>
         <v>13.4</v>
       </c>
-      <c r="J67" s="61" t="s">
+      <c r="J67" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="K67" s="62"/>
-      <c r="L67" s="62"/>
-      <c r="M67" s="62"/>
-      <c r="N67" s="63"/>
+      <c r="K67" s="65"/>
+      <c r="L67" s="65"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="66"/>
       <c r="O67" s="32">
         <f>SUM(O64:O66)</f>
         <v>517</v>
@@ -4475,13 +4476,13 @@
       <c r="J69" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="K69" s="55" t="s">
+      <c r="K69" s="71" t="s">
         <v>276</v>
       </c>
-      <c r="L69" s="56"/>
-      <c r="M69" s="56"/>
-      <c r="N69" s="56"/>
-      <c r="O69" s="57"/>
+      <c r="L69" s="72"/>
+      <c r="M69" s="72"/>
+      <c r="N69" s="72"/>
+      <c r="O69" s="73"/>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
@@ -4544,14 +4545,14 @@
         <f t="shared" si="14"/>
         <v>27.76</v>
       </c>
-      <c r="J71" s="69" t="s">
+      <c r="J71" s="74" t="s">
         <v>275</v>
       </c>
-      <c r="K71" s="70"/>
-      <c r="L71" s="70"/>
-      <c r="M71" s="70"/>
-      <c r="N71" s="70"/>
-      <c r="O71" s="71"/>
+      <c r="K71" s="75"/>
+      <c r="L71" s="75"/>
+      <c r="M71" s="75"/>
+      <c r="N71" s="75"/>
+      <c r="O71" s="76"/>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
@@ -4735,7 +4736,7 @@
         <v>2.34</v>
       </c>
       <c r="G76" s="6">
-        <f t="shared" ref="G76:G82" si="22">E76*F76</f>
+        <f t="shared" ref="G76:G81" si="22">E76*F76</f>
         <v>7.02</v>
       </c>
       <c r="J76" s="2" t="s">
@@ -4779,14 +4780,14 @@
         <f t="shared" si="22"/>
         <v>7.02</v>
       </c>
-      <c r="J77" s="69" t="s">
+      <c r="J77" s="74" t="s">
         <v>283</v>
       </c>
-      <c r="K77" s="70"/>
-      <c r="L77" s="70"/>
-      <c r="M77" s="70"/>
-      <c r="N77" s="70"/>
-      <c r="O77" s="71"/>
+      <c r="K77" s="75"/>
+      <c r="L77" s="75"/>
+      <c r="M77" s="75"/>
+      <c r="N77" s="75"/>
+      <c r="O77" s="76"/>
     </row>
     <row r="78" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="2" t="s">
@@ -4931,13 +4932,13 @@
         <f t="shared" si="22"/>
         <v>9.58</v>
       </c>
-      <c r="J81" s="61" t="s">
+      <c r="J81" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="K81" s="62"/>
-      <c r="L81" s="62"/>
-      <c r="M81" s="62"/>
-      <c r="N81" s="62"/>
+      <c r="K81" s="65"/>
+      <c r="L81" s="65"/>
+      <c r="M81" s="65"/>
+      <c r="N81" s="65"/>
       <c r="O81" s="54">
         <f>SUM(O72:O80)</f>
         <v>411.5</v>
@@ -5150,14 +5151,14 @@
       </c>
     </row>
     <row r="92" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="58" t="s">
+      <c r="B92" s="61" t="s">
         <v>254</v>
       </c>
-      <c r="C92" s="59"/>
-      <c r="D92" s="59"/>
-      <c r="E92" s="59"/>
-      <c r="F92" s="59"/>
-      <c r="G92" s="60"/>
+      <c r="C92" s="62"/>
+      <c r="D92" s="62"/>
+      <c r="E92" s="62"/>
+      <c r="F92" s="62"/>
+      <c r="G92" s="63"/>
     </row>
     <row r="93" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B93" s="16" t="s">
@@ -5270,14 +5271,14 @@
       </c>
     </row>
     <row r="98" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="58" t="s">
+      <c r="B98" s="61" t="s">
         <v>298</v>
       </c>
-      <c r="C98" s="59"/>
-      <c r="D98" s="59"/>
-      <c r="E98" s="59"/>
-      <c r="F98" s="59"/>
-      <c r="G98" s="60"/>
+      <c r="C98" s="62"/>
+      <c r="D98" s="62"/>
+      <c r="E98" s="62"/>
+      <c r="F98" s="62"/>
+      <c r="G98" s="63"/>
     </row>
     <row r="99" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="2" t="s">
@@ -5302,14 +5303,14 @@
       </c>
     </row>
     <row r="100" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="58" t="s">
+      <c r="B100" s="61" t="s">
         <v>235</v>
       </c>
-      <c r="C100" s="59"/>
-      <c r="D100" s="59"/>
-      <c r="E100" s="59"/>
-      <c r="F100" s="59"/>
-      <c r="G100" s="60"/>
+      <c r="C100" s="62"/>
+      <c r="D100" s="62"/>
+      <c r="E100" s="62"/>
+      <c r="F100" s="62"/>
+      <c r="G100" s="63"/>
     </row>
     <row r="101" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="2" t="s">
@@ -5334,42 +5335,42 @@
       </c>
     </row>
     <row r="102" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="64" t="s">
+      <c r="B102" s="55" t="s">
         <v>269</v>
       </c>
-      <c r="C102" s="65"/>
-      <c r="D102" s="65"/>
-      <c r="E102" s="65"/>
-      <c r="F102" s="66"/>
+      <c r="C102" s="56"/>
+      <c r="D102" s="56"/>
+      <c r="E102" s="56"/>
+      <c r="F102" s="57"/>
       <c r="G102" s="21">
         <f>SUM(G5:G101)</f>
-        <v>2261.0660000000007</v>
+        <v>2270.0560000000005</v>
       </c>
     </row>
     <row r="103" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="64" t="s">
+      <c r="B103" s="55" t="s">
         <v>270</v>
       </c>
-      <c r="C103" s="65"/>
-      <c r="D103" s="65"/>
-      <c r="E103" s="65"/>
-      <c r="F103" s="66"/>
+      <c r="C103" s="56"/>
+      <c r="D103" s="56"/>
+      <c r="E103" s="56"/>
+      <c r="F103" s="57"/>
       <c r="G103" s="52">
         <f>(SUM(G5:G101))/G2</f>
-        <v>2261.0660000000007</v>
+        <v>2270.0560000000005</v>
       </c>
     </row>
     <row r="104" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="64" t="s">
+      <c r="B104" s="55" t="s">
         <v>260</v>
       </c>
-      <c r="C104" s="65"/>
-      <c r="D104" s="65"/>
-      <c r="E104" s="65"/>
-      <c r="F104" s="66"/>
+      <c r="C104" s="56"/>
+      <c r="D104" s="56"/>
+      <c r="E104" s="56"/>
+      <c r="F104" s="57"/>
       <c r="G104" s="53">
         <f>G103+O67</f>
-        <v>2778.0660000000007</v>
+        <v>2787.0560000000005</v>
       </c>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
@@ -5378,6 +5379,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="B92:G92"/>
+    <mergeCell ref="J67:N67"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="J49:N49"/>
+    <mergeCell ref="J53:O53"/>
+    <mergeCell ref="J55:O55"/>
+    <mergeCell ref="J57:O57"/>
+    <mergeCell ref="J59:N59"/>
+    <mergeCell ref="J71:O71"/>
+    <mergeCell ref="K69:O69"/>
+    <mergeCell ref="J81:N81"/>
+    <mergeCell ref="K51:O51"/>
+    <mergeCell ref="K38:O38"/>
+    <mergeCell ref="J77:O77"/>
+    <mergeCell ref="B98:G98"/>
     <mergeCell ref="B104:F104"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="B102:F102"/>
@@ -5394,22 +5411,6 @@
     <mergeCell ref="J46:O46"/>
     <mergeCell ref="J63:O63"/>
     <mergeCell ref="K61:O61"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="B92:G92"/>
-    <mergeCell ref="J67:N67"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="J49:N49"/>
-    <mergeCell ref="J53:O53"/>
-    <mergeCell ref="J55:O55"/>
-    <mergeCell ref="J57:O57"/>
-    <mergeCell ref="J59:N59"/>
-    <mergeCell ref="J71:O71"/>
-    <mergeCell ref="K69:O69"/>
-    <mergeCell ref="J81:N81"/>
-    <mergeCell ref="K51:O51"/>
-    <mergeCell ref="K38:O38"/>
-    <mergeCell ref="J77:O77"/>
-    <mergeCell ref="B98:G98"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{182E6AD4-2BF8-453D-8168-0C5471656634}"/>
@@ -5764,6 +5765,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="fb0bfce0-b493-4733-b695-336371de64d4" xsi:nil="true"/>
@@ -5772,15 +5782,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5803,6 +5804,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD534FFF-F9D4-45E9-B4A8-C5178968AA79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5811,12 +5820,4 @@
     <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/LC-CNC-BoM.xlsx
+++ b/LC-CNC-BoM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk.sharepoint.com/sites/UT_DesktopMillingMachine/Shared Documents/General/GitHub-Landon/LC-CNC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1181" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03A9831F-5709-4459-843B-4295C5CE50DA}"/>
+  <xr:revisionPtr revIDLastSave="1183" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BDAAAB5-9E87-4D8C-88E8-9D5854070E70}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="1680" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1545" yWindow="1920" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1777,6 +1777,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5552,6 +5556,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="fb0bfce0-b493-4733-b695-336371de64d4" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a816e368-bd7d-4e73-ae60-f7bbf4d187c7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010049C730614A98FF4D948BAAFAA2763638" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="71752533c218a459f0bd7314a8d27046">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a816e368-bd7d-4e73-ae60-f7bbf4d187c7" xmlns:ns3="fb0bfce0-b493-4733-b695-336371de64d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56df45e61c8cd6f396207a6803100ce0" ns2:_="" ns3:_="">
     <xsd:import namespace="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
@@ -5764,27 +5788,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="fb0bfce0-b493-4733-b695-336371de64d4" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a816e368-bd7d-4e73-ae60-f7bbf4d187c7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD534FFF-F9D4-45E9-B4A8-C5178968AA79}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fb0bfce0-b493-4733-b695-336371de64d4"/>
+    <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5B4CFA9-3BF7-4410-A240-4C3EA4FF6CE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5801,23 +5824,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD534FFF-F9D4-45E9-B4A8-C5178968AA79}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fb0bfce0-b493-4733-b695-336371de64d4"/>
-    <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/LC-CNC-BoM.xlsx
+++ b/LC-CNC-BoM.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1183" documentId="11_FCC9E17DDF51C54A1A3D9BFC69DB0C4BF401B41C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BDAAAB5-9E87-4D8C-88E8-9D5854070E70}"/>
   <bookViews>
-    <workbookView xWindow="1545" yWindow="1920" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1715,23 +1715,14 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1745,22 +1736,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2064,24 +2064,24 @@
       <c r="B2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="60"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="74"/>
       <c r="G2" s="19">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="71" t="s">
+      <c r="K2" s="55" t="s">
         <v>264</v>
       </c>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="73"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="57"/>
     </row>
     <row r="3" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="43" t="s">
@@ -2122,7 +2122,7 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="58" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="67"/>
@@ -2130,14 +2130,14 @@
       <c r="E4" s="67"/>
       <c r="F4" s="67"/>
       <c r="G4" s="68"/>
-      <c r="J4" s="61" t="s">
+      <c r="J4" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="60"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
@@ -2221,14 +2221,14 @@
       </c>
     </row>
     <row r="7" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="60"/>
       <c r="J7" s="2" t="s">
         <v>171</v>
       </c>
@@ -2788,14 +2788,14 @@
         <f t="shared" si="4"/>
         <v>69.38</v>
       </c>
-      <c r="J21" s="61" t="s">
+      <c r="J21" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="62"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="63"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="60"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
@@ -2985,14 +2985,14 @@
         <f t="shared" si="6"/>
         <v>8.99</v>
       </c>
-      <c r="J26" s="61" t="s">
+      <c r="J26" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="K26" s="62"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="63"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="60"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
@@ -3354,13 +3354,13 @@
         <f t="shared" ref="G36:G37" si="11">E36*F36</f>
         <v>13.99</v>
       </c>
-      <c r="J36" s="64" t="s">
+      <c r="J36" s="61" t="s">
         <v>189</v>
       </c>
-      <c r="K36" s="65"/>
-      <c r="L36" s="65"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="66"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="62"/>
+      <c r="M36" s="62"/>
+      <c r="N36" s="63"/>
       <c r="O36" s="14">
         <f>SUM(O5:O35)</f>
         <v>1259.6799999999998</v>
@@ -3412,13 +3412,13 @@
       <c r="J38" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="K38" s="71" t="s">
+      <c r="K38" s="55" t="s">
         <v>266</v>
       </c>
-      <c r="L38" s="72"/>
-      <c r="M38" s="72"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="57"/>
     </row>
     <row r="39" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
@@ -3481,7 +3481,7 @@
         <f t="shared" si="12"/>
         <v>39.99</v>
       </c>
-      <c r="J40" s="61" t="s">
+      <c r="J40" s="58" t="s">
         <v>209</v>
       </c>
       <c r="K40" s="67"/>
@@ -3696,7 +3696,7 @@
       </c>
     </row>
     <row r="46" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="61" t="s">
+      <c r="B46" s="58" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="67"/>
@@ -3704,7 +3704,7 @@
       <c r="E46" s="67"/>
       <c r="F46" s="67"/>
       <c r="G46" s="68"/>
-      <c r="J46" s="61" t="s">
+      <c r="J46" s="58" t="s">
         <v>100</v>
       </c>
       <c r="K46" s="67"/>
@@ -3754,14 +3754,14 @@
       </c>
     </row>
     <row r="48" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="61" t="s">
+      <c r="B48" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="62"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="63"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="60"/>
       <c r="J48" s="2" t="s">
         <v>169</v>
       </c>
@@ -3802,13 +3802,13 @@
         <f t="shared" ref="G49:G101" si="14">E49*F49</f>
         <v>29.54</v>
       </c>
-      <c r="J49" s="64" t="s">
+      <c r="J49" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="K49" s="65"/>
-      <c r="L49" s="65"/>
-      <c r="M49" s="65"/>
-      <c r="N49" s="66"/>
+      <c r="K49" s="62"/>
+      <c r="L49" s="62"/>
+      <c r="M49" s="62"/>
+      <c r="N49" s="63"/>
       <c r="O49" s="14">
         <f>SUM(O40:O48)</f>
         <v>319.13</v>
@@ -3860,13 +3860,13 @@
       <c r="J51" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K51" s="71" t="s">
+      <c r="K51" s="55" t="s">
         <v>277</v>
       </c>
-      <c r="L51" s="72"/>
-      <c r="M51" s="72"/>
-      <c r="N51" s="72"/>
-      <c r="O51" s="73"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="56"/>
+      <c r="N51" s="56"/>
+      <c r="O51" s="57"/>
     </row>
     <row r="52" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
@@ -3929,7 +3929,7 @@
         <f t="shared" si="14"/>
         <v>15.24</v>
       </c>
-      <c r="J53" s="61" t="s">
+      <c r="J53" s="58" t="s">
         <v>209</v>
       </c>
       <c r="K53" s="67"/>
@@ -4000,7 +4000,7 @@
         <f t="shared" si="14"/>
         <v>41.8</v>
       </c>
-      <c r="J55" s="61" t="s">
+      <c r="J55" s="58" t="s">
         <v>100</v>
       </c>
       <c r="K55" s="67"/>
@@ -4071,7 +4071,7 @@
         <f t="shared" ref="G57:G64" si="16">E57*F57</f>
         <v>19.100000000000001</v>
       </c>
-      <c r="J57" s="61" t="s">
+      <c r="J57" s="58" t="s">
         <v>230</v>
       </c>
       <c r="K57" s="67"/>
@@ -4142,13 +4142,13 @@
         <f t="shared" si="16"/>
         <v>8.33</v>
       </c>
-      <c r="J59" s="64" t="s">
+      <c r="J59" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="K59" s="65"/>
-      <c r="L59" s="65"/>
-      <c r="M59" s="65"/>
-      <c r="N59" s="66"/>
+      <c r="K59" s="62"/>
+      <c r="L59" s="62"/>
+      <c r="M59" s="62"/>
+      <c r="N59" s="63"/>
       <c r="O59" s="14">
         <f>SUM(O54,O58)</f>
         <v>961.95</v>
@@ -4200,13 +4200,13 @@
       <c r="J61" s="33" t="s">
         <v>250</v>
       </c>
-      <c r="K61" s="71" t="s">
+      <c r="K61" s="55" t="s">
         <v>286</v>
       </c>
-      <c r="L61" s="72"/>
-      <c r="M61" s="72"/>
-      <c r="N61" s="72"/>
-      <c r="O61" s="73"/>
+      <c r="L61" s="56"/>
+      <c r="M61" s="56"/>
+      <c r="N61" s="56"/>
+      <c r="O61" s="57"/>
     </row>
     <row r="62" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="16" t="s">
@@ -4269,14 +4269,14 @@
         <f t="shared" si="16"/>
         <v>12.36</v>
       </c>
-      <c r="J63" s="61" t="s">
+      <c r="J63" s="58" t="s">
         <v>246</v>
       </c>
-      <c r="K63" s="69"/>
-      <c r="L63" s="69"/>
-      <c r="M63" s="69"/>
-      <c r="N63" s="69"/>
-      <c r="O63" s="70"/>
+      <c r="K63" s="75"/>
+      <c r="L63" s="75"/>
+      <c r="M63" s="75"/>
+      <c r="N63" s="75"/>
+      <c r="O63" s="76"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
@@ -4422,13 +4422,13 @@
         <f t="shared" si="19"/>
         <v>13.4</v>
       </c>
-      <c r="J67" s="64" t="s">
+      <c r="J67" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="K67" s="65"/>
-      <c r="L67" s="65"/>
-      <c r="M67" s="65"/>
-      <c r="N67" s="66"/>
+      <c r="K67" s="62"/>
+      <c r="L67" s="62"/>
+      <c r="M67" s="62"/>
+      <c r="N67" s="63"/>
       <c r="O67" s="32">
         <f>SUM(O64:O66)</f>
         <v>517</v>
@@ -4480,13 +4480,13 @@
       <c r="J69" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="K69" s="71" t="s">
+      <c r="K69" s="55" t="s">
         <v>276</v>
       </c>
-      <c r="L69" s="72"/>
-      <c r="M69" s="72"/>
-      <c r="N69" s="72"/>
-      <c r="O69" s="73"/>
+      <c r="L69" s="56"/>
+      <c r="M69" s="56"/>
+      <c r="N69" s="56"/>
+      <c r="O69" s="57"/>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
@@ -4549,14 +4549,14 @@
         <f t="shared" si="14"/>
         <v>27.76</v>
       </c>
-      <c r="J71" s="74" t="s">
+      <c r="J71" s="69" t="s">
         <v>275</v>
       </c>
-      <c r="K71" s="75"/>
-      <c r="L71" s="75"/>
-      <c r="M71" s="75"/>
-      <c r="N71" s="75"/>
-      <c r="O71" s="76"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="70"/>
+      <c r="M71" s="70"/>
+      <c r="N71" s="70"/>
+      <c r="O71" s="71"/>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
@@ -4784,14 +4784,14 @@
         <f t="shared" si="22"/>
         <v>7.02</v>
       </c>
-      <c r="J77" s="74" t="s">
+      <c r="J77" s="69" t="s">
         <v>283</v>
       </c>
-      <c r="K77" s="75"/>
-      <c r="L77" s="75"/>
-      <c r="M77" s="75"/>
-      <c r="N77" s="75"/>
-      <c r="O77" s="76"/>
+      <c r="K77" s="70"/>
+      <c r="L77" s="70"/>
+      <c r="M77" s="70"/>
+      <c r="N77" s="70"/>
+      <c r="O77" s="71"/>
     </row>
     <row r="78" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="2" t="s">
@@ -4936,13 +4936,13 @@
         <f t="shared" si="22"/>
         <v>9.58</v>
       </c>
-      <c r="J81" s="64" t="s">
+      <c r="J81" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="K81" s="65"/>
-      <c r="L81" s="65"/>
-      <c r="M81" s="65"/>
-      <c r="N81" s="65"/>
+      <c r="K81" s="62"/>
+      <c r="L81" s="62"/>
+      <c r="M81" s="62"/>
+      <c r="N81" s="62"/>
       <c r="O81" s="54">
         <f>SUM(O72:O80)</f>
         <v>411.5</v>
@@ -5155,14 +5155,14 @@
       </c>
     </row>
     <row r="92" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="61" t="s">
+      <c r="B92" s="58" t="s">
         <v>254</v>
       </c>
-      <c r="C92" s="62"/>
-      <c r="D92" s="62"/>
-      <c r="E92" s="62"/>
-      <c r="F92" s="62"/>
-      <c r="G92" s="63"/>
+      <c r="C92" s="59"/>
+      <c r="D92" s="59"/>
+      <c r="E92" s="59"/>
+      <c r="F92" s="59"/>
+      <c r="G92" s="60"/>
     </row>
     <row r="93" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B93" s="16" t="s">
@@ -5275,14 +5275,14 @@
       </c>
     </row>
     <row r="98" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="61" t="s">
+      <c r="B98" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="C98" s="62"/>
-      <c r="D98" s="62"/>
-      <c r="E98" s="62"/>
-      <c r="F98" s="62"/>
-      <c r="G98" s="63"/>
+      <c r="C98" s="59"/>
+      <c r="D98" s="59"/>
+      <c r="E98" s="59"/>
+      <c r="F98" s="59"/>
+      <c r="G98" s="60"/>
     </row>
     <row r="99" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="2" t="s">
@@ -5307,14 +5307,14 @@
       </c>
     </row>
     <row r="100" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="61" t="s">
+      <c r="B100" s="58" t="s">
         <v>235</v>
       </c>
-      <c r="C100" s="62"/>
-      <c r="D100" s="62"/>
-      <c r="E100" s="62"/>
-      <c r="F100" s="62"/>
-      <c r="G100" s="63"/>
+      <c r="C100" s="59"/>
+      <c r="D100" s="59"/>
+      <c r="E100" s="59"/>
+      <c r="F100" s="59"/>
+      <c r="G100" s="60"/>
     </row>
     <row r="101" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="2" t="s">
@@ -5339,39 +5339,39 @@
       </c>
     </row>
     <row r="102" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="55" t="s">
+      <c r="B102" s="64" t="s">
         <v>269</v>
       </c>
-      <c r="C102" s="56"/>
-      <c r="D102" s="56"/>
-      <c r="E102" s="56"/>
-      <c r="F102" s="57"/>
+      <c r="C102" s="65"/>
+      <c r="D102" s="65"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="66"/>
       <c r="G102" s="21">
         <f>SUM(G5:G101)</f>
         <v>2270.0560000000005</v>
       </c>
     </row>
     <row r="103" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="55" t="s">
+      <c r="B103" s="64" t="s">
         <v>270</v>
       </c>
-      <c r="C103" s="56"/>
-      <c r="D103" s="56"/>
-      <c r="E103" s="56"/>
-      <c r="F103" s="57"/>
+      <c r="C103" s="65"/>
+      <c r="D103" s="65"/>
+      <c r="E103" s="65"/>
+      <c r="F103" s="66"/>
       <c r="G103" s="52">
         <f>(SUM(G5:G101))/G2</f>
         <v>2270.0560000000005</v>
       </c>
     </row>
     <row r="104" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="55" t="s">
+      <c r="B104" s="64" t="s">
         <v>260</v>
       </c>
-      <c r="C104" s="56"/>
-      <c r="D104" s="56"/>
-      <c r="E104" s="56"/>
-      <c r="F104" s="57"/>
+      <c r="C104" s="65"/>
+      <c r="D104" s="65"/>
+      <c r="E104" s="65"/>
+      <c r="F104" s="66"/>
       <c r="G104" s="53">
         <f>G103+O67</f>
         <v>2787.0560000000005</v>
@@ -5383,6 +5383,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J21:O21"/>
+    <mergeCell ref="J26:O26"/>
+    <mergeCell ref="J36:N36"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B100:G100"/>
+    <mergeCell ref="J40:O40"/>
+    <mergeCell ref="J46:O46"/>
+    <mergeCell ref="J63:O63"/>
+    <mergeCell ref="K61:O61"/>
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="B92:G92"/>
     <mergeCell ref="J67:N67"/>
@@ -5399,22 +5415,6 @@
     <mergeCell ref="K38:O38"/>
     <mergeCell ref="J77:O77"/>
     <mergeCell ref="B98:G98"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="B102:F102"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J21:O21"/>
-    <mergeCell ref="J26:O26"/>
-    <mergeCell ref="J36:N36"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="B100:G100"/>
-    <mergeCell ref="J40:O40"/>
-    <mergeCell ref="J46:O46"/>
-    <mergeCell ref="J63:O63"/>
-    <mergeCell ref="K61:O61"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{182E6AD4-2BF8-453D-8168-0C5471656634}"/>
@@ -5556,15 +5556,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="fb0bfce0-b493-4733-b695-336371de64d4" xsi:nil="true"/>
@@ -5573,6 +5564,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5789,20 +5789,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD534FFF-F9D4-45E9-B4A8-C5178968AA79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="fb0bfce0-b493-4733-b695-336371de64d4"/>
     <ds:schemaRef ds:uri="a816e368-bd7d-4e73-ae60-f7bbf4d187c7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA33EB9-975B-4CAF-BADE-D8C6854E172C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
